--- a/docs/CDC/CDC_MODULES.xlsx
+++ b/docs/CDC/CDC_MODULES.xlsx
@@ -8433,7 +8433,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I119"/>
+  <dimension ref="A1:I117"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -8530,7 +8530,7 @@
         <v>Nom metier</v>
       </c>
       <c r="B6" t="str">
-        <v/>
+        <v>Maintenance - Demande de materiel</v>
       </c>
       <c r="C6" t="str">
         <v>ex. Maintenance, RH, SMQ</v>
@@ -8541,7 +8541,7 @@
         <v>Code court (URL)</v>
       </c>
       <c r="B7" t="str">
-        <v/>
+        <v>maintenance</v>
       </c>
       <c r="C7" t="str">
         <v>ex. maint, rh, smq</v>
@@ -8552,7 +8552,7 @@
         <v>Service responsable</v>
       </c>
       <c r="B8" t="str">
-        <v/>
+        <v>Service Maintenance</v>
       </c>
       <c r="C8" t="str">
         <v>equipe traitante</v>
@@ -8563,7 +8563,7 @@
         <v>Manager du service</v>
       </c>
       <c r="B9" t="str">
-        <v/>
+        <v>Sylvain ANTZ</v>
       </c>
       <c r="C9" t="str">
         <v>prenom NOM</v>
@@ -8574,7 +8574,7 @@
         <v>Hub projet/dossier ?</v>
       </c>
       <c r="B10" t="str">
-        <v/>
+        <v>NON</v>
       </c>
       <c r="C10" t="str">
         <v>OUI / NON</v>
@@ -8585,7 +8585,7 @@
         <v>Plusieurs sous-types ?</v>
       </c>
       <c r="B11" t="str">
-        <v/>
+        <v>NON</v>
       </c>
       <c r="C11" t="str">
         <v>OUI / NON</v>
@@ -8596,7 +8596,7 @@
         <v>Demandeurs autorises</v>
       </c>
       <c r="B12" t="str">
-        <v/>
+        <v>techniciens du service maintenance</v>
       </c>
       <c r="C12" t="str">
         <v>tous / managers / services X,Y</v>
@@ -8607,7 +8607,7 @@
         <v>Donnees sensibles ?</v>
       </c>
       <c r="B13" t="str">
-        <v/>
+        <v>NON</v>
       </c>
       <c r="C13" t="str">
         <v>OUI / NON</v>
@@ -8654,25 +8654,25 @@
         <v>1</v>
       </c>
       <c r="B17" t="str">
-        <v/>
+        <v>DEMANDE DE MATERIEL</v>
       </c>
       <c r="C17" t="str">
-        <v/>
+        <v>Commande d articles de maintenance</v>
       </c>
       <c r="D17" t="str">
-        <v/>
+        <v>logistique apres validation coordinateur</v>
       </c>
       <c r="E17" t="str">
-        <v/>
+        <v>Sylvain ANTZ (coordinateur)</v>
       </c>
       <c r="F17" t="str">
-        <v/>
+        <v>NON</v>
       </c>
       <c r="G17" t="str">
-        <v/>
+        <v>variable selon delai fournisseur</v>
       </c>
       <c r="H17" t="str">
-        <v/>
+        <v>date livraison souhaitee</v>
       </c>
     </row>
     <row r="18">
@@ -8832,7 +8832,7 @@
         <v>auto</v>
       </c>
       <c r="G25" t="str">
-        <v>pre-rempli</v>
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -8863,7 +8863,7 @@
         <v>3</v>
       </c>
       <c r="B27" t="str">
-        <v>Description</v>
+        <v>Justification / contexte</v>
       </c>
       <c r="C27" t="str">
         <v>textarea</v>
@@ -8878,7 +8878,7 @@
         <v>demandeur</v>
       </c>
       <c r="G27" t="str">
-        <v/>
+        <v>pour appuyer la validation</v>
       </c>
     </row>
     <row r="28">
@@ -8886,13 +8886,13 @@
         <v>4</v>
       </c>
       <c r="B28" t="str">
-        <v>Pieces jointes</v>
+        <v>Lignes d articles</v>
       </c>
       <c r="C28" t="str">
-        <v>files</v>
+        <v>sub-table</v>
       </c>
       <c r="D28" t="str">
-        <v>NON</v>
+        <v>OUI</v>
       </c>
       <c r="E28" t="str">
         <v>COMMUN</v>
@@ -8901,7 +8901,7 @@
         <v>demandeur</v>
       </c>
       <c r="G28" t="str">
-        <v/>
+        <v>cf. ligne ci-dessous</v>
       </c>
     </row>
     <row r="29">
@@ -8909,22 +8909,22 @@
         <v>5</v>
       </c>
       <c r="B29" t="str">
-        <v/>
+        <v xml:space="preserve">  - Article (ref)</v>
       </c>
       <c r="C29" t="str">
-        <v/>
+        <v>select (catalogue Divalto)</v>
       </c>
       <c r="D29" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="E29" t="str">
-        <v/>
+        <v>COMMUN</v>
       </c>
       <c r="F29" t="str">
-        <v/>
+        <v>demandeur</v>
       </c>
       <c r="G29" t="str">
-        <v/>
+        <v>autocomplete sur referentiel articles</v>
       </c>
     </row>
     <row r="30">
@@ -8932,22 +8932,22 @@
         <v>6</v>
       </c>
       <c r="B30" t="str">
-        <v/>
+        <v xml:space="preserve">  - Designation</v>
       </c>
       <c r="C30" t="str">
-        <v/>
+        <v>text</v>
       </c>
       <c r="D30" t="str">
-        <v/>
+        <v>auto</v>
       </c>
       <c r="E30" t="str">
-        <v/>
+        <v>COMMUN</v>
       </c>
       <c r="F30" t="str">
-        <v/>
+        <v>auto</v>
       </c>
       <c r="G30" t="str">
-        <v/>
+        <v>rempli depuis l article</v>
       </c>
     </row>
     <row r="31">
@@ -8955,19 +8955,19 @@
         <v>7</v>
       </c>
       <c r="B31" t="str">
-        <v/>
+        <v xml:space="preserve">  - Quantite</v>
       </c>
       <c r="C31" t="str">
-        <v/>
+        <v>number</v>
       </c>
       <c r="D31" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="E31" t="str">
-        <v/>
+        <v>COMMUN</v>
       </c>
       <c r="F31" t="str">
-        <v/>
+        <v>demandeur</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -8978,22 +8978,22 @@
         <v>8</v>
       </c>
       <c r="B32" t="str">
-        <v/>
+        <v>Date de besoin</v>
       </c>
       <c r="C32" t="str">
-        <v/>
+        <v>date</v>
       </c>
       <c r="D32" t="str">
-        <v/>
+        <v>NON</v>
       </c>
       <c r="E32" t="str">
-        <v/>
+        <v>COMMUN</v>
       </c>
       <c r="F32" t="str">
-        <v/>
+        <v>demandeur</v>
       </c>
       <c r="G32" t="str">
-        <v/>
+        <v>optionnel</v>
       </c>
     </row>
     <row r="33">
@@ -9001,22 +9001,22 @@
         <v>9</v>
       </c>
       <c r="B33" t="str">
-        <v/>
+        <v>Pieces jointes</v>
       </c>
       <c r="C33" t="str">
-        <v/>
+        <v>files</v>
       </c>
       <c r="D33" t="str">
-        <v/>
+        <v>NON</v>
       </c>
       <c r="E33" t="str">
-        <v/>
+        <v>COMMUN</v>
       </c>
       <c r="F33" t="str">
-        <v/>
+        <v>demandeur</v>
       </c>
       <c r="G33" t="str">
-        <v/>
+        <v>photo, plan, devis...</v>
       </c>
     </row>
     <row r="34">
@@ -9043,474 +9043,483 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="str">
+      <c r="A35">
+        <v>11</v>
+      </c>
+      <c r="B35" t="str">
+        <v/>
+      </c>
+      <c r="C35" t="str">
+        <v/>
+      </c>
+      <c r="D35" t="str">
+        <v/>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v/>
+      </c>
+      <c r="G35" t="str">
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="str">
-        <v># Aide types</v>
+      <c r="A36">
+        <v>12</v>
       </c>
       <c r="B36" t="str">
-        <v>text / textarea / number / date / datetime / select / multi-select / bool / files / profile / company / department</v>
+        <v/>
+      </c>
+      <c r="C36" t="str">
+        <v/>
+      </c>
+      <c r="D36" t="str">
+        <v/>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v/>
+      </c>
+      <c r="G36" t="str">
+        <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="str">
-        <v># Communs OU prestation</v>
+      <c r="A37">
+        <v>13</v>
       </c>
       <c r="B37" t="str">
-        <v>COMMUN ou nom(s) prestation(s) separes par |</v>
+        <v/>
+      </c>
+      <c r="C37" t="str">
+        <v/>
+      </c>
+      <c r="D37" t="str">
+        <v/>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v/>
+      </c>
+      <c r="G37" t="str">
+        <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="str">
+      <c r="A38">
+        <v>14</v>
+      </c>
+      <c r="B38" t="str">
+        <v/>
+      </c>
+      <c r="C38" t="str">
+        <v/>
+      </c>
+      <c r="D38" t="str">
+        <v/>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v/>
+      </c>
+      <c r="G38" t="str">
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>### 4. WORKFLOW (etats et transitions) ###</v>
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
+        <v># Aide types</v>
+      </c>
+      <c r="B40" t="str">
+        <v>text / textarea / number / date / datetime / select / multi-select / bool / files / profile / company / department</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v># Communs OU prestation</v>
+      </c>
+      <c r="B41" t="str">
+        <v>COMMUN ou nom(s) prestation(s) separes par |</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>### 4. WORKFLOW (etats et transitions) ###</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
         <v>#</v>
       </c>
-      <c r="B40" t="str">
+      <c r="B44" t="str">
         <v>Statut</v>
       </c>
-      <c r="C40" t="str">
+      <c r="C44" t="str">
         <v>Description</v>
       </c>
-      <c r="D40" t="str">
+      <c r="D44" t="str">
         <v>Qui agit ?</v>
       </c>
-      <c r="E40" t="str">
+      <c r="E44" t="str">
         <v>Statuts suivants</v>
       </c>
-      <c r="F40" t="str">
+      <c r="F44" t="str">
         <v>Action UI (label bouton)</v>
       </c>
-      <c r="G40" t="str">
+      <c r="G44" t="str">
         <v>Effet</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41">
-        <v>1</v>
-      </c>
-      <c r="B41" t="str">
-        <v>soumise</v>
-      </c>
-      <c r="C41" t="str">
-        <v>Demande creee</v>
-      </c>
-      <c r="D41" t="str">
-        <v/>
-      </c>
-      <c r="E41" t="str">
-        <v/>
-      </c>
-      <c r="F41" t="str">
-        <v/>
-      </c>
-      <c r="G41" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42">
-        <v>2</v>
-      </c>
-      <c r="B42" t="str">
-        <v>affectee</v>
-      </c>
-      <c r="C42" t="str">
-        <v>Affectee a executant</v>
-      </c>
-      <c r="D42" t="str">
-        <v/>
-      </c>
-      <c r="E42" t="str">
-        <v/>
-      </c>
-      <c r="F42" t="str">
-        <v/>
-      </c>
-      <c r="G42" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43">
-        <v>3</v>
-      </c>
-      <c r="B43" t="str">
-        <v>en_cours</v>
-      </c>
-      <c r="C43" t="str">
-        <v>En cours</v>
-      </c>
-      <c r="D43" t="str">
-        <v/>
-      </c>
-      <c r="E43" t="str">
-        <v/>
-      </c>
-      <c r="F43" t="str">
-        <v/>
-      </c>
-      <c r="G43" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44">
-        <v>4</v>
-      </c>
-      <c r="B44" t="str">
-        <v>a_valider</v>
-      </c>
-      <c r="C44" t="str">
-        <v>Attente validation</v>
-      </c>
-      <c r="D44" t="str">
-        <v/>
-      </c>
-      <c r="E44" t="str">
-        <v/>
-      </c>
-      <c r="F44" t="str">
-        <v/>
-      </c>
-      <c r="G44" t="str">
-        <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B45" t="str">
-        <v>complement_demande</v>
+        <v>en_attente_validation</v>
       </c>
       <c r="C45" t="str">
-        <v>Manque info</v>
+        <v>Demande creee, attente validation coordinateur</v>
       </c>
       <c r="D45" t="str">
-        <v/>
+        <v>Sylvain ANTZ</v>
       </c>
       <c r="E45" t="str">
-        <v/>
+        <v>demande_de_devis / refusee</v>
       </c>
       <c r="F45" t="str">
-        <v/>
+        <v>Valider / Refuser</v>
       </c>
       <c r="G45" t="str">
-        <v/>
+        <v>a la validation : creation tache commande pour logistique</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B46" t="str">
-        <v>realisee</v>
+        <v>demande_de_devis</v>
       </c>
       <c r="C46" t="str">
-        <v>Terminee</v>
+        <v>Logistique cherche fournisseur / devis</v>
       </c>
       <c r="D46" t="str">
-        <v>-</v>
+        <v>logistique</v>
       </c>
       <c r="E46" t="str">
-        <v>-</v>
+        <v>bon_de_commande_envoye</v>
       </c>
       <c r="F46" t="str">
-        <v>-</v>
+        <v>Devis recu</v>
       </c>
       <c r="G46" t="str">
-        <v>terminal</v>
+        <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B47" t="str">
-        <v>cloturee</v>
+        <v>bon_de_commande_envoye</v>
       </c>
       <c r="C47" t="str">
-        <v>Cloturee</v>
+        <v>BdC envoye au fournisseur</v>
       </c>
       <c r="D47" t="str">
-        <v>-</v>
+        <v>logistique</v>
       </c>
       <c r="E47" t="str">
-        <v>-</v>
+        <v>ar_recu</v>
       </c>
       <c r="F47" t="str">
-        <v>-</v>
+        <v>AR recu</v>
       </c>
       <c r="G47" t="str">
-        <v>terminal</v>
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B48" t="str">
-        <v>abandonnee</v>
+        <v>ar_recu</v>
       </c>
       <c r="C48" t="str">
-        <v>Annulee</v>
+        <v>Accuse reception fournisseur</v>
       </c>
       <c r="D48" t="str">
+        <v>logistique</v>
+      </c>
+      <c r="E48" t="str">
+        <v>commande_livree</v>
+      </c>
+      <c r="F48" t="str">
+        <v>Marquer livre</v>
+      </c>
+      <c r="G48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>5</v>
+      </c>
+      <c r="B49" t="str">
+        <v>commande_livree</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Materiel recu chez nous</v>
+      </c>
+      <c r="D49" t="str">
+        <v>logistique</v>
+      </c>
+      <c r="E49" t="str">
+        <v>commande_distribuee</v>
+      </c>
+      <c r="F49" t="str">
+        <v>Distribuer au technicien</v>
+      </c>
+      <c r="G49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>6</v>
+      </c>
+      <c r="B50" t="str">
+        <v>commande_distribuee</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Remis au technicien (terminal)</v>
+      </c>
+      <c r="D50" t="str">
         <v>-</v>
       </c>
-      <c r="E48" t="str">
+      <c r="E50" t="str">
         <v>-</v>
       </c>
-      <c r="F48" t="str">
+      <c r="F50" t="str">
         <v>-</v>
       </c>
-      <c r="G48" t="str">
+      <c r="G50" t="str">
         <v>terminal</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="str">
+    <row r="51">
+      <c r="A51">
+        <v>7</v>
+      </c>
+      <c r="B51" t="str">
+        <v>refusee</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Refusee par coordinateur</v>
+      </c>
+      <c r="D51" t="str">
+        <v>-</v>
+      </c>
+      <c r="E51" t="str">
+        <v>-</v>
+      </c>
+      <c r="F51" t="str">
+        <v>-</v>
+      </c>
+      <c r="G51" t="str">
+        <v>terminal - notif demandeur avec motif</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
         <v>### 5. SOUS-TACHES (uniquement si demande genere multi-taches) ###</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="str">
+    <row r="54">
+      <c r="A54" t="str">
         <v>#</v>
       </c>
-      <c r="B51" t="str">
+      <c r="B54" t="str">
         <v>Prestation</v>
       </c>
-      <c r="C51" t="str">
+      <c r="C54" t="str">
         <v>Sous-tache</v>
       </c>
-      <c r="D51" t="str">
+      <c r="D54" t="str">
         <v>Service cible</v>
       </c>
-      <c r="E51" t="str">
+      <c r="E54" t="str">
         <v>Affectation</v>
       </c>
-      <c r="F51" t="str">
+      <c r="F54" t="str">
         <v>Validateur N1</v>
       </c>
-      <c r="G51" t="str">
+      <c r="G54" t="str">
         <v>Duree</v>
       </c>
-      <c r="H51" t="str">
+      <c r="H54" t="str">
         <v>Ordre</v>
       </c>
-      <c r="I51" t="str">
+      <c r="I54" t="str">
         <v>Parallele ?</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52">
+    <row r="55">
+      <c r="A55">
         <v>1</v>
       </c>
-      <c r="B52" t="str">
-        <v/>
-      </c>
-      <c r="C52" t="str">
-        <v/>
-      </c>
-      <c r="D52" t="str">
-        <v/>
-      </c>
-      <c r="E52" t="str">
-        <v/>
-      </c>
-      <c r="F52" t="str">
-        <v/>
-      </c>
-      <c r="G52" t="str">
-        <v/>
-      </c>
-      <c r="H52">
+      <c r="B55" t="str">
+        <v/>
+      </c>
+      <c r="C55" t="str">
+        <v/>
+      </c>
+      <c r="D55" t="str">
+        <v/>
+      </c>
+      <c r="E55" t="str">
+        <v/>
+      </c>
+      <c r="F55" t="str">
+        <v/>
+      </c>
+      <c r="G55" t="str">
+        <v/>
+      </c>
+      <c r="H55">
         <v>0</v>
       </c>
-      <c r="I52" t="str">
-        <v>OUI</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
+      <c r="I55" t="str">
+        <v>OUI</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
         <v>2</v>
       </c>
-      <c r="B53" t="str">
-        <v/>
-      </c>
-      <c r="C53" t="str">
-        <v/>
-      </c>
-      <c r="D53" t="str">
-        <v/>
-      </c>
-      <c r="E53" t="str">
-        <v/>
-      </c>
-      <c r="F53" t="str">
-        <v/>
-      </c>
-      <c r="G53" t="str">
-        <v/>
-      </c>
-      <c r="H53">
+      <c r="B56" t="str">
+        <v/>
+      </c>
+      <c r="C56" t="str">
+        <v/>
+      </c>
+      <c r="D56" t="str">
+        <v/>
+      </c>
+      <c r="E56" t="str">
+        <v/>
+      </c>
+      <c r="F56" t="str">
+        <v/>
+      </c>
+      <c r="G56" t="str">
+        <v/>
+      </c>
+      <c r="H56">
         <v>0</v>
       </c>
-      <c r="I53" t="str">
-        <v>OUI</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
+      <c r="I56" t="str">
+        <v>OUI</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
         <v>3</v>
       </c>
-      <c r="B54" t="str">
-        <v/>
-      </c>
-      <c r="C54" t="str">
-        <v/>
-      </c>
-      <c r="D54" t="str">
-        <v/>
-      </c>
-      <c r="E54" t="str">
-        <v/>
-      </c>
-      <c r="F54" t="str">
-        <v/>
-      </c>
-      <c r="G54" t="str">
-        <v/>
-      </c>
-      <c r="H54">
+      <c r="B57" t="str">
+        <v/>
+      </c>
+      <c r="C57" t="str">
+        <v/>
+      </c>
+      <c r="D57" t="str">
+        <v/>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57" t="str">
+        <v/>
+      </c>
+      <c r="G57" t="str">
+        <v/>
+      </c>
+      <c r="H57">
         <v>0</v>
       </c>
-      <c r="I54" t="str">
-        <v>OUI</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="str">
+      <c r="I57" t="str">
+        <v>OUI</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
         <v>### 6. NOTIFICATIONS ###</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="str">
+    <row r="60">
+      <c r="A60" t="str">
         <v>#</v>
       </c>
-      <c r="B57" t="str">
+      <c r="B60" t="str">
         <v>Evenement</v>
       </c>
-      <c r="C57" t="str">
+      <c r="C60" t="str">
         <v>Destinataire(s)</v>
       </c>
-      <c r="D57" t="str">
+      <c r="D60" t="str">
         <v>Canal</v>
       </c>
-      <c r="E57" t="str">
+      <c r="E60" t="str">
         <v>Message</v>
       </c>
-      <c r="F57" t="str">
+      <c r="F60" t="str">
         <v>Priorite</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58">
-        <v>1</v>
-      </c>
-      <c r="B58" t="str">
-        <v>Demande soumise</v>
-      </c>
-      <c r="C58" t="str">
-        <v/>
-      </c>
-      <c r="D58" t="str">
-        <v>in-app</v>
-      </c>
-      <c r="E58" t="str">
-        <v/>
-      </c>
-      <c r="F58" t="str">
-        <v>normale</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59">
-        <v>2</v>
-      </c>
-      <c r="B59" t="str">
-        <v>Affectation</v>
-      </c>
-      <c r="C59" t="str">
-        <v/>
-      </c>
-      <c r="D59" t="str">
-        <v>in-app</v>
-      </c>
-      <c r="E59" t="str">
-        <v/>
-      </c>
-      <c r="F59" t="str">
-        <v>normale</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60">
-        <v>3</v>
-      </c>
-      <c r="B60" t="str">
-        <v>Demande validation</v>
-      </c>
-      <c r="C60" t="str">
-        <v/>
-      </c>
-      <c r="D60" t="str">
-        <v>in-app</v>
-      </c>
-      <c r="E60" t="str">
-        <v/>
-      </c>
-      <c r="F60" t="str">
-        <v>haute</v>
       </c>
     </row>
     <row r="61">
       <c r="A61">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B61" t="str">
-        <v>Complement demande</v>
+        <v>Demande soumise</v>
       </c>
       <c r="C61" t="str">
-        <v/>
+        <v>Sylvain ANTZ</v>
       </c>
       <c r="D61" t="str">
         <v>in-app</v>
       </c>
       <c r="E61" t="str">
-        <v/>
+        <v>Nouvelle demande materiel de &lt;demandeur&gt; - &lt;N lignes&gt; articles</v>
       </c>
       <c r="F61" t="str">
         <v>haute</v>
@@ -9518,19 +9527,19 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B62" t="str">
-        <v>Validee / Refusee</v>
+        <v>Validee</v>
       </c>
       <c r="C62" t="str">
-        <v/>
+        <v>demandeur + logistique</v>
       </c>
       <c r="D62" t="str">
         <v>in-app</v>
       </c>
       <c r="E62" t="str">
-        <v/>
+        <v>Votre demande materiel est validee, en cours de commande</v>
       </c>
       <c r="F62" t="str">
         <v>normale</v>
@@ -9538,55 +9547,82 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B63" t="str">
-        <v>Cloturee</v>
+        <v>Refusee</v>
       </c>
       <c r="C63" t="str">
-        <v/>
+        <v>demandeur</v>
       </c>
       <c r="D63" t="str">
         <v>in-app</v>
       </c>
       <c r="E63" t="str">
-        <v/>
+        <v>Votre demande materiel a ete refusee : &lt;motif&gt;</v>
       </c>
       <c r="F63" t="str">
-        <v>normale</v>
+        <v>haute</v>
       </c>
     </row>
     <row r="64">
       <c r="A64">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B64" t="str">
-        <v>SLA depasse</v>
+        <v>BdC envoye</v>
       </c>
       <c r="C64" t="str">
-        <v/>
+        <v>demandeur</v>
       </c>
       <c r="D64" t="str">
         <v>in-app</v>
       </c>
       <c r="E64" t="str">
-        <v/>
+        <v>Votre commande a ete passee aupres du fournisseur</v>
       </c>
       <c r="F64" t="str">
-        <v>urgente</v>
+        <v>normale</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="str">
-        <v/>
+      <c r="A65">
+        <v>5</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Livree</v>
+      </c>
+      <c r="C65" t="str">
+        <v>demandeur</v>
+      </c>
+      <c r="D65" t="str">
+        <v>in-app</v>
+      </c>
+      <c r="E65" t="str">
+        <v>Votre materiel est arrive, viens le retirer</v>
+      </c>
+      <c r="F65" t="str">
+        <v>haute</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="str">
-        <v># Note</v>
+      <c r="A66">
+        <v>6</v>
       </c>
       <c r="B66" t="str">
-        <v>Le commentaire de tache est deja gere par le trigger BE-010 (notif assigne+manager+demandeur). Inutile de le re-declarer.</v>
+        <v>Distribuee</v>
+      </c>
+      <c r="C66" t="str">
+        <v>demandeur</v>
+      </c>
+      <c r="D66" t="str">
+        <v>in-app</v>
+      </c>
+      <c r="E66" t="str">
+        <v>Materiel remis - merci de confirmer reception</v>
+      </c>
+      <c r="F66" t="str">
+        <v>normale</v>
       </c>
     </row>
     <row r="67">
@@ -9596,60 +9632,45 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>### 7. KPI DASHBOARD ###</v>
+        <v># Note</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Le commentaire de tache est deja gere par le trigger BE-010 (notif assigne+manager+demandeur). Inutile de le re-declarer.</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>### 7. KPI DASHBOARD ###</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
         <v>#</v>
       </c>
-      <c r="B69" t="str">
+      <c r="B71" t="str">
         <v>KPI (label)</v>
       </c>
-      <c r="C69" t="str">
+      <c r="C71" t="str">
         <v>Formule</v>
       </c>
-      <c r="D69" t="str">
+      <c r="D71" t="str">
         <v>Couleur</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70">
-        <v>1</v>
-      </c>
-      <c r="B70" t="str">
-        <v>Total actives</v>
-      </c>
-      <c r="C70" t="str">
-        <v>count(status NOT IN terminaux)</v>
-      </c>
-      <c r="D70" t="str">
-        <v>neutre</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71">
-        <v>2</v>
-      </c>
-      <c r="B71" t="str">
-        <v>En retard</v>
-      </c>
-      <c r="C71" t="str">
-        <v>count(due_date &lt; today AND active)</v>
-      </c>
-      <c r="D71" t="str">
-        <v>rouge</v>
       </c>
     </row>
     <row r="72">
       <c r="A72">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B72" t="str">
-        <v>A valider</v>
+        <v>Demandes en attente validation</v>
       </c>
       <c r="C72" t="str">
-        <v>count(status=a_valider)</v>
+        <v>count(status=en_attente_validation)</v>
       </c>
       <c r="D72" t="str">
         <v>ambre</v>
@@ -9657,81 +9678,90 @@
     </row>
     <row r="73">
       <c r="A73">
+        <v>2</v>
+      </c>
+      <c r="B73" t="str">
+        <v>En cours de commande</v>
+      </c>
+      <c r="C73" t="str">
+        <v>count(status IN (demande_de_devis, bon_de_commande_envoye, ar_recu))</v>
+      </c>
+      <c r="D73" t="str">
+        <v>bleu</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>3</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Livrees a distribuer</v>
+      </c>
+      <c r="C74" t="str">
+        <v>count(status=commande_livree)</v>
+      </c>
+      <c r="D74" t="str">
+        <v>vert</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
         <v>4</v>
       </c>
-      <c r="B73" t="str">
-        <v>Non assignees</v>
-      </c>
-      <c r="C73" t="str">
-        <v>count(assignee_id IS NULL AND active)</v>
-      </c>
-      <c r="D73" t="str">
-        <v>violet</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="str">
-        <v># Filtres souhaites</v>
-      </c>
       <c r="B75" t="str">
-        <v>Active ?</v>
+        <v>Refusees ce mois</v>
       </c>
       <c r="C75" t="str">
-        <v>Notes</v>
+        <v>count(status=refusee AND month=current)</v>
+      </c>
+      <c r="D75" t="str">
+        <v>rouge</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="str">
-        <v>Recherche libre</v>
+      <c r="A76">
+        <v>5</v>
       </c>
       <c r="B76" t="str">
-        <v>OUI</v>
+        <v>Total articles commandes ce mois</v>
       </c>
       <c r="C76" t="str">
-        <v>titre / numero</v>
+        <v>sum(quantite) sur ce mois</v>
+      </c>
+      <c r="D76" t="str">
+        <v>neutre</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Statut</v>
-      </c>
-      <c r="B77" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="C77" t="str">
         <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Demandeur</v>
+        <v># Filtres souhaites</v>
       </c>
       <c r="B78" t="str">
-        <v>OUI</v>
+        <v>Active ?</v>
       </c>
       <c r="C78" t="str">
-        <v/>
+        <v>Notes</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Assigne</v>
+        <v>Recherche libre</v>
       </c>
       <c r="B79" t="str">
         <v>OUI</v>
       </c>
       <c r="C79" t="str">
-        <v/>
+        <v>titre / numero</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>En retard (toggle)</v>
+        <v>Statut</v>
       </c>
       <c r="B80" t="str">
         <v>OUI</v>
@@ -9742,10 +9772,10 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Prestation</v>
+        <v>Demandeur</v>
       </c>
       <c r="B81" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="C81" t="str">
         <v/>
@@ -9753,10 +9783,10 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Filtre metier 1</v>
+        <v>Assigne</v>
       </c>
       <c r="B82" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="C82" t="str">
         <v/>
@@ -9764,124 +9794,79 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
+        <v>En retard (toggle)</v>
+      </c>
+      <c r="B83" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="C83" t="str">
         <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>### 8. PERMISSIONS ###</v>
+        <v>Prestation</v>
+      </c>
+      <c r="B84" t="str">
+        <v/>
+      </c>
+      <c r="C84" t="str">
+        <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Action</v>
+        <v>Filtre metier 1</v>
       </c>
       <c r="B85" t="str">
-        <v>Demandeur</v>
+        <v/>
       </c>
       <c r="C85" t="str">
-        <v>Executant/Cible</v>
-      </c>
-      <c r="D85" t="str">
-        <v>Manager service</v>
-      </c>
-      <c r="E85" t="str">
-        <v>Validateur N1</v>
-      </c>
-      <c r="F85" t="str">
-        <v>Validateur N2</v>
-      </c>
-      <c r="G85" t="str">
-        <v>Admin</v>
-      </c>
-      <c r="H85" t="str">
-        <v>Autre</v>
+        <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Creer demande</v>
-      </c>
-      <c r="B86" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="C86" t="str">
-        <v/>
-      </c>
-      <c r="D86" t="str">
-        <v/>
-      </c>
-      <c r="E86" t="str">
-        <v/>
-      </c>
-      <c r="F86" t="str">
-        <v/>
-      </c>
-      <c r="G86" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="H86" t="str">
         <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Voir ses demandes</v>
-      </c>
-      <c r="B87" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="C87" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="D87" t="str">
-        <v/>
-      </c>
-      <c r="E87" t="str">
-        <v/>
-      </c>
-      <c r="F87" t="str">
-        <v/>
-      </c>
-      <c r="G87" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="H87" t="str">
-        <v/>
+        <v>### 8. PERMISSIONS ###</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Voir TOUTES</v>
+        <v>Action</v>
       </c>
       <c r="B88" t="str">
-        <v/>
+        <v>Demandeur</v>
       </c>
       <c r="C88" t="str">
-        <v/>
+        <v>Executant/Cible</v>
       </c>
       <c r="D88" t="str">
-        <v/>
+        <v>Manager service</v>
       </c>
       <c r="E88" t="str">
-        <v/>
+        <v>Validateur N1</v>
       </c>
       <c r="F88" t="str">
-        <v/>
+        <v>Validateur N2</v>
       </c>
       <c r="G88" t="str">
-        <v>OUI</v>
+        <v>Admin</v>
       </c>
       <c r="H88" t="str">
-        <v/>
+        <v>Autre</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Affecter</v>
+        <v>Creer demande</v>
       </c>
       <c r="B89" t="str">
-        <v/>
+        <v>OUI (technicien maintenance)</v>
       </c>
       <c r="C89" t="str">
         <v/>
@@ -9904,10 +9889,10 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Reaffecter</v>
+        <v>Voir ses demandes</v>
       </c>
       <c r="B90" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="C90" t="str">
         <v/>
@@ -9930,10 +9915,10 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Annuler</v>
+        <v>Voir TOUTES</v>
       </c>
       <c r="B91" t="str">
-        <v>sienne</v>
+        <v/>
       </c>
       <c r="C91" t="str">
         <v/>
@@ -9951,12 +9936,12 @@
         <v>OUI</v>
       </c>
       <c r="H91" t="str">
-        <v/>
+        <v>Sylvain + logistique</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Valider N1</v>
+        <v>Valider/Refuser</v>
       </c>
       <c r="B92" t="str">
         <v/>
@@ -9968,7 +9953,7 @@
         <v/>
       </c>
       <c r="E92" t="str">
-        <v>OUI</v>
+        <v/>
       </c>
       <c r="F92" t="str">
         <v/>
@@ -9977,12 +9962,12 @@
         <v>OUI</v>
       </c>
       <c r="H92" t="str">
-        <v/>
+        <v>Sylvain ANTZ</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Valider N2</v>
+        <v>Faire avancer etat commande</v>
       </c>
       <c r="B93" t="str">
         <v/>
@@ -9997,61 +9982,76 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>OUI</v>
+        <v/>
       </c>
       <c r="G93" t="str">
         <v>OUI</v>
       </c>
       <c r="H93" t="str">
-        <v/>
+        <v>logistique</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
+        <v>Annuler une demande</v>
+      </c>
+      <c r="B94" t="str">
+        <v>la sienne (avant validation)</v>
+      </c>
+      <c r="C94" t="str">
+        <v/>
+      </c>
+      <c r="D94" t="str">
+        <v/>
+      </c>
+      <c r="E94" t="str">
+        <v/>
+      </c>
+      <c r="F94" t="str">
+        <v/>
+      </c>
+      <c r="G94" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="H94" t="str">
         <v/>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>### 9. HUB PROJET / DOSSIER (si applicable) ###</v>
+        <v/>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Champ</v>
-      </c>
-      <c r="B96" t="str">
-        <v>Valeur</v>
-      </c>
-      <c r="C96" t="str">
-        <v>Aide</v>
+        <v>### 9. HUB PROJET / DOSSIER (si applicable) ###</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Hub active ?</v>
+        <v>Champ</v>
       </c>
       <c r="B97" t="str">
-        <v/>
+        <v>Valeur</v>
       </c>
       <c r="C97" t="str">
-        <v>OUI / NON</v>
+        <v>Aide</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Concept</v>
+        <v>Hub active ?</v>
       </c>
       <c r="B98" t="str">
-        <v/>
+        <v>NON</v>
       </c>
       <c r="C98" t="str">
-        <v>ex. dossier client, projet R&amp;D, audit</v>
+        <v>chaque demande est independante</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Nom entite</v>
+        <v>Concept</v>
       </c>
       <c r="B99" t="str">
         <v/>
@@ -10062,196 +10062,181 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Code/identifiant</v>
+        <v>Nom entite</v>
       </c>
       <c r="B100" t="str">
         <v/>
       </c>
       <c r="C100" t="str">
-        <v>format</v>
+        <v/>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Onglets souhaites</v>
+        <v>Code/identifiant</v>
       </c>
       <c r="B101" t="str">
         <v/>
       </c>
       <c r="C101" t="str">
-        <v>Fiche / Taches / Timeline / Discussions / Fichiers</v>
+        <v/>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Visibilite</v>
+        <v>Onglets</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>qui peut lire / ecrire</v>
+        <v/>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
+        <v>Visibilite</v>
+      </c>
+      <c r="B103" t="str">
+        <v/>
+      </c>
+      <c r="C103" t="str">
         <v/>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>### 10. INTEGRATIONS EXTERNES ###</v>
+        <v/>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Outil</v>
-      </c>
-      <c r="B105" t="str">
-        <v>Pour quoi ?</v>
-      </c>
-      <c r="C105" t="str">
-        <v>Sens</v>
-      </c>
-      <c r="D105" t="str">
-        <v>Statut</v>
-      </c>
-      <c r="E105" t="str">
-        <v>Priorite</v>
+        <v>### 10. INTEGRATIONS EXTERNES ###</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Lucca</v>
+        <v>Outil</v>
       </c>
       <c r="B106" t="str">
-        <v/>
+        <v>Pour quoi ?</v>
       </c>
       <c r="C106" t="str">
-        <v/>
+        <v>Sens</v>
       </c>
       <c r="D106" t="str">
-        <v/>
+        <v>Statut</v>
       </c>
       <c r="E106" t="str">
-        <v/>
+        <v>Priorite</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Yooz</v>
+        <v>Divalto</v>
       </c>
       <c r="B107" t="str">
-        <v/>
+        <v>referentiel articles + creation BdC</v>
       </c>
       <c r="C107" t="str">
-        <v/>
+        <v>lecture+ecriture</v>
       </c>
       <c r="D107" t="str">
-        <v/>
+        <v>partiel</v>
       </c>
       <c r="E107" t="str">
-        <v/>
+        <v>haute</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Pipedrive</v>
+        <v>Yooz</v>
       </c>
       <c r="B108" t="str">
-        <v/>
+        <v>rapprochement facture fournisseur</v>
       </c>
       <c r="C108" t="str">
-        <v/>
+        <v>lecture</v>
       </c>
       <c r="D108" t="str">
-        <v/>
+        <v>a faire</v>
       </c>
       <c r="E108" t="str">
-        <v/>
+        <v>normale</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Divalto</v>
-      </c>
-      <c r="B109" t="str">
-        <v/>
-      </c>
-      <c r="C109" t="str">
-        <v/>
-      </c>
-      <c r="D109" t="str">
-        <v/>
-      </c>
-      <c r="E109" t="str">
         <v/>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>SharePoint</v>
-      </c>
-      <c r="B110" t="str">
-        <v/>
-      </c>
-      <c r="C110" t="str">
-        <v/>
-      </c>
-      <c r="D110" t="str">
-        <v/>
-      </c>
-      <c r="E110" t="str">
-        <v/>
+        <v>### 11. QUESTIONS OUVERTES ###</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v/>
+        <v>#</v>
       </c>
       <c r="B111" t="str">
-        <v/>
+        <v>Question</v>
       </c>
       <c r="C111" t="str">
-        <v/>
+        <v>Importance</v>
       </c>
       <c r="D111" t="str">
-        <v/>
-      </c>
-      <c r="E111" t="str">
-        <v/>
+        <v>Reponse</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="str">
+      <c r="A112">
+        <v>1</v>
+      </c>
+      <c r="B112" t="str">
+        <v>Le coordinateur Sylvain a-t-il un suppleant si absent ?</v>
+      </c>
+      <c r="C112" t="str">
+        <v>bloquant</v>
+      </c>
+      <c r="D112" t="str">
         <v/>
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="str">
-        <v>### 11. QUESTIONS OUVERTES ###</v>
+      <c r="A113">
+        <v>2</v>
+      </c>
+      <c r="B113" t="str">
+        <v>Refus : doit-on imposer un motif ? template de motifs ?</v>
+      </c>
+      <c r="C113" t="str">
+        <v>normal</v>
+      </c>
+      <c r="D113" t="str">
+        <v/>
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="str">
-        <v>#</v>
+      <c r="A114">
+        <v>3</v>
       </c>
       <c r="B114" t="str">
-        <v>Question</v>
+        <v>Articles : on garde le catalogue Divalto comme referentiel ou on stocke localement ?</v>
       </c>
       <c r="C114" t="str">
-        <v>Importance</v>
+        <v>normal</v>
       </c>
       <c r="D114" t="str">
-        <v>Reponse</v>
+        <v/>
       </c>
     </row>
     <row r="115">
       <c r="A115">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B115" t="str">
-        <v/>
+        <v>Limite budgetaire par demande (validation N2 si &gt; X EUR) ?</v>
       </c>
       <c r="C115" t="str">
         <v>normal</v>
@@ -10262,13 +10247,13 @@
     </row>
     <row r="116">
       <c r="A116">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B116" t="str">
-        <v/>
+        <v>Reset a zero des anciennes demandes en prod ?</v>
       </c>
       <c r="C116" t="str">
-        <v>normal</v>
+        <v>bloquant</v>
       </c>
       <c r="D116" t="str">
         <v/>
@@ -10276,10 +10261,10 @@
     </row>
     <row r="117">
       <c r="A117">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B117" t="str">
-        <v/>
+        <v>Le bouton "Distribuer" ferme la demande ou il y a une etape "confirmation reception technicien" ?</v>
       </c>
       <c r="C117" t="str">
         <v>normal</v>
@@ -10288,37 +10273,9 @@
         <v/>
       </c>
     </row>
-    <row r="118">
-      <c r="A118">
-        <v>4</v>
-      </c>
-      <c r="B118" t="str">
-        <v/>
-      </c>
-      <c r="C118" t="str">
-        <v>normal</v>
-      </c>
-      <c r="D118" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119">
-        <v>5</v>
-      </c>
-      <c r="B119" t="str">
-        <v/>
-      </c>
-      <c r="C119" t="str">
-        <v>normal</v>
-      </c>
-      <c r="D119" t="str">
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I119"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I117"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/docs/CDC/CDC_MODULES.xlsx
+++ b/docs/CDC/CDC_MODULES.xlsx
@@ -12174,7 +12174,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I119"/>
+  <dimension ref="A1:I160"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -12282,7 +12282,7 @@
         <v>Code court (URL)</v>
       </c>
       <c r="B7" t="str">
-        <v/>
+        <v>comm</v>
       </c>
       <c r="C7" t="str">
         <v>ex. maint, rh, smq</v>
@@ -12293,7 +12293,7 @@
         <v>Service responsable</v>
       </c>
       <c r="B8" t="str">
-        <v/>
+        <v>Service Communication / Marketing</v>
       </c>
       <c r="C8" t="str">
         <v>equipe traitante</v>
@@ -12304,7 +12304,7 @@
         <v>Manager du service</v>
       </c>
       <c r="B9" t="str">
-        <v/>
+        <v>Claire SASSIAS</v>
       </c>
       <c r="C9" t="str">
         <v>prenom NOM</v>
@@ -12315,7 +12315,7 @@
         <v>Hub projet/dossier ?</v>
       </c>
       <c r="B10" t="str">
-        <v/>
+        <v>NON</v>
       </c>
       <c r="C10" t="str">
         <v>OUI / NON</v>
@@ -12337,7 +12337,7 @@
         <v>Demandeurs autorises</v>
       </c>
       <c r="B12" t="str">
-        <v>?</v>
+        <v>tous les collaborateurs (avec filiale du demandeur)</v>
       </c>
       <c r="C12" t="str">
         <v>tous / managers / services X,Y</v>
@@ -12348,7 +12348,7 @@
         <v>Donnees sensibles ?</v>
       </c>
       <c r="B13" t="str">
-        <v/>
+        <v>NON</v>
       </c>
       <c r="C13" t="str">
         <v>OUI / NON</v>
@@ -12395,25 +12395,25 @@
         <v>1</v>
       </c>
       <c r="B17" t="str">
-        <v>RESERVATION DE STAND</v>
+        <v>DEMANDE COMMUNICATION MARKETING</v>
       </c>
       <c r="C17" t="str">
-        <v/>
+        <v>Demande generique creation/refonte d un livrable com (plaquette, prez, logo, kit, video, NL, site...)</v>
       </c>
       <c r="D17" t="str">
-        <v/>
+        <v>Claire SASSIAS (attribue ensuite a Geraldine PEIFFER, Diane MANGIN ou Chloe SARLOT)</v>
       </c>
       <c r="E17" t="str">
-        <v/>
+        <v>?</v>
       </c>
       <c r="F17" t="str">
-        <v/>
+        <v>NON</v>
       </c>
       <c r="G17" t="str">
-        <v/>
+        <v>variable</v>
       </c>
       <c r="H17" t="str">
-        <v/>
+        <v>date rendu souhaitee</v>
       </c>
     </row>
     <row r="18">
@@ -12421,25 +12421,25 @@
         <v>2</v>
       </c>
       <c r="B18" t="str">
-        <v>DEMANDE DE PRESTATION</v>
+        <v>RESERVATION STAND NOMADE</v>
       </c>
       <c r="C18" t="str">
-        <v/>
+        <v>Reservation et logistique d un stand pour un salon</v>
       </c>
       <c r="D18" t="str">
-        <v/>
+        <v>Claire SASSIAS / equipe Comm</v>
       </c>
       <c r="E18" t="str">
-        <v/>
+        <v>NON</v>
       </c>
       <c r="F18" t="str">
-        <v/>
+        <v>NON</v>
       </c>
       <c r="G18" t="str">
-        <v/>
+        <v>lie a date debut salon</v>
       </c>
       <c r="H18" t="str">
-        <v/>
+        <v>date reception souhaitee</v>
       </c>
     </row>
     <row r="19">
@@ -12573,7 +12573,7 @@
         <v>auto</v>
       </c>
       <c r="G25" t="str">
-        <v>pre-rempli</v>
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -12604,10 +12604,10 @@
         <v>3</v>
       </c>
       <c r="B27" t="str">
-        <v>Description</v>
+        <v>Filiale</v>
       </c>
       <c r="C27" t="str">
-        <v>textarea</v>
+        <v>select</v>
       </c>
       <c r="D27" t="str">
         <v>OUI</v>
@@ -12619,7 +12619,7 @@
         <v>demandeur</v>
       </c>
       <c r="G27" t="str">
-        <v/>
+        <v>KEON, KEON.BIO, KEON.CO, NASKEO, CAPCOO, TERGREEN, SYCOMORE, TEIKEI, GO PEI, AUTRES</v>
       </c>
     </row>
     <row r="28">
@@ -12627,22 +12627,22 @@
         <v>4</v>
       </c>
       <c r="B28" t="str">
-        <v>Pieces jointes</v>
+        <v>NOM DU PROJET</v>
       </c>
       <c r="C28" t="str">
-        <v>files</v>
+        <v>text</v>
       </c>
       <c r="D28" t="str">
-        <v>NON</v>
+        <v>OUI</v>
       </c>
       <c r="E28" t="str">
-        <v>COMMUN</v>
+        <v>DEMANDE COMMUNICATION MARKETING</v>
       </c>
       <c r="F28" t="str">
         <v>demandeur</v>
       </c>
       <c r="G28" t="str">
-        <v/>
+        <v>ex. COM SUMA, offre NASKEO</v>
       </c>
     </row>
     <row r="29">
@@ -12650,22 +12650,22 @@
         <v>5</v>
       </c>
       <c r="B29" t="str">
-        <v/>
+        <v>OBJECTIF</v>
       </c>
       <c r="C29" t="str">
-        <v/>
+        <v>textarea</v>
       </c>
       <c r="D29" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="E29" t="str">
-        <v/>
+        <v>DEMANDE COMMUNICATION MARKETING</v>
       </c>
       <c r="F29" t="str">
-        <v/>
+        <v>demandeur</v>
       </c>
       <c r="G29" t="str">
-        <v/>
+        <v>but : generer du lead, fideliser, faire acheter...</v>
       </c>
     </row>
     <row r="30">
@@ -12673,22 +12673,22 @@
         <v>6</v>
       </c>
       <c r="B30" t="str">
-        <v/>
+        <v>CIBLE</v>
       </c>
       <c r="C30" t="str">
-        <v/>
+        <v>textarea</v>
       </c>
       <c r="D30" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="E30" t="str">
-        <v/>
+        <v>DEMANDE COMMUNICATION MARKETING</v>
       </c>
       <c r="F30" t="str">
-        <v/>
+        <v>demandeur</v>
       </c>
       <c r="G30" t="str">
-        <v/>
+        <v>agriculteurs, porteurs de projet, collectivites...</v>
       </c>
     </row>
     <row r="31">
@@ -12696,22 +12696,22 @@
         <v>7</v>
       </c>
       <c r="B31" t="str">
-        <v/>
+        <v>DESCRIPTION DU BESOIN</v>
       </c>
       <c r="C31" t="str">
-        <v/>
+        <v>textarea</v>
       </c>
       <c r="D31" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="E31" t="str">
-        <v/>
+        <v>DEMANDE COMMUNICATION MARKETING</v>
       </c>
       <c r="F31" t="str">
-        <v/>
+        <v>demandeur</v>
       </c>
       <c r="G31" t="str">
-        <v/>
+        <v>redaction quelques lignes</v>
       </c>
     </row>
     <row r="32">
@@ -12719,22 +12719,22 @@
         <v>8</v>
       </c>
       <c r="B32" t="str">
-        <v/>
+        <v>CONTRAINTES</v>
       </c>
       <c r="C32" t="str">
-        <v/>
+        <v>textarea</v>
       </c>
       <c r="D32" t="str">
-        <v/>
+        <v>NON</v>
       </c>
       <c r="E32" t="str">
-        <v/>
+        <v>DEMANDE COMMUNICATION MARKETING</v>
       </c>
       <c r="F32" t="str">
-        <v/>
+        <v>demandeur</v>
       </c>
       <c r="G32" t="str">
-        <v/>
+        <v>canaux specifiques, partenariats...</v>
       </c>
     </row>
     <row r="33">
@@ -12742,19 +12742,19 @@
         <v>9</v>
       </c>
       <c r="B33" t="str">
-        <v/>
+        <v>DATE DE RENDU SOUHAITEE</v>
       </c>
       <c r="C33" t="str">
-        <v/>
+        <v>date</v>
       </c>
       <c r="D33" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="E33" t="str">
-        <v/>
+        <v>DEMANDE COMMUNICATION MARKETING</v>
       </c>
       <c r="F33" t="str">
-        <v/>
+        <v>demandeur</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -12765,96 +12765,180 @@
         <v>10</v>
       </c>
       <c r="B34" t="str">
-        <v/>
+        <v>DATE DE RENDU FIXEE</v>
       </c>
       <c r="C34" t="str">
-        <v/>
+        <v>date</v>
       </c>
       <c r="D34" t="str">
-        <v/>
+        <v>NON</v>
       </c>
       <c r="E34" t="str">
-        <v/>
+        <v>DEMANDE COMMUNICATION MARKETING</v>
       </c>
       <c r="F34" t="str">
-        <v/>
+        <v>cible (Claire/equipe)</v>
       </c>
       <c r="G34" t="str">
-        <v/>
+        <v>date reelle apres planning</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="str">
-        <v/>
+      <c r="A35">
+        <v>11</v>
+      </c>
+      <c r="B35" t="str">
+        <v>PRIORITE</v>
+      </c>
+      <c r="C35" t="str">
+        <v>select</v>
+      </c>
+      <c r="D35" t="str">
+        <v>NON</v>
+      </c>
+      <c r="E35" t="str">
+        <v>DEMANDE COMMUNICATION MARKETING</v>
+      </c>
+      <c r="F35" t="str">
+        <v>cible</v>
+      </c>
+      <c r="G35" t="str">
+        <v>PAS DE PRIORITE / PRIORITE MOYENNE / PRIORITE HAUTE</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="str">
-        <v># Aide types</v>
+      <c r="A36">
+        <v>12</v>
       </c>
       <c r="B36" t="str">
-        <v>text / textarea / number / date / datetime / select / multi-select / bool / files / profile / company / department</v>
+        <v>ATTRIBUTION</v>
+      </c>
+      <c r="C36" t="str">
+        <v>profile</v>
+      </c>
+      <c r="D36" t="str">
+        <v>NON</v>
+      </c>
+      <c r="E36" t="str">
+        <v>DEMANDE COMMUNICATION MARKETING</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Claire SASSIAS</v>
+      </c>
+      <c r="G36" t="str">
+        <v>Geraldine PEIFFER / Diane MANGIN / Chloe SARLOT</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="str">
-        <v># Communs OU prestation</v>
+      <c r="A37">
+        <v>13</v>
       </c>
       <c r="B37" t="str">
-        <v>COMMUN ou nom(s) prestation(s) separes par |</v>
+        <v>DESCRIPTION / COMMENTAIRES</v>
+      </c>
+      <c r="C37" t="str">
+        <v>textarea (longue)</v>
+      </c>
+      <c r="D37" t="str">
+        <v>NON</v>
+      </c>
+      <c r="E37" t="str">
+        <v>DEMANDE COMMUNICATION MARKETING</v>
+      </c>
+      <c r="F37" t="str">
+        <v>cible</v>
+      </c>
+      <c r="G37" t="str">
+        <v>fil d echange / suivi (deja un fil dans la liste actuelle)</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="str">
-        <v/>
+      <c r="A38">
+        <v>14</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Pieces jointes</v>
+      </c>
+      <c r="C38" t="str">
+        <v>files</v>
+      </c>
+      <c r="D38" t="str">
+        <v>NON</v>
+      </c>
+      <c r="E38" t="str">
+        <v>DEMANDE COMMUNICATION MARKETING</v>
+      </c>
+      <c r="F38" t="str">
+        <v>demandeur + cible</v>
+      </c>
+      <c r="G38" t="str">
+        <v>CDC, photos, charte...</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="str">
-        <v>### 4. WORKFLOW (etats et transitions) ###</v>
+      <c r="A39">
+        <v>15</v>
+      </c>
+      <c r="B39" t="str">
+        <v>NOM DU SALON</v>
+      </c>
+      <c r="C39" t="str">
+        <v>text</v>
+      </c>
+      <c r="D39" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="E39" t="str">
+        <v>RESERVATION STAND NOMADE</v>
+      </c>
+      <c r="F39" t="str">
+        <v>demandeur</v>
+      </c>
+      <c r="G39" t="str">
+        <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="str">
-        <v>#</v>
+      <c r="A40">
+        <v>16</v>
       </c>
       <c r="B40" t="str">
-        <v>Statut</v>
+        <v>DATE DEBUT DE SALON</v>
       </c>
       <c r="C40" t="str">
-        <v>Description</v>
+        <v>date</v>
       </c>
       <c r="D40" t="str">
-        <v>Qui agit ?</v>
+        <v>OUI</v>
       </c>
       <c r="E40" t="str">
-        <v>Statuts suivants</v>
+        <v>RESERVATION STAND NOMADE</v>
       </c>
       <c r="F40" t="str">
-        <v>Action UI (label bouton)</v>
+        <v>demandeur</v>
       </c>
       <c r="G40" t="str">
-        <v>Effet</v>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B41" t="str">
-        <v>soumise</v>
+        <v>DATE FIN DE SALON</v>
       </c>
       <c r="C41" t="str">
-        <v>Demande creee</v>
+        <v>date</v>
       </c>
       <c r="D41" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="E41" t="str">
-        <v/>
+        <v>RESERVATION STAND NOMADE</v>
       </c>
       <c r="F41" t="str">
-        <v/>
+        <v>demandeur</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -12862,22 +12946,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="B42" t="str">
-        <v>affectee</v>
+        <v>RESPONSABLE SALON</v>
       </c>
       <c r="C42" t="str">
-        <v>Affectee a executant</v>
+        <v>profile</v>
       </c>
       <c r="D42" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="E42" t="str">
-        <v/>
+        <v>RESERVATION STAND NOMADE</v>
       </c>
       <c r="F42" t="str">
-        <v/>
+        <v>demandeur</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -12885,68 +12969,68 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="B43" t="str">
-        <v>en_cours</v>
+        <v>Mode de recuperation du stand</v>
       </c>
       <c r="C43" t="str">
-        <v>En cours</v>
+        <v>select</v>
       </c>
       <c r="D43" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="E43" t="str">
-        <v/>
+        <v>RESERVATION STAND NOMADE</v>
       </c>
       <c r="F43" t="str">
-        <v/>
+        <v>demandeur</v>
       </c>
       <c r="G43" t="str">
-        <v/>
+        <v>A ENVOYER (transporteur) / RETRAIT SUR PLACE / ?</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="B44" t="str">
-        <v>a_valider</v>
+        <v>ADRESSE D ENVOI DU STAND</v>
       </c>
       <c r="C44" t="str">
-        <v>Attente validation</v>
+        <v>address</v>
       </c>
       <c r="D44" t="str">
-        <v/>
+        <v>conditionnel</v>
       </c>
       <c r="E44" t="str">
-        <v/>
+        <v>RESERVATION STAND NOMADE</v>
       </c>
       <c r="F44" t="str">
-        <v/>
+        <v>demandeur</v>
       </c>
       <c r="G44" t="str">
-        <v/>
+        <v>si Mode = A ENVOYER</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="B45" t="str">
-        <v>complement_demande</v>
+        <v>DATE RECEPTION STAND SOUHAITEE</v>
       </c>
       <c r="C45" t="str">
-        <v>Manque info</v>
+        <v>date</v>
       </c>
       <c r="D45" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="E45" t="str">
-        <v/>
+        <v>RESERVATION STAND NOMADE</v>
       </c>
       <c r="F45" t="str">
-        <v/>
+        <v>demandeur</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -12954,367 +13038,439 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B46" t="str">
-        <v>realisee</v>
+        <v>COLLABORATEUR QUI VA RECUPERER LE STAND</v>
       </c>
       <c r="C46" t="str">
-        <v>Terminee</v>
+        <v>profile</v>
       </c>
       <c r="D46" t="str">
-        <v>-</v>
+        <v>NON</v>
       </c>
       <c r="E46" t="str">
-        <v>-</v>
+        <v>RESERVATION STAND NOMADE</v>
       </c>
       <c r="F46" t="str">
-        <v>-</v>
+        <v>demandeur</v>
       </c>
       <c r="G46" t="str">
-        <v>terminal</v>
+        <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="B47" t="str">
-        <v>cloturee</v>
+        <v>DATE DE RECEPTION A BGN (retour)</v>
       </c>
       <c r="C47" t="str">
-        <v>Cloturee</v>
+        <v>date</v>
       </c>
       <c r="D47" t="str">
-        <v>-</v>
+        <v>OUI</v>
       </c>
       <c r="E47" t="str">
-        <v>-</v>
+        <v>RESERVATION STAND NOMADE</v>
       </c>
       <c r="F47" t="str">
-        <v>-</v>
+        <v>demandeur</v>
       </c>
       <c r="G47" t="str">
-        <v>terminal</v>
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="B48" t="str">
-        <v>abandonnee</v>
+        <v>COLLABORATEUR RESPONSABLE DU RETOUR</v>
       </c>
       <c r="C48" t="str">
-        <v>Annulee</v>
+        <v>profile</v>
       </c>
       <c r="D48" t="str">
-        <v>-</v>
+        <v>OUI</v>
       </c>
       <c r="E48" t="str">
-        <v>-</v>
+        <v>RESERVATION STAND NOMADE</v>
       </c>
       <c r="F48" t="str">
-        <v>-</v>
+        <v>demandeur</v>
       </c>
       <c r="G48" t="str">
-        <v>terminal</v>
+        <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="str">
-        <v/>
+      <c r="A49">
+        <v>25</v>
+      </c>
+      <c r="B49" t="str">
+        <v>MODE DE RETOUR DU STAND</v>
+      </c>
+      <c r="C49" t="str">
+        <v>select</v>
+      </c>
+      <c r="D49" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="E49" t="str">
+        <v>RESERVATION STAND NOMADE</v>
+      </c>
+      <c r="F49" t="str">
+        <v>demandeur</v>
+      </c>
+      <c r="G49" t="str">
+        <v>TRANSPORTEUR / DEPOSE PAR COLLAB / ?</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="str">
-        <v>### 5. SOUS-TACHES (uniquement si demande genere multi-taches) ###</v>
+      <c r="A50">
+        <v>26</v>
+      </c>
+      <c r="B50" t="str">
+        <v>KIT OPERATIONNEL</v>
+      </c>
+      <c r="C50" t="str">
+        <v>bool</v>
+      </c>
+      <c r="D50" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="E50" t="str">
+        <v>RESERVATION STAND NOMADE</v>
+      </c>
+      <c r="F50" t="str">
+        <v>demandeur</v>
+      </c>
+      <c r="G50" t="str">
+        <v>fournir kit ou pas</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="str">
-        <v>#</v>
+      <c r="A51">
+        <v>27</v>
       </c>
       <c r="B51" t="str">
-        <v>Prestation</v>
+        <v>GOODIES STYLOS (qte)</v>
       </c>
       <c r="C51" t="str">
-        <v>Sous-tache</v>
+        <v>number</v>
       </c>
       <c r="D51" t="str">
-        <v>Service cible</v>
+        <v>NON</v>
       </c>
       <c r="E51" t="str">
-        <v>Affectation</v>
+        <v>RESERVATION STAND NOMADE</v>
       </c>
       <c r="F51" t="str">
-        <v>Validateur N1</v>
+        <v>demandeur</v>
       </c>
       <c r="G51" t="str">
-        <v>Duree</v>
-      </c>
-      <c r="H51" t="str">
-        <v>Ordre</v>
-      </c>
-      <c r="I51" t="str">
-        <v>Parallele ?</v>
+        <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="B52" t="str">
-        <v/>
+        <v>GOODIES SEAUX (qte)</v>
       </c>
       <c r="C52" t="str">
-        <v/>
+        <v>number</v>
       </c>
       <c r="D52" t="str">
-        <v/>
+        <v>NON</v>
       </c>
       <c r="E52" t="str">
-        <v/>
+        <v>RESERVATION STAND NOMADE</v>
       </c>
       <c r="F52" t="str">
-        <v/>
+        <v>demandeur</v>
       </c>
       <c r="G52" t="str">
         <v/>
-      </c>
-      <c r="H52">
-        <v>0</v>
-      </c>
-      <c r="I52" t="str">
-        <v>OUI</v>
       </c>
     </row>
     <row r="53">
       <c r="A53">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="B53" t="str">
-        <v/>
+        <v>PLAQUETTES GROUPE KEON (qte)</v>
       </c>
       <c r="C53" t="str">
-        <v/>
+        <v>number</v>
       </c>
       <c r="D53" t="str">
-        <v/>
+        <v>NON</v>
       </c>
       <c r="E53" t="str">
-        <v/>
+        <v>RESERVATION STAND NOMADE</v>
       </c>
       <c r="F53" t="str">
-        <v/>
+        <v>demandeur</v>
       </c>
       <c r="G53" t="str">
         <v/>
-      </c>
-      <c r="H53">
-        <v>0</v>
-      </c>
-      <c r="I53" t="str">
-        <v>OUI</v>
       </c>
     </row>
     <row r="54">
       <c r="A54">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="B54" t="str">
-        <v/>
+        <v>PLAQUETTES GUIDE PRATIQUE (qte)</v>
       </c>
       <c r="C54" t="str">
-        <v/>
+        <v>number</v>
       </c>
       <c r="D54" t="str">
-        <v/>
+        <v>NON</v>
       </c>
       <c r="E54" t="str">
-        <v/>
+        <v>RESERVATION STAND NOMADE</v>
       </c>
       <c r="F54" t="str">
-        <v/>
+        <v>demandeur</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
-      <c r="H54">
-        <v>0</v>
-      </c>
-      <c r="I54" t="str">
-        <v>OUI</v>
-      </c>
     </row>
     <row r="55">
-      <c r="A55" t="str">
+      <c r="A55">
+        <v>31</v>
+      </c>
+      <c r="B55" t="str">
+        <v>PLAQUETTES METHA ET BIODECHETS (qte)</v>
+      </c>
+      <c r="C55" t="str">
+        <v>number</v>
+      </c>
+      <c r="D55" t="str">
+        <v>NON</v>
+      </c>
+      <c r="E55" t="str">
+        <v>RESERVATION STAND NOMADE</v>
+      </c>
+      <c r="F55" t="str">
+        <v>demandeur</v>
+      </c>
+      <c r="G55" t="str">
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="str">
-        <v>### 6. NOTIFICATIONS ###</v>
+      <c r="A56">
+        <v>32</v>
+      </c>
+      <c r="B56" t="str">
+        <v>PLAQUETTES TERGREEN (qte)</v>
+      </c>
+      <c r="C56" t="str">
+        <v>number</v>
+      </c>
+      <c r="D56" t="str">
+        <v>NON</v>
+      </c>
+      <c r="E56" t="str">
+        <v>RESERVATION STAND NOMADE</v>
+      </c>
+      <c r="F56" t="str">
+        <v>demandeur</v>
+      </c>
+      <c r="G56" t="str">
+        <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="str">
-        <v>#</v>
+      <c r="A57">
+        <v>33</v>
       </c>
       <c r="B57" t="str">
-        <v>Evenement</v>
+        <v>PLAQUETTES NSK MONOMETHA (qte)</v>
       </c>
       <c r="C57" t="str">
-        <v>Destinataire(s)</v>
+        <v>number</v>
       </c>
       <c r="D57" t="str">
-        <v>Canal</v>
+        <v>NON</v>
       </c>
       <c r="E57" t="str">
-        <v>Message</v>
+        <v>RESERVATION STAND NOMADE</v>
       </c>
       <c r="F57" t="str">
-        <v>Priorite</v>
+        <v>demandeur</v>
+      </c>
+      <c r="G57" t="str">
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="B58" t="str">
-        <v>Demande soumise</v>
+        <v>PLAQUETTES NASKEO (qte)</v>
       </c>
       <c r="C58" t="str">
-        <v/>
+        <v>number</v>
       </c>
       <c r="D58" t="str">
-        <v>in-app</v>
+        <v>NON</v>
       </c>
       <c r="E58" t="str">
-        <v/>
+        <v>RESERVATION STAND NOMADE</v>
       </c>
       <c r="F58" t="str">
-        <v>normale</v>
+        <v>demandeur</v>
+      </c>
+      <c r="G58" t="str">
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="B59" t="str">
-        <v>Affectation</v>
+        <v>REMARQUES PARTICULIERES</v>
       </c>
       <c r="C59" t="str">
-        <v/>
+        <v>textarea</v>
       </c>
       <c r="D59" t="str">
-        <v>in-app</v>
+        <v>NON</v>
       </c>
       <c r="E59" t="str">
-        <v/>
+        <v>RESERVATION STAND NOMADE</v>
       </c>
       <c r="F59" t="str">
-        <v>normale</v>
+        <v>demandeur</v>
+      </c>
+      <c r="G59" t="str">
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="B60" t="str">
-        <v>Demande validation</v>
+        <v/>
       </c>
       <c r="C60" t="str">
         <v/>
       </c>
       <c r="D60" t="str">
-        <v>in-app</v>
+        <v/>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>haute</v>
+        <v/>
+      </c>
+      <c r="G60" t="str">
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="B61" t="str">
-        <v>Complement demande</v>
+        <v/>
       </c>
       <c r="C61" t="str">
         <v/>
       </c>
       <c r="D61" t="str">
-        <v>in-app</v>
+        <v/>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>haute</v>
+        <v/>
+      </c>
+      <c r="G61" t="str">
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="B62" t="str">
-        <v>Validee / Refusee</v>
+        <v/>
       </c>
       <c r="C62" t="str">
         <v/>
       </c>
       <c r="D62" t="str">
-        <v>in-app</v>
+        <v/>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>normale</v>
+        <v/>
+      </c>
+      <c r="G62" t="str">
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="B63" t="str">
-        <v>Cloturee</v>
+        <v/>
       </c>
       <c r="C63" t="str">
         <v/>
       </c>
       <c r="D63" t="str">
-        <v>in-app</v>
+        <v/>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>normale</v>
+        <v/>
+      </c>
+      <c r="G63" t="str">
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="B64" t="str">
-        <v>SLA depasse</v>
+        <v/>
       </c>
       <c r="C64" t="str">
         <v/>
       </c>
       <c r="D64" t="str">
-        <v>in-app</v>
+        <v/>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>urgente</v>
+        <v/>
+      </c>
+      <c r="G64" t="str">
+        <v/>
       </c>
     </row>
     <row r="65">
@@ -13324,302 +13480,440 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v># Note</v>
+        <v># Aide types</v>
       </c>
       <c r="B66" t="str">
-        <v>Le commentaire de tache est deja gere par le trigger BE-010 (notif assigne+manager+demandeur). Inutile de le re-declarer.</v>
+        <v>text / textarea / number / date / datetime / select / multi-select / bool / files / profile / company / department</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v/>
+        <v># Communs OU prestation</v>
+      </c>
+      <c r="B67" t="str">
+        <v>COMMUN ou nom(s) prestation(s) separes par |</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>### 7. KPI DASHBOARD ###</v>
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
+        <v>### 4. WORKFLOW (etats et transitions) ###</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
         <v>#</v>
       </c>
-      <c r="B69" t="str">
-        <v>KPI (label)</v>
-      </c>
-      <c r="C69" t="str">
-        <v>Formule</v>
-      </c>
-      <c r="D69" t="str">
-        <v>Couleur</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70">
-        <v>1</v>
-      </c>
       <c r="B70" t="str">
-        <v>Total actives</v>
+        <v>Statut</v>
       </c>
       <c r="C70" t="str">
-        <v>count(status NOT IN terminaux)</v>
+        <v>Description</v>
       </c>
       <c r="D70" t="str">
-        <v>neutre</v>
+        <v>Qui agit ?</v>
+      </c>
+      <c r="E70" t="str">
+        <v>Statuts suivants</v>
+      </c>
+      <c r="F70" t="str">
+        <v>Action UI (label bouton)</v>
+      </c>
+      <c r="G70" t="str">
+        <v>Effet</v>
       </c>
     </row>
     <row r="71">
       <c r="A71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B71" t="str">
-        <v>En retard</v>
+        <v>soumise</v>
       </c>
       <c r="C71" t="str">
-        <v>count(due_date &lt; today AND active)</v>
+        <v>Demande creee</v>
       </c>
       <c r="D71" t="str">
-        <v>rouge</v>
+        <v>Claire SASSIAS</v>
+      </c>
+      <c r="E71" t="str">
+        <v>attribuee</v>
+      </c>
+      <c r="F71" t="str">
+        <v>Affecter (Geraldine/Diane/Chloe)</v>
+      </c>
+      <c r="G71" t="str">
+        <v>fixe priorite + date rendu fixee</v>
       </c>
     </row>
     <row r="72">
       <c r="A72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B72" t="str">
-        <v>A valider</v>
+        <v>attribuee</v>
       </c>
       <c r="C72" t="str">
-        <v>count(status=a_valider)</v>
+        <v>Attribuee a un createur</v>
       </c>
       <c r="D72" t="str">
-        <v>ambre</v>
+        <v>cible</v>
+      </c>
+      <c r="E72" t="str">
+        <v>brief</v>
+      </c>
+      <c r="F72" t="str">
+        <v>Demarrer brief</v>
+      </c>
+      <c r="G72" t="str">
+        <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73">
+        <v>3</v>
+      </c>
+      <c r="B73" t="str">
+        <v>brief</v>
+      </c>
+      <c r="C73" t="str">
+        <v>Cadrage en cours avec demandeur</v>
+      </c>
+      <c r="D73" t="str">
+        <v>cible</v>
+      </c>
+      <c r="E73" t="str">
+        <v>conception</v>
+      </c>
+      <c r="F73" t="str">
+        <v/>
+      </c>
+      <c r="G73" t="str">
+        <v>date_brief</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
         <v>4</v>
       </c>
-      <c r="B73" t="str">
-        <v>Non assignees</v>
-      </c>
-      <c r="C73" t="str">
-        <v>count(assignee_id IS NULL AND active)</v>
-      </c>
-      <c r="D73" t="str">
-        <v>violet</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="str">
-        <v/>
+      <c r="B74" t="str">
+        <v>conception</v>
+      </c>
+      <c r="C74" t="str">
+        <v>Definition de la creation</v>
+      </c>
+      <c r="D74" t="str">
+        <v>cible</v>
+      </c>
+      <c r="E74" t="str">
+        <v>creation</v>
+      </c>
+      <c r="F74" t="str">
+        <v/>
+      </c>
+      <c r="G74" t="str">
+        <v>date_conception</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="str">
-        <v># Filtres souhaites</v>
+      <c r="A75">
+        <v>5</v>
       </c>
       <c r="B75" t="str">
-        <v>Active ?</v>
+        <v>creation</v>
       </c>
       <c r="C75" t="str">
-        <v>Notes</v>
+        <v>Realisation du livrable</v>
+      </c>
+      <c r="D75" t="str">
+        <v>cible</v>
+      </c>
+      <c r="E75" t="str">
+        <v>production</v>
+      </c>
+      <c r="F75" t="str">
+        <v/>
+      </c>
+      <c r="G75" t="str">
+        <v>date_creation</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="str">
-        <v>Recherche libre</v>
+      <c r="A76">
+        <v>6</v>
       </c>
       <c r="B76" t="str">
-        <v>OUI</v>
+        <v>production</v>
       </c>
       <c r="C76" t="str">
-        <v>titre / numero</v>
+        <v>Production / impression / fournisseur externe</v>
+      </c>
+      <c r="D76" t="str">
+        <v>cible</v>
+      </c>
+      <c r="E76" t="str">
+        <v>recette</v>
+      </c>
+      <c r="F76" t="str">
+        <v/>
+      </c>
+      <c r="G76" t="str">
+        <v>date_production</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="str">
-        <v>Statut</v>
+      <c r="A77">
+        <v>7</v>
       </c>
       <c r="B77" t="str">
-        <v>OUI</v>
+        <v>recette</v>
       </c>
       <c r="C77" t="str">
-        <v/>
+        <v>Validation finale par demandeur</v>
+      </c>
+      <c r="D77" t="str">
+        <v>demandeur</v>
+      </c>
+      <c r="E77" t="str">
+        <v>terminee / creation (si modifs)</v>
+      </c>
+      <c r="F77" t="str">
+        <v>Valider / Demander modif</v>
+      </c>
+      <c r="G77" t="str">
+        <v>date_recette</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="str">
-        <v>Demandeur</v>
+      <c r="A78">
+        <v>8</v>
       </c>
       <c r="B78" t="str">
-        <v>OUI</v>
+        <v>terminee</v>
       </c>
       <c r="C78" t="str">
-        <v/>
+        <v>Livrable valide</v>
+      </c>
+      <c r="D78" t="str">
+        <v>-</v>
+      </c>
+      <c r="E78" t="str">
+        <v>livraison</v>
+      </c>
+      <c r="F78" t="str">
+        <v/>
+      </c>
+      <c r="G78" t="str">
+        <v>date_terminee</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="str">
-        <v>Assigne</v>
+      <c r="A79">
+        <v>9</v>
       </c>
       <c r="B79" t="str">
-        <v>OUI</v>
+        <v>livraison</v>
       </c>
       <c r="C79" t="str">
-        <v/>
+        <v>Livre au destinataire (terminal)</v>
+      </c>
+      <c r="D79" t="str">
+        <v>-</v>
+      </c>
+      <c r="E79" t="str">
+        <v>-</v>
+      </c>
+      <c r="F79" t="str">
+        <v>-</v>
+      </c>
+      <c r="G79" t="str">
+        <v>date_livraison - terminal</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="str">
-        <v>En retard (toggle)</v>
+      <c r="A80">
+        <v>10</v>
       </c>
       <c r="B80" t="str">
-        <v>OUI</v>
+        <v>abandonnee</v>
       </c>
       <c r="C80" t="str">
-        <v/>
+        <v>Abandonnee (terminal)</v>
+      </c>
+      <c r="D80" t="str">
+        <v>-</v>
+      </c>
+      <c r="E80" t="str">
+        <v>-</v>
+      </c>
+      <c r="F80" t="str">
+        <v>-</v>
+      </c>
+      <c r="G80" t="str">
+        <v>terminal</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="str">
-        <v>Prestation</v>
+      <c r="A81">
+        <v>11</v>
       </c>
       <c r="B81" t="str">
-        <v/>
+        <v>stand_reservee</v>
       </c>
       <c r="C81" t="str">
-        <v/>
+        <v>Stand reserve, attente prep</v>
+      </c>
+      <c r="D81" t="str">
+        <v>equipe Comm</v>
+      </c>
+      <c r="E81" t="str">
+        <v>stand_prepare</v>
+      </c>
+      <c r="F81" t="str">
+        <v>Marquer prepare</v>
+      </c>
+      <c r="G81" t="str">
+        <v>specifique stand</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="str">
-        <v>Filtre metier 1</v>
+      <c r="A82">
+        <v>12</v>
       </c>
       <c r="B82" t="str">
-        <v/>
+        <v>stand_envoye</v>
       </c>
       <c r="C82" t="str">
-        <v/>
+        <v>Stand envoye au lieu salon</v>
+      </c>
+      <c r="D82" t="str">
+        <v>equipe Comm</v>
+      </c>
+      <c r="E82" t="str">
+        <v>stand_au_salon</v>
+      </c>
+      <c r="F82" t="str">
+        <v/>
+      </c>
+      <c r="G82" t="str">
+        <v>specifique stand</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="str">
-        <v/>
+      <c r="A83">
+        <v>13</v>
+      </c>
+      <c r="B83" t="str">
+        <v>stand_au_salon</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Stand sur le salon</v>
+      </c>
+      <c r="D83" t="str">
+        <v>responsable salon</v>
+      </c>
+      <c r="E83" t="str">
+        <v>stand_retour</v>
+      </c>
+      <c r="F83" t="str">
+        <v/>
+      </c>
+      <c r="G83" t="str">
+        <v>specifique stand</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="str">
-        <v>### 8. PERMISSIONS ###</v>
+      <c r="A84">
+        <v>14</v>
+      </c>
+      <c r="B84" t="str">
+        <v>stand_retour</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Stand revenu a BGN</v>
+      </c>
+      <c r="D84" t="str">
+        <v>equipe Comm</v>
+      </c>
+      <c r="E84" t="str">
+        <v>stand_cloturee</v>
+      </c>
+      <c r="F84" t="str">
+        <v/>
+      </c>
+      <c r="G84" t="str">
+        <v>specifique stand</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="str">
-        <v>Action</v>
+      <c r="A85">
+        <v>15</v>
       </c>
       <c r="B85" t="str">
-        <v>Demandeur</v>
+        <v>stand_cloturee</v>
       </c>
       <c r="C85" t="str">
-        <v>Executant/Cible</v>
+        <v>Cloturee (terminal)</v>
       </c>
       <c r="D85" t="str">
-        <v>Manager service</v>
+        <v>-</v>
       </c>
       <c r="E85" t="str">
-        <v>Validateur N1</v>
+        <v>-</v>
       </c>
       <c r="F85" t="str">
-        <v>Validateur N2</v>
+        <v>-</v>
       </c>
       <c r="G85" t="str">
-        <v>Admin</v>
-      </c>
-      <c r="H85" t="str">
-        <v>Autre</v>
+        <v>specifique stand - terminal</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Creer demande</v>
-      </c>
-      <c r="B86" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="C86" t="str">
-        <v/>
-      </c>
-      <c r="D86" t="str">
-        <v/>
-      </c>
-      <c r="E86" t="str">
-        <v/>
-      </c>
-      <c r="F86" t="str">
-        <v/>
-      </c>
-      <c r="G86" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="H86" t="str">
         <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Voir ses demandes</v>
-      </c>
-      <c r="B87" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="C87" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="D87" t="str">
-        <v/>
-      </c>
-      <c r="E87" t="str">
-        <v/>
-      </c>
-      <c r="F87" t="str">
-        <v/>
-      </c>
-      <c r="G87" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="H87" t="str">
-        <v/>
+        <v>### 5. SOUS-TACHES (uniquement si demande genere multi-taches) ###</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Voir TOUTES</v>
+        <v>#</v>
       </c>
       <c r="B88" t="str">
-        <v/>
+        <v>Prestation</v>
       </c>
       <c r="C88" t="str">
-        <v/>
+        <v>Sous-tache</v>
       </c>
       <c r="D88" t="str">
-        <v/>
+        <v>Service cible</v>
       </c>
       <c r="E88" t="str">
-        <v/>
+        <v>Affectation</v>
       </c>
       <c r="F88" t="str">
-        <v/>
+        <v>Validateur N1</v>
       </c>
       <c r="G88" t="str">
-        <v>OUI</v>
+        <v>Duree</v>
       </c>
       <c r="H88" t="str">
-        <v/>
+        <v>Ordre</v>
+      </c>
+      <c r="I88" t="str">
+        <v>Parallele ?</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="str">
-        <v>Affecter</v>
+      <c r="A89">
+        <v>1</v>
       </c>
       <c r="B89" t="str">
         <v/>
@@ -13637,15 +13931,18 @@
         <v/>
       </c>
       <c r="G89" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="H89" t="str">
-        <v/>
+        <v/>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+      <c r="I89" t="str">
+        <v>OUI</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="str">
-        <v>Reaffecter</v>
+      <c r="A90">
+        <v>2</v>
       </c>
       <c r="B90" t="str">
         <v/>
@@ -13663,18 +13960,21 @@
         <v/>
       </c>
       <c r="G90" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="H90" t="str">
-        <v/>
+        <v/>
+      </c>
+      <c r="H90">
+        <v>0</v>
+      </c>
+      <c r="I90" t="str">
+        <v>OUI</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="str">
-        <v>Annuler</v>
+      <c r="A91">
+        <v>3</v>
       </c>
       <c r="B91" t="str">
-        <v>sienne</v>
+        <v/>
       </c>
       <c r="C91" t="str">
         <v/>
@@ -13689,377 +13989,978 @@
         <v/>
       </c>
       <c r="G91" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="H91" t="str">
-        <v/>
+        <v/>
+      </c>
+      <c r="H91">
+        <v>0</v>
+      </c>
+      <c r="I91" t="str">
+        <v>OUI</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Valider N1</v>
-      </c>
-      <c r="B92" t="str">
-        <v/>
-      </c>
-      <c r="C92" t="str">
-        <v/>
-      </c>
-      <c r="D92" t="str">
-        <v/>
-      </c>
-      <c r="E92" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="F92" t="str">
-        <v/>
-      </c>
-      <c r="G92" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="H92" t="str">
         <v/>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Valider N2</v>
-      </c>
-      <c r="B93" t="str">
-        <v/>
-      </c>
-      <c r="C93" t="str">
-        <v/>
-      </c>
-      <c r="D93" t="str">
-        <v/>
-      </c>
-      <c r="E93" t="str">
-        <v/>
-      </c>
-      <c r="F93" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="G93" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="H93" t="str">
-        <v/>
+        <v>### 6. NOTIFICATIONS ###</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v/>
+        <v>#</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Evenement</v>
+      </c>
+      <c r="C94" t="str">
+        <v>Destinataire(s)</v>
+      </c>
+      <c r="D94" t="str">
+        <v>Canal</v>
+      </c>
+      <c r="E94" t="str">
+        <v>Message</v>
+      </c>
+      <c r="F94" t="str">
+        <v>Priorite</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="str">
-        <v>### 9. HUB PROJET / DOSSIER (si applicable) ###</v>
+      <c r="A95">
+        <v>1</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Demande soumise</v>
+      </c>
+      <c r="C95" t="str">
+        <v>Claire SASSIAS</v>
+      </c>
+      <c r="D95" t="str">
+        <v>in-app</v>
+      </c>
+      <c r="E95" t="str">
+        <v>Nouvelle demande comm &lt;type&gt; de &lt;demandeur&gt; pour &lt;filiale&gt;</v>
+      </c>
+      <c r="F95" t="str">
+        <v>haute</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="str">
-        <v>Champ</v>
+      <c r="A96">
+        <v>2</v>
       </c>
       <c r="B96" t="str">
-        <v>Valeur</v>
+        <v>Attribution</v>
       </c>
       <c r="C96" t="str">
-        <v>Aide</v>
+        <v>cible (Geraldine/Diane/Chloe)</v>
+      </c>
+      <c r="D96" t="str">
+        <v>in-app</v>
+      </c>
+      <c r="E96" t="str">
+        <v>Vous etes attribuee sur &lt;projet&gt;, rendu &lt;date_rendu_fixee&gt;</v>
+      </c>
+      <c r="F96" t="str">
+        <v>normale</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="str">
-        <v>Hub active ?</v>
+      <c r="A97">
+        <v>3</v>
       </c>
       <c r="B97" t="str">
-        <v/>
+        <v>Brief lance</v>
       </c>
       <c r="C97" t="str">
-        <v>OUI / NON</v>
+        <v>demandeur</v>
+      </c>
+      <c r="D97" t="str">
+        <v>in-app</v>
+      </c>
+      <c r="E97" t="str">
+        <v>Le brief de votre projet &lt;nom&gt; demarre</v>
+      </c>
+      <c r="F97" t="str">
+        <v>normale</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="str">
-        <v>Concept</v>
+      <c r="A98">
+        <v>4</v>
       </c>
       <c r="B98" t="str">
-        <v/>
+        <v>Recette demandee</v>
       </c>
       <c r="C98" t="str">
-        <v>ex. dossier client, projet R&amp;D, audit</v>
+        <v>demandeur</v>
+      </c>
+      <c r="D98" t="str">
+        <v>in-app</v>
+      </c>
+      <c r="E98" t="str">
+        <v>Votre projet &lt;nom&gt; est pret pour validation</v>
+      </c>
+      <c r="F98" t="str">
+        <v>haute</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="str">
-        <v>Nom entite</v>
+      <c r="A99">
+        <v>5</v>
       </c>
       <c r="B99" t="str">
-        <v/>
+        <v>Modif demandee</v>
       </c>
       <c r="C99" t="str">
-        <v/>
+        <v>cible</v>
+      </c>
+      <c r="D99" t="str">
+        <v>in-app</v>
+      </c>
+      <c r="E99" t="str">
+        <v>&lt;demandeur&gt; demande des modifications sur &lt;nom&gt;</v>
+      </c>
+      <c r="F99" t="str">
+        <v>haute</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="str">
-        <v>Code/identifiant</v>
+      <c r="A100">
+        <v>6</v>
       </c>
       <c r="B100" t="str">
-        <v/>
+        <v>Livraison</v>
       </c>
       <c r="C100" t="str">
-        <v>format</v>
+        <v>demandeur + filiale concernee</v>
+      </c>
+      <c r="D100" t="str">
+        <v>in-app</v>
+      </c>
+      <c r="E100" t="str">
+        <v>Projet &lt;nom&gt; livre</v>
+      </c>
+      <c r="F100" t="str">
+        <v>normale</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="str">
-        <v>Onglets souhaites</v>
+      <c r="A101">
+        <v>7</v>
       </c>
       <c r="B101" t="str">
-        <v/>
+        <v>Stand reserve</v>
       </c>
       <c r="C101" t="str">
-        <v>Fiche / Taches / Timeline / Discussions / Fichiers</v>
+        <v>responsable salon</v>
+      </c>
+      <c r="D101" t="str">
+        <v>in-app</v>
+      </c>
+      <c r="E101" t="str">
+        <v>Votre stand pour &lt;salon&gt; est confirme</v>
+      </c>
+      <c r="F101" t="str">
+        <v>normale</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="str">
-        <v>Visibilite</v>
+      <c r="A102">
+        <v>8</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>Stand expedie</v>
       </c>
       <c r="C102" t="str">
-        <v>qui peut lire / ecrire</v>
+        <v>responsable salon + collab recuperation</v>
+      </c>
+      <c r="D102" t="str">
+        <v>in-app</v>
+      </c>
+      <c r="E102" t="str">
+        <v>Stand expedie le &lt;date&gt;, reception prevue le &lt;date&gt;</v>
+      </c>
+      <c r="F102" t="str">
+        <v>haute</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="str">
-        <v/>
+      <c r="A103">
+        <v>9</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Retour stand programme</v>
+      </c>
+      <c r="C103" t="str">
+        <v>collab retour</v>
+      </c>
+      <c r="D103" t="str">
+        <v>in-app</v>
+      </c>
+      <c r="E103" t="str">
+        <v>Date retour stand a BGN : &lt;date&gt;</v>
+      </c>
+      <c r="F103" t="str">
+        <v>normale</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>### 10. INTEGRATIONS EXTERNES ###</v>
+        <v/>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Outil</v>
+        <v># Note</v>
       </c>
       <c r="B105" t="str">
-        <v>Pour quoi ?</v>
-      </c>
-      <c r="C105" t="str">
-        <v>Sens</v>
-      </c>
-      <c r="D105" t="str">
-        <v>Statut</v>
-      </c>
-      <c r="E105" t="str">
-        <v>Priorite</v>
+        <v>Le commentaire de tache est deja gere par le trigger BE-010 (notif assigne+manager+demandeur). Inutile de le re-declarer.</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Lucca</v>
-      </c>
-      <c r="B106" t="str">
-        <v/>
-      </c>
-      <c r="C106" t="str">
-        <v/>
-      </c>
-      <c r="D106" t="str">
-        <v/>
-      </c>
-      <c r="E106" t="str">
         <v/>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Yooz</v>
-      </c>
-      <c r="B107" t="str">
-        <v/>
-      </c>
-      <c r="C107" t="str">
-        <v/>
-      </c>
-      <c r="D107" t="str">
-        <v/>
-      </c>
-      <c r="E107" t="str">
-        <v/>
+        <v>### 7. KPI DASHBOARD ###</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Pipedrive</v>
+        <v>#</v>
       </c>
       <c r="B108" t="str">
-        <v/>
+        <v>KPI (label)</v>
       </c>
       <c r="C108" t="str">
-        <v/>
+        <v>Formule</v>
       </c>
       <c r="D108" t="str">
-        <v/>
-      </c>
-      <c r="E108" t="str">
-        <v/>
+        <v>Couleur</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="str">
+      <c r="A109">
+        <v>1</v>
+      </c>
+      <c r="B109" t="str">
+        <v>Demandes actives</v>
+      </c>
+      <c r="C109" t="str">
+        <v>count(status NOT IN terminaux)</v>
+      </c>
+      <c r="D109" t="str">
+        <v>neutre</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110">
+        <v>2</v>
+      </c>
+      <c r="B110" t="str">
+        <v>En retard (date_rendu_fixee depassee)</v>
+      </c>
+      <c r="C110" t="str">
+        <v>count(date_rendu_fixee &lt; today AND active)</v>
+      </c>
+      <c r="D110" t="str">
+        <v>rouge</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111">
+        <v>3</v>
+      </c>
+      <c r="B111" t="str">
+        <v>Sans attribution</v>
+      </c>
+      <c r="C111" t="str">
+        <v>count(status=soumise AND attribution IS NULL)</v>
+      </c>
+      <c r="D111" t="str">
+        <v>ambre</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112">
+        <v>4</v>
+      </c>
+      <c r="B112" t="str">
+        <v>A valider (recette)</v>
+      </c>
+      <c r="C112" t="str">
+        <v>count(status=recette)</v>
+      </c>
+      <c r="D112" t="str">
+        <v>violet</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113">
+        <v>5</v>
+      </c>
+      <c r="B113" t="str">
+        <v>Salons a venir J+30</v>
+      </c>
+      <c r="C113" t="str">
+        <v>count(prestation=stand AND date_debut_salon BETWEEN today AND today+30)</v>
+      </c>
+      <c r="D113" t="str">
+        <v>bleu</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114">
+        <v>6</v>
+      </c>
+      <c r="B114" t="str">
+        <v>Demandes par filiale (mois)</v>
+      </c>
+      <c r="C114" t="str">
+        <v>group by filiale, count</v>
+      </c>
+      <c r="D114" t="str">
+        <v>vert</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v># Filtres souhaites</v>
+      </c>
+      <c r="B116" t="str">
+        <v>Active ?</v>
+      </c>
+      <c r="C116" t="str">
+        <v>Notes</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>Recherche libre</v>
+      </c>
+      <c r="B117" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="C117" t="str">
+        <v>titre / numero</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>Statut</v>
+      </c>
+      <c r="B118" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="C118" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>Demandeur</v>
+      </c>
+      <c r="B119" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="C119" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>Assigne</v>
+      </c>
+      <c r="B120" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="C120" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>En retard (toggle)</v>
+      </c>
+      <c r="B121" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="C121" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>Prestation</v>
+      </c>
+      <c r="B122" t="str">
+        <v/>
+      </c>
+      <c r="C122" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>Filtre metier 1</v>
+      </c>
+      <c r="B123" t="str">
+        <v/>
+      </c>
+      <c r="C123" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>### 8. PERMISSIONS ###</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>Action</v>
+      </c>
+      <c r="B126" t="str">
+        <v>Demandeur</v>
+      </c>
+      <c r="C126" t="str">
+        <v>Executant/Cible</v>
+      </c>
+      <c r="D126" t="str">
+        <v>Manager service</v>
+      </c>
+      <c r="E126" t="str">
+        <v>Validateur N1</v>
+      </c>
+      <c r="F126" t="str">
+        <v>Validateur N2</v>
+      </c>
+      <c r="G126" t="str">
+        <v>Admin</v>
+      </c>
+      <c r="H126" t="str">
+        <v>Autre</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>Creer demande</v>
+      </c>
+      <c r="B127" t="str">
+        <v>OUI (tous collaborateurs)</v>
+      </c>
+      <c r="C127" t="str">
+        <v/>
+      </c>
+      <c r="D127" t="str">
+        <v/>
+      </c>
+      <c r="E127" t="str">
+        <v/>
+      </c>
+      <c r="F127" t="str">
+        <v/>
+      </c>
+      <c r="G127" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="H127" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>Voir ses demandes</v>
+      </c>
+      <c r="B128" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="C128" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="D128" t="str">
+        <v>OUI (filiale)</v>
+      </c>
+      <c r="E128" t="str">
+        <v/>
+      </c>
+      <c r="F128" t="str">
+        <v/>
+      </c>
+      <c r="G128" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="H128" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>Voir TOUTES</v>
+      </c>
+      <c r="B129" t="str">
+        <v/>
+      </c>
+      <c r="C129" t="str">
+        <v/>
+      </c>
+      <c r="D129" t="str">
+        <v/>
+      </c>
+      <c r="E129" t="str">
+        <v/>
+      </c>
+      <c r="F129" t="str">
+        <v/>
+      </c>
+      <c r="G129" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="H129" t="str">
+        <v>Equipe Comm complete</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>Attribuer / fixer priorite / date rendu</v>
+      </c>
+      <c r="B130" t="str">
+        <v/>
+      </c>
+      <c r="C130" t="str">
+        <v/>
+      </c>
+      <c r="D130" t="str">
+        <v/>
+      </c>
+      <c r="E130" t="str">
+        <v/>
+      </c>
+      <c r="F130" t="str">
+        <v/>
+      </c>
+      <c r="G130" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="H130" t="str">
+        <v>Claire SASSIAS</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>Faire avancer le statut</v>
+      </c>
+      <c r="B131" t="str">
+        <v/>
+      </c>
+      <c r="C131" t="str">
+        <v>OUI (sa demande)</v>
+      </c>
+      <c r="D131" t="str">
+        <v/>
+      </c>
+      <c r="E131" t="str">
+        <v/>
+      </c>
+      <c r="F131" t="str">
+        <v/>
+      </c>
+      <c r="G131" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="H131" t="str">
+        <v>Equipe Comm</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>Valider la recette</v>
+      </c>
+      <c r="B132" t="str">
+        <v>sienne</v>
+      </c>
+      <c r="C132" t="str">
+        <v/>
+      </c>
+      <c r="D132" t="str">
+        <v/>
+      </c>
+      <c r="E132" t="str">
+        <v/>
+      </c>
+      <c r="F132" t="str">
+        <v/>
+      </c>
+      <c r="G132" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="H132" t="str">
+        <v>demandeur</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>Annuler</v>
+      </c>
+      <c r="B133" t="str">
+        <v>sienne (avant attribution)</v>
+      </c>
+      <c r="C133" t="str">
+        <v/>
+      </c>
+      <c r="D133" t="str">
+        <v/>
+      </c>
+      <c r="E133" t="str">
+        <v/>
+      </c>
+      <c r="F133" t="str">
+        <v/>
+      </c>
+      <c r="G133" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="H133" t="str">
+        <v>Claire SASSIAS</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>### 9. HUB PROJET / DOSSIER (si applicable) ###</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>Champ</v>
+      </c>
+      <c r="B136" t="str">
+        <v>Valeur</v>
+      </c>
+      <c r="C136" t="str">
+        <v>Aide</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>Hub active ?</v>
+      </c>
+      <c r="B137" t="str">
+        <v>NON</v>
+      </c>
+      <c r="C137" t="str">
+        <v>a confirmer - on pourrait grouper par filiale ou par salon</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>Concept</v>
+      </c>
+      <c r="B138" t="str">
+        <v/>
+      </c>
+      <c r="C138" t="str">
+        <v>option : Salon (regrouper toutes les demandes liees a un salon : stand + plaquettes + signaletique)</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>Nom entite</v>
+      </c>
+      <c r="B139" t="str">
+        <v/>
+      </c>
+      <c r="C139" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>Code/identifiant</v>
+      </c>
+      <c r="B140" t="str">
+        <v/>
+      </c>
+      <c r="C140" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>Onglets</v>
+      </c>
+      <c r="B141" t="str">
+        <v/>
+      </c>
+      <c r="C141" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>Visibilite</v>
+      </c>
+      <c r="B142" t="str">
+        <v/>
+      </c>
+      <c r="C142" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>### 10. INTEGRATIONS EXTERNES ###</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>Outil</v>
+      </c>
+      <c r="B145" t="str">
+        <v>Pour quoi ?</v>
+      </c>
+      <c r="C145" t="str">
+        <v>Sens</v>
+      </c>
+      <c r="D145" t="str">
+        <v>Statut</v>
+      </c>
+      <c r="E145" t="str">
+        <v>Priorite</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>SharePoint Lists</v>
+      </c>
+      <c r="B146" t="str">
+        <v>source actuelle des 2 formulaires (a remplacer)</v>
+      </c>
+      <c r="C146" t="str">
+        <v>lecture (one-shot import) puis arret</v>
+      </c>
+      <c r="D146" t="str">
+        <v>a faire</v>
+      </c>
+      <c r="E146" t="str">
+        <v>haute</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>Yooz</v>
+      </c>
+      <c r="B147" t="str">
+        <v>BdC fournisseur (impressions, goodies)</v>
+      </c>
+      <c r="C147" t="str">
+        <v>lecture</v>
+      </c>
+      <c r="D147" t="str">
+        <v>a faire</v>
+      </c>
+      <c r="E147" t="str">
+        <v>normal</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
         <v>Divalto</v>
       </c>
-      <c r="B109" t="str">
-        <v/>
-      </c>
-      <c r="C109" t="str">
-        <v/>
-      </c>
-      <c r="D109" t="str">
-        <v/>
-      </c>
-      <c r="E109" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="str">
-        <v>SharePoint</v>
-      </c>
-      <c r="B110" t="str">
-        <v/>
-      </c>
-      <c r="C110" t="str">
-        <v/>
-      </c>
-      <c r="D110" t="str">
-        <v/>
-      </c>
-      <c r="E110" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="str">
-        <v/>
-      </c>
-      <c r="B111" t="str">
-        <v/>
-      </c>
-      <c r="C111" t="str">
-        <v/>
-      </c>
-      <c r="D111" t="str">
-        <v/>
-      </c>
-      <c r="E111" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="str">
+      <c r="B148" t="str">
+        <v>creation BdC</v>
+      </c>
+      <c r="C148" t="str">
+        <v>ecriture</v>
+      </c>
+      <c r="D148" t="str">
+        <v>a faire</v>
+      </c>
+      <c r="E148" t="str">
+        <v>normal</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>Letsignit</v>
+      </c>
+      <c r="B149" t="str">
+        <v>signature mail (campagnes internes)</v>
+      </c>
+      <c r="C149" t="str">
+        <v>ecriture</v>
+      </c>
+      <c r="D149" t="str">
+        <v>a faire</v>
+      </c>
+      <c r="E149" t="str">
+        <v>nice-to-have</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
         <v>### 11. QUESTIONS OUVERTES ###</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" t="str">
+    <row r="152">
+      <c r="A152" t="str">
         <v>#</v>
       </c>
-      <c r="B114" t="str">
+      <c r="B152" t="str">
         <v>Question</v>
       </c>
-      <c r="C114" t="str">
+      <c r="C152" t="str">
         <v>Importance</v>
       </c>
-      <c r="D114" t="str">
+      <c r="D152" t="str">
         <v>Reponse</v>
       </c>
     </row>
-    <row r="115">
-      <c r="A115">
+    <row r="153">
+      <c r="A153">
         <v>1</v>
       </c>
-      <c r="B115" t="str">
-        <v/>
-      </c>
-      <c r="C115" t="str">
+      <c r="B153" t="str">
+        <v>Migration des donnees existantes : on importe les ~30 lignes du SharePoint actuel ?</v>
+      </c>
+      <c r="C153" t="str">
+        <v>bloquant</v>
+      </c>
+      <c r="D153" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154">
+        <v>2</v>
+      </c>
+      <c r="B154" t="str">
+        <v>ATTRIBUTION : auto sur charge d equipe ou Claire decide manuellement a chaque fois ?</v>
+      </c>
+      <c r="C154" t="str">
+        <v>bloquant</v>
+      </c>
+      <c r="D154" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155">
+        <v>3</v>
+      </c>
+      <c r="B155" t="str">
+        <v>Statut d approbation (champ existant) : qui approuve quoi ? c est en plus de la validation recette ?</v>
+      </c>
+      <c r="C155" t="str">
         <v>normal</v>
       </c>
-      <c r="D115" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116">
-        <v>2</v>
-      </c>
-      <c r="B116" t="str">
-        <v/>
-      </c>
-      <c r="C116" t="str">
+      <c r="D155" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156">
+        <v>4</v>
+      </c>
+      <c r="B156" t="str">
+        <v>Etat avancement finance (BDC-OK, "0", "Valide et livre") : on garde ce double suivi prod/finance ou on fusionne ?</v>
+      </c>
+      <c r="C156" t="str">
         <v>normal</v>
       </c>
-      <c r="D116" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117">
-        <v>3</v>
-      </c>
-      <c r="B117" t="str">
-        <v/>
-      </c>
-      <c r="C117" t="str">
+      <c r="D156" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157">
+        <v>5</v>
+      </c>
+      <c r="B157" t="str">
+        <v>Stand : workflow lie aux dates (envoi auto declenche selon date debut salon - X jours) ?</v>
+      </c>
+      <c r="C157" t="str">
         <v>normal</v>
       </c>
-      <c r="D117" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118">
-        <v>4</v>
-      </c>
-      <c r="B118" t="str">
-        <v/>
-      </c>
-      <c r="C118" t="str">
+      <c r="D157" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158">
+        <v>6</v>
+      </c>
+      <c r="B158" t="str">
+        <v>Goodies/plaquettes : on reverse le stock dans l app ou on garde un suivi externe ?</v>
+      </c>
+      <c r="C158" t="str">
         <v>normal</v>
       </c>
-      <c r="D118" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119">
-        <v>5</v>
-      </c>
-      <c r="B119" t="str">
-        <v/>
-      </c>
-      <c r="C119" t="str">
+      <c r="D158" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159">
+        <v>7</v>
+      </c>
+      <c r="B159" t="str">
+        <v>Hub par salon : pertinent ? un salon engendre souvent plusieurs demandes (stand + plaquette + roll-up + AO traiteur)</v>
+      </c>
+      <c r="C159" t="str">
         <v>normal</v>
       </c>
-      <c r="D119" t="str">
+      <c r="D159" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160">
+        <v>8</v>
+      </c>
+      <c r="B160" t="str">
+        <v>Permission par filiale : un collab de NASKEO doit-il voir uniquement les demandes NASKEO ?</v>
+      </c>
+      <c r="C160" t="str">
+        <v>normal</v>
+      </c>
+      <c r="D160" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I119"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I160"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/docs/CDC/CDC_MODULES.xlsx
+++ b/docs/CDC/CDC_MODULES.xlsx
@@ -405,9 +405,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A35"/>
-  <cols>
-    <col min="1" max="1" width="110.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -585,6 +582,7 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:A35"/>
   </ignoredErrors>
@@ -594,17 +592,6 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I121"/>
-  <cols>
-    <col min="1" max="1" width="28.83203125" customWidth="1"/>
-    <col min="2" max="2" width="32.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="22.83203125" customWidth="1"/>
-    <col min="5" max="5" width="22.83203125" customWidth="1"/>
-    <col min="6" max="6" width="22.83203125" customWidth="1"/>
-    <col min="7" max="7" width="18.83203125" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -723,7 +710,7 @@
         <v>Manager du service</v>
       </c>
       <c r="B9" t="str">
-        <v>?</v>
+        <v>valentin BERTRAND</v>
       </c>
       <c r="C9" t="str">
         <v>prenom NOM</v>
@@ -1259,22 +1246,19 @@
         <v>11</v>
       </c>
       <c r="B37" t="str">
-        <v>?</v>
+        <v>Nom de la BI concernée</v>
       </c>
       <c r="C37" t="str">
-        <v/>
+        <v>text</v>
       </c>
       <c r="D37" t="str">
-        <v/>
+        <v>NON</v>
       </c>
       <c r="E37" t="str">
-        <v>SUPPORT LUCCA</v>
+        <v>REPORTING POWER BI</v>
       </c>
       <c r="F37" t="str">
-        <v/>
-      </c>
-      <c r="G37" t="str">
-        <v>a definir</v>
+        <v>demandeur et cible</v>
       </c>
     </row>
     <row r="38">
@@ -1282,22 +1266,22 @@
         <v>12</v>
       </c>
       <c r="B38" t="str">
-        <v>?</v>
+        <v>Matériel</v>
       </c>
       <c r="C38" t="str">
-        <v/>
+        <v>select</v>
       </c>
       <c r="D38" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="E38" t="str">
-        <v>REPORTING POWER BI</v>
+        <v>MATERIEL</v>
       </c>
       <c r="F38" t="str">
-        <v/>
+        <v>demandeur</v>
       </c>
       <c r="G38" t="str">
-        <v>a definir</v>
+        <v>souris,clavier,casque, pc, telephone</v>
       </c>
     </row>
     <row r="39">
@@ -2452,7 +2436,7 @@
         <v>bloquant</v>
       </c>
       <c r="D116" t="str">
-        <v/>
+        <v>il faut tout garder les données concernant les budgets/carto, projets IT</v>
       </c>
     </row>
     <row r="117">
@@ -2466,7 +2450,7 @@
         <v>bloquant</v>
       </c>
       <c r="D117" t="str">
-        <v/>
+        <v>les 2</v>
       </c>
     </row>
     <row r="118">
@@ -2480,7 +2464,7 @@
         <v>bloquant</v>
       </c>
       <c r="D118" t="str">
-        <v/>
+        <v>completé</v>
       </c>
     </row>
     <row r="119">
@@ -2494,7 +2478,7 @@
         <v>normal</v>
       </c>
       <c r="D119" t="str">
-        <v/>
+        <v>indicatif plan de charge</v>
       </c>
     </row>
     <row r="120">
@@ -2508,7 +2492,7 @@
         <v>normal</v>
       </c>
       <c r="D120" t="str">
-        <v/>
+        <v>pas de Hub</v>
       </c>
     </row>
     <row r="121">
@@ -2522,10 +2506,11 @@
         <v>normal</v>
       </c>
       <c r="D121" t="str">
-        <v/>
+        <v>Valentin</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:I121"/>
   </ignoredErrors>
@@ -2535,17 +2520,6 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I197"/>
-  <cols>
-    <col min="1" max="1" width="28.83203125" customWidth="1"/>
-    <col min="2" max="2" width="32.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="22.83203125" customWidth="1"/>
-    <col min="5" max="5" width="22.83203125" customWidth="1"/>
-    <col min="6" max="6" width="22.83203125" customWidth="1"/>
-    <col min="7" max="7" width="18.83203125" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6239,7 +6213,7 @@
         <v>Code/identifiant</v>
       </c>
       <c r="B175" t="str">
-        <v>?</v>
+        <v>RH-2026-0001</v>
       </c>
       <c r="C175" t="str">
         <v>matricule SILAE ou RH-2026-0001 ?</v>
@@ -6431,7 +6405,7 @@
         <v>bloquant</v>
       </c>
       <c r="D190" t="str">
-        <v/>
+        <v>oui</v>
       </c>
     </row>
     <row r="191">
@@ -6445,7 +6419,7 @@
         <v>bloquant</v>
       </c>
       <c r="D191" t="str">
-        <v/>
+        <v>oui</v>
       </c>
     </row>
     <row r="192">
@@ -6459,7 +6433,7 @@
         <v>normal</v>
       </c>
       <c r="D192" t="str">
-        <v/>
+        <v>parrallèles</v>
       </c>
     </row>
     <row r="193">
@@ -6473,7 +6447,7 @@
         <v>normal</v>
       </c>
       <c r="D193" t="str">
-        <v/>
+        <v>1h</v>
       </c>
     </row>
     <row r="194">
@@ -6487,7 +6461,7 @@
         <v>normal</v>
       </c>
       <c r="D194" t="str">
-        <v/>
+        <v>notif</v>
       </c>
     </row>
     <row r="195">
@@ -6501,7 +6475,7 @@
         <v>bloquant</v>
       </c>
       <c r="D195" t="str">
-        <v/>
+        <v>RH</v>
       </c>
     </row>
     <row r="196">
@@ -6515,7 +6489,7 @@
         <v>bloquant</v>
       </c>
       <c r="D196" t="str">
-        <v/>
+        <v>validation Camille BOLO ou Partick Foltzenvogel</v>
       </c>
     </row>
     <row r="197">
@@ -6529,10 +6503,11 @@
         <v>normal</v>
       </c>
       <c r="D197" t="str">
-        <v/>
+        <v>non</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:I197"/>
   </ignoredErrors>
@@ -6541,18 +6516,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I119"/>
-  <cols>
-    <col min="1" max="1" width="28.83203125" customWidth="1"/>
-    <col min="2" max="2" width="32.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="22.83203125" customWidth="1"/>
-    <col min="5" max="5" width="22.83203125" customWidth="1"/>
-    <col min="6" max="6" width="22.83203125" customWidth="1"/>
-    <col min="7" max="7" width="18.83203125" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:I151"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6638,7 +6602,7 @@
         <v>Nom metier</v>
       </c>
       <c r="B6" t="str">
-        <v/>
+        <v>Innovation</v>
       </c>
       <c r="C6" t="str">
         <v>ex. Maintenance, RH, SMQ</v>
@@ -6649,7 +6613,7 @@
         <v>Code court (URL)</v>
       </c>
       <c r="B7" t="str">
-        <v/>
+        <v>inno</v>
       </c>
       <c r="C7" t="str">
         <v>ex. maint, rh, smq</v>
@@ -6660,7 +6624,7 @@
         <v>Service responsable</v>
       </c>
       <c r="B8" t="str">
-        <v/>
+        <v>Service Innovation</v>
       </c>
       <c r="C8" t="str">
         <v>equipe traitante</v>
@@ -6671,7 +6635,7 @@
         <v>Manager du service</v>
       </c>
       <c r="B9" t="str">
-        <v/>
+        <v>CRO</v>
       </c>
       <c r="C9" t="str">
         <v>prenom NOM</v>
@@ -6682,7 +6646,7 @@
         <v>Hub projet/dossier ?</v>
       </c>
       <c r="B10" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="C10" t="str">
         <v>OUI / NON</v>
@@ -6693,7 +6657,7 @@
         <v>Plusieurs sous-types ?</v>
       </c>
       <c r="B11" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="C11" t="str">
         <v>OUI / NON</v>
@@ -6704,7 +6668,7 @@
         <v>Demandeurs autorises</v>
       </c>
       <c r="B12" t="str">
-        <v/>
+        <v>tous les collaborateurs</v>
       </c>
       <c r="C12" t="str">
         <v>tous / managers / services X,Y</v>
@@ -6715,7 +6679,7 @@
         <v>Donnees sensibles ?</v>
       </c>
       <c r="B13" t="str">
-        <v/>
+        <v>NON</v>
       </c>
       <c r="C13" t="str">
         <v>OUI / NON</v>
@@ -6762,25 +6726,25 @@
         <v>1</v>
       </c>
       <c r="B17" t="str">
-        <v/>
+        <v>NOUVELLE DEMANDE INNOVATION</v>
       </c>
       <c r="C17" t="str">
-        <v/>
+        <v>Idee / projet a instruire</v>
       </c>
       <c r="D17" t="str">
-        <v/>
+        <v>Service Innovation</v>
       </c>
       <c r="E17" t="str">
-        <v/>
+        <v>CRO</v>
       </c>
       <c r="F17" t="str">
-        <v/>
+        <v>CODIR</v>
       </c>
       <c r="G17" t="str">
-        <v/>
+        <v>2 semaines</v>
       </c>
       <c r="H17" t="str">
-        <v/>
+        <v>date CODIR</v>
       </c>
     </row>
     <row r="18">
@@ -6788,25 +6752,25 @@
         <v>2</v>
       </c>
       <c r="B18" t="str">
-        <v/>
+        <v>MAJ AVANCEMENT PROJET</v>
       </c>
       <c r="C18" t="str">
-        <v/>
+        <v>Mise a jour etat / livrables projet</v>
       </c>
       <c r="D18" t="str">
-        <v/>
+        <v>Responsable projet</v>
       </c>
       <c r="E18" t="str">
-        <v/>
+        <v>CRO</v>
       </c>
       <c r="F18" t="str">
-        <v/>
+        <v>NON</v>
       </c>
       <c r="G18" t="str">
-        <v/>
+        <v>1j</v>
       </c>
       <c r="H18" t="str">
-        <v/>
+        <v>?</v>
       </c>
     </row>
     <row r="19">
@@ -7017,22 +6981,22 @@
         <v>5</v>
       </c>
       <c r="B29" t="str">
-        <v/>
+        <v>Prestation</v>
       </c>
       <c r="C29" t="str">
-        <v/>
+        <v>select</v>
       </c>
       <c r="D29" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="E29" t="str">
-        <v/>
+        <v>COMMUN</v>
       </c>
       <c r="F29" t="str">
-        <v/>
+        <v>demandeur</v>
       </c>
       <c r="G29" t="str">
-        <v/>
+        <v>2 valeurs</v>
       </c>
     </row>
     <row r="30">
@@ -7040,22 +7004,22 @@
         <v>6</v>
       </c>
       <c r="B30" t="str">
-        <v/>
+        <v>Nom projet</v>
       </c>
       <c r="C30" t="str">
-        <v/>
+        <v>text</v>
       </c>
       <c r="D30" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="E30" t="str">
-        <v/>
+        <v>NOUVELLE DEMANDE INNOVATION</v>
       </c>
       <c r="F30" t="str">
-        <v/>
+        <v>demandeur</v>
       </c>
       <c r="G30" t="str">
-        <v/>
+        <v>libre</v>
       </c>
     </row>
     <row r="31">
@@ -7063,22 +7027,22 @@
         <v>7</v>
       </c>
       <c r="B31" t="str">
-        <v/>
+        <v>Code projet</v>
       </c>
       <c r="C31" t="str">
-        <v/>
+        <v>text</v>
       </c>
       <c r="D31" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="E31" t="str">
-        <v/>
+        <v>COMMUN</v>
       </c>
       <c r="F31" t="str">
-        <v/>
+        <v>service Innovation</v>
       </c>
       <c r="G31" t="str">
-        <v/>
+        <v>genere apres CODIR (ex MONI, MIXI)</v>
       </c>
     </row>
     <row r="32">
@@ -7086,22 +7050,22 @@
         <v>8</v>
       </c>
       <c r="B32" t="str">
-        <v/>
+        <v>Filiale concernee</v>
       </c>
       <c r="C32" t="str">
-        <v/>
+        <v>select</v>
       </c>
       <c r="D32" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="E32" t="str">
-        <v/>
+        <v>NOUVELLE DEMANDE INNOVATION</v>
       </c>
       <c r="F32" t="str">
-        <v/>
+        <v>demandeur</v>
       </c>
       <c r="G32" t="str">
-        <v/>
+        <v>NASKEO/KEON.BIO/TEIKEI/SYCOMORE/KEON/CAPCOO/INTERFILIALE/GECO2/EXTERNE</v>
       </c>
     </row>
     <row r="33">
@@ -7109,22 +7073,22 @@
         <v>9</v>
       </c>
       <c r="B33" t="str">
-        <v/>
+        <v>Service Innovation</v>
       </c>
       <c r="C33" t="str">
-        <v/>
+        <v>select</v>
       </c>
       <c r="D33" t="str">
-        <v/>
+        <v>NON</v>
       </c>
       <c r="E33" t="str">
-        <v/>
+        <v>NOUVELLE DEMANDE INNOVATION</v>
       </c>
       <c r="F33" t="str">
-        <v/>
+        <v>service Innovation</v>
       </c>
       <c r="G33" t="str">
-        <v/>
+        <v>NEW B / autres</v>
       </c>
     </row>
     <row r="34">
@@ -7132,142 +7096,226 @@
         <v>10</v>
       </c>
       <c r="B34" t="str">
-        <v/>
+        <v>Service porteur</v>
       </c>
       <c r="C34" t="str">
-        <v/>
+        <v>select</v>
       </c>
       <c r="D34" t="str">
-        <v/>
+        <v>NON</v>
       </c>
       <c r="E34" t="str">
-        <v/>
+        <v>NOUVELLE DEMANDE INNOVATION</v>
       </c>
       <c r="F34" t="str">
-        <v/>
+        <v>service Innovation</v>
       </c>
       <c r="G34" t="str">
-        <v/>
+        <v>liste des services</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="str">
-        <v/>
+      <c r="A35">
+        <v>11</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Usage</v>
+      </c>
+      <c r="C35" t="str">
+        <v>select</v>
+      </c>
+      <c r="D35" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="E35" t="str">
+        <v>NOUVELLE DEMANDE INNOVATION</v>
+      </c>
+      <c r="F35" t="str">
+        <v>demandeur</v>
+      </c>
+      <c r="G35" t="str">
+        <v>Exploitation/Maintenance/Developpement/Construction/Etudes/Conception/Administratif/Commerce Methaniseur/BPA</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="str">
-        <v># Aide types</v>
+      <c r="A36">
+        <v>12</v>
       </c>
       <c r="B36" t="str">
-        <v>text / textarea / number / date / datetime / select / multi-select / bool / files / profile / company / department</v>
+        <v>Demandeur / porteur</v>
+      </c>
+      <c r="C36" t="str">
+        <v>profile</v>
+      </c>
+      <c r="D36" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="E36" t="str">
+        <v>COMMUN</v>
+      </c>
+      <c r="F36" t="str">
+        <v>demandeur</v>
+      </c>
+      <c r="G36" t="str">
+        <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="str">
-        <v># Communs OU prestation</v>
+      <c r="A37">
+        <v>13</v>
       </c>
       <c r="B37" t="str">
-        <v>COMMUN ou nom(s) prestation(s) separes par |</v>
+        <v>Responsable projet</v>
+      </c>
+      <c r="C37" t="str">
+        <v>profile</v>
+      </c>
+      <c r="D37" t="str">
+        <v>NON</v>
+      </c>
+      <c r="E37" t="str">
+        <v>COMMUN</v>
+      </c>
+      <c r="F37" t="str">
+        <v>service Innovation</v>
+      </c>
+      <c r="G37" t="str">
+        <v>rempli a l affectation</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="str">
-        <v/>
+      <c r="A38">
+        <v>14</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Sponsor</v>
+      </c>
+      <c r="C38" t="str">
+        <v>multi-select</v>
+      </c>
+      <c r="D38" t="str">
+        <v>NON</v>
+      </c>
+      <c r="E38" t="str">
+        <v>COMMUN</v>
+      </c>
+      <c r="F38" t="str">
+        <v>tous</v>
+      </c>
+      <c r="G38" t="str">
+        <v>fonctionne comme un like projet</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="str">
-        <v>### 4. WORKFLOW (etats et transitions) ###</v>
+      <c r="A39">
+        <v>15</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Etiquettes</v>
+      </c>
+      <c r="C39" t="str">
+        <v>multi-select</v>
+      </c>
+      <c r="D39" t="str">
+        <v>NON</v>
+      </c>
+      <c r="E39" t="str">
+        <v>COMMUN</v>
+      </c>
+      <c r="F39" t="str">
+        <v>demandeur</v>
+      </c>
+      <c r="G39" t="str">
+        <v>libre + suggestions existantes</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="str">
-        <v>#</v>
+      <c r="A40">
+        <v>16</v>
       </c>
       <c r="B40" t="str">
-        <v>Statut</v>
+        <v>Thematique abordee</v>
       </c>
       <c r="C40" t="str">
-        <v>Description</v>
+        <v>select</v>
       </c>
       <c r="D40" t="str">
-        <v>Qui agit ?</v>
+        <v>NON</v>
       </c>
       <c r="E40" t="str">
-        <v>Statuts suivants</v>
+        <v>NOUVELLE DEMANDE INNOVATION</v>
       </c>
       <c r="F40" t="str">
-        <v>Action UI (label bouton)</v>
+        <v>demandeur</v>
       </c>
       <c r="G40" t="str">
-        <v>Effet</v>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B41" t="str">
-        <v>soumise</v>
+        <v>Challenge Inno ?</v>
       </c>
       <c r="C41" t="str">
-        <v>Demande creee</v>
+        <v>select</v>
       </c>
       <c r="D41" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="E41" t="str">
-        <v/>
+        <v>NOUVELLE DEMANDE INNOVATION</v>
       </c>
       <c r="F41" t="str">
-        <v/>
+        <v>demandeur</v>
       </c>
       <c r="G41" t="str">
-        <v/>
+        <v>Oui / Non / A arbitrer</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="B42" t="str">
-        <v>affectee</v>
+        <v>Date debut</v>
       </c>
       <c r="C42" t="str">
-        <v>Affectee a executant</v>
+        <v>date</v>
       </c>
       <c r="D42" t="str">
-        <v/>
+        <v>NON</v>
       </c>
       <c r="E42" t="str">
-        <v/>
+        <v>COMMUN</v>
       </c>
       <c r="F42" t="str">
-        <v/>
+        <v>service Innovation</v>
       </c>
       <c r="G42" t="str">
-        <v/>
+        <v>apres arbitrage CODIR</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="B43" t="str">
-        <v>en_cours</v>
+        <v>Date fin previsionnelle</v>
       </c>
       <c r="C43" t="str">
-        <v>En cours</v>
+        <v>date</v>
       </c>
       <c r="D43" t="str">
-        <v/>
+        <v>NON</v>
       </c>
       <c r="E43" t="str">
-        <v/>
+        <v>COMMUN</v>
       </c>
       <c r="F43" t="str">
-        <v/>
+        <v>service Innovation</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -7275,243 +7323,207 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="B44" t="str">
-        <v>a_valider</v>
+        <v>% avancement estime</v>
       </c>
       <c r="C44" t="str">
-        <v>Attente validation</v>
+        <v>select</v>
       </c>
       <c r="D44" t="str">
-        <v/>
+        <v>NON</v>
       </c>
       <c r="E44" t="str">
-        <v/>
+        <v>MAJ AVANCEMENT PROJET</v>
       </c>
       <c r="F44" t="str">
-        <v/>
+        <v>responsable projet</v>
       </c>
       <c r="G44" t="str">
-        <v/>
+        <v>0-25 / 25-50 / 50-70 / 70-100</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="B45" t="str">
-        <v>complement_demande</v>
+        <v>Etat du projet</v>
       </c>
       <c r="C45" t="str">
-        <v>Manque info</v>
+        <v>select</v>
       </c>
       <c r="D45" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="E45" t="str">
-        <v/>
+        <v>COMMUN</v>
       </c>
       <c r="F45" t="str">
-        <v/>
+        <v>service Innovation</v>
       </c>
       <c r="G45" t="str">
-        <v/>
+        <v>A arbitrer/A debuter/En cours/A deployer/Termine/Ecarte/Standby/Non viable</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B46" t="str">
-        <v>realisee</v>
+        <v>Livrable intermediaire</v>
       </c>
       <c r="C46" t="str">
-        <v>Terminee</v>
+        <v>text</v>
       </c>
       <c r="D46" t="str">
-        <v>-</v>
+        <v>NON</v>
       </c>
       <c r="E46" t="str">
-        <v>-</v>
+        <v>COMMUN</v>
       </c>
       <c r="F46" t="str">
-        <v>-</v>
+        <v>responsable projet</v>
       </c>
       <c r="G46" t="str">
-        <v>terminal</v>
+        <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="B47" t="str">
-        <v>cloturee</v>
+        <v>Livrable final</v>
       </c>
       <c r="C47" t="str">
-        <v>Cloturee</v>
+        <v>text</v>
       </c>
       <c r="D47" t="str">
-        <v>-</v>
+        <v>NON</v>
       </c>
       <c r="E47" t="str">
-        <v>-</v>
+        <v>COMMUN</v>
       </c>
       <c r="F47" t="str">
-        <v>-</v>
+        <v>responsable projet</v>
       </c>
       <c r="G47" t="str">
-        <v>terminal</v>
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="B48" t="str">
-        <v>abandonnee</v>
+        <v>Difficulte / Complexite</v>
       </c>
       <c r="C48" t="str">
-        <v>Annulee</v>
+        <v>number</v>
       </c>
       <c r="D48" t="str">
-        <v>-</v>
+        <v>NON</v>
       </c>
       <c r="E48" t="str">
-        <v>-</v>
+        <v>COMMUN</v>
       </c>
       <c r="F48" t="str">
-        <v>-</v>
+        <v>service Innovation</v>
       </c>
       <c r="G48" t="str">
-        <v>terminal</v>
+        <v>echelle 1-10</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="str">
-        <v/>
+      <c r="A49">
+        <v>25</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Niveau strategique</v>
+      </c>
+      <c r="C49" t="str">
+        <v>number</v>
+      </c>
+      <c r="D49" t="str">
+        <v>NON</v>
+      </c>
+      <c r="E49" t="str">
+        <v>COMMUN</v>
+      </c>
+      <c r="F49" t="str">
+        <v>CODIR</v>
+      </c>
+      <c r="G49" t="str">
+        <v>echelle 1-10 (1 peu / 10 tres strategique)</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="str">
-        <v>### 5. SOUS-TACHES (uniquement si demande genere multi-taches) ###</v>
+      <c r="A50">
+        <v>26</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Priorisation / Urgence</v>
+      </c>
+      <c r="C50" t="str">
+        <v>select</v>
+      </c>
+      <c r="D50" t="str">
+        <v>NON</v>
+      </c>
+      <c r="E50" t="str">
+        <v>COMMUN</v>
+      </c>
+      <c r="F50" t="str">
+        <v>CODIR</v>
+      </c>
+      <c r="G50" t="str">
+        <v>prioritaire / non prioritaire</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="str">
-        <v>#</v>
+      <c r="A51">
+        <v>27</v>
       </c>
       <c r="B51" t="str">
-        <v>Prestation</v>
+        <v>Commentaire demande</v>
       </c>
       <c r="C51" t="str">
-        <v>Sous-tache</v>
+        <v>textarea</v>
       </c>
       <c r="D51" t="str">
-        <v>Service cible</v>
+        <v>NON</v>
       </c>
       <c r="E51" t="str">
-        <v>Affectation</v>
+        <v>NOUVELLE DEMANDE INNOVATION</v>
       </c>
       <c r="F51" t="str">
-        <v>Validateur N1</v>
+        <v>demandeur</v>
       </c>
       <c r="G51" t="str">
-        <v>Duree</v>
-      </c>
-      <c r="H51" t="str">
-        <v>Ordre</v>
-      </c>
-      <c r="I51" t="str">
-        <v>Parallele ?</v>
+        <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52">
-        <v>1</v>
-      </c>
-      <c r="B52" t="str">
-        <v/>
-      </c>
-      <c r="C52" t="str">
-        <v/>
-      </c>
-      <c r="D52" t="str">
-        <v/>
-      </c>
-      <c r="E52" t="str">
-        <v/>
-      </c>
-      <c r="F52" t="str">
-        <v/>
-      </c>
-      <c r="G52" t="str">
-        <v/>
-      </c>
-      <c r="H52">
-        <v>0</v>
-      </c>
-      <c r="I52" t="str">
-        <v>OUI</v>
+      <c r="A52" t="str">
+        <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53">
-        <v>2</v>
+      <c r="A53" t="str">
+        <v># Aide types</v>
       </c>
       <c r="B53" t="str">
-        <v/>
-      </c>
-      <c r="C53" t="str">
-        <v/>
-      </c>
-      <c r="D53" t="str">
-        <v/>
-      </c>
-      <c r="E53" t="str">
-        <v/>
-      </c>
-      <c r="F53" t="str">
-        <v/>
-      </c>
-      <c r="G53" t="str">
-        <v/>
-      </c>
-      <c r="H53">
-        <v>0</v>
-      </c>
-      <c r="I53" t="str">
-        <v>OUI</v>
+        <v>text / textarea / number / date / datetime / select / multi-select / bool / files / profile / company / department</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54">
-        <v>3</v>
+      <c r="A54" t="str">
+        <v># Communs OU prestation</v>
       </c>
       <c r="B54" t="str">
-        <v/>
-      </c>
-      <c r="C54" t="str">
-        <v/>
-      </c>
-      <c r="D54" t="str">
-        <v/>
-      </c>
-      <c r="E54" t="str">
-        <v/>
-      </c>
-      <c r="F54" t="str">
-        <v/>
-      </c>
-      <c r="G54" t="str">
-        <v/>
-      </c>
-      <c r="H54">
-        <v>0</v>
-      </c>
-      <c r="I54" t="str">
-        <v>OUI</v>
+        <v>COMMUN ou nom(s) prestation(s) separes par |</v>
       </c>
     </row>
     <row r="55">
@@ -7521,7 +7533,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>### 6. NOTIFICATIONS ###</v>
+        <v>### 4. WORKFLOW (etats et transitions) ###</v>
       </c>
     </row>
     <row r="57">
@@ -7529,19 +7541,22 @@
         <v>#</v>
       </c>
       <c r="B57" t="str">
-        <v>Evenement</v>
+        <v>Statut</v>
       </c>
       <c r="C57" t="str">
-        <v>Destinataire(s)</v>
+        <v>Description</v>
       </c>
       <c r="D57" t="str">
-        <v>Canal</v>
+        <v>Qui agit ?</v>
       </c>
       <c r="E57" t="str">
-        <v>Message</v>
+        <v>Statuts suivants</v>
       </c>
       <c r="F57" t="str">
-        <v>Priorite</v>
+        <v>Action UI (label bouton)</v>
+      </c>
+      <c r="G57" t="str">
+        <v>Effet</v>
       </c>
     </row>
     <row r="58">
@@ -7549,19 +7564,22 @@
         <v>1</v>
       </c>
       <c r="B58" t="str">
-        <v>Demande soumise</v>
+        <v>soumise</v>
       </c>
       <c r="C58" t="str">
-        <v/>
+        <v>Demande creee par demandeur</v>
       </c>
       <c r="D58" t="str">
-        <v>in-app</v>
+        <v>(auto)</v>
       </c>
       <c r="E58" t="str">
-        <v/>
+        <v>en_instruction</v>
       </c>
       <c r="F58" t="str">
-        <v>normale</v>
+        <v>-</v>
+      </c>
+      <c r="G58" t="str">
+        <v>auto-bascule</v>
       </c>
     </row>
     <row r="59">
@@ -7569,19 +7587,22 @@
         <v>2</v>
       </c>
       <c r="B59" t="str">
-        <v>Affectation</v>
+        <v>en_instruction</v>
       </c>
       <c r="C59" t="str">
-        <v/>
+        <v>Service Innovation collecte / qualifie</v>
       </c>
       <c r="D59" t="str">
-        <v>in-app</v>
+        <v>service Innovation</v>
       </c>
       <c r="E59" t="str">
-        <v/>
+        <v>preparation_codir / complement_demande / abandonnee</v>
       </c>
       <c r="F59" t="str">
-        <v>normale</v>
+        <v>Qualifier</v>
+      </c>
+      <c r="G59" t="str">
+        <v/>
       </c>
     </row>
     <row r="60">
@@ -7589,19 +7610,22 @@
         <v>3</v>
       </c>
       <c r="B60" t="str">
-        <v>Demande validation</v>
+        <v>complement_demande</v>
       </c>
       <c r="C60" t="str">
-        <v/>
+        <v>Manque info, retour demandeur</v>
       </c>
       <c r="D60" t="str">
-        <v>in-app</v>
+        <v>demandeur</v>
       </c>
       <c r="E60" t="str">
-        <v/>
+        <v>en_instruction</v>
       </c>
       <c r="F60" t="str">
-        <v>haute</v>
+        <v>J ai repondu</v>
+      </c>
+      <c r="G60" t="str">
+        <v/>
       </c>
     </row>
     <row r="61">
@@ -7609,19 +7633,22 @@
         <v>4</v>
       </c>
       <c r="B61" t="str">
-        <v>Complement demande</v>
+        <v>preparation_codir</v>
       </c>
       <c r="C61" t="str">
-        <v/>
+        <v>Dossier en cours de preparation pour CODIR</v>
       </c>
       <c r="D61" t="str">
-        <v>in-app</v>
+        <v>service Innovation</v>
       </c>
       <c r="E61" t="str">
-        <v/>
+        <v>arbitrage_codir</v>
       </c>
       <c r="F61" t="str">
-        <v>haute</v>
+        <v>Pret pour CODIR</v>
+      </c>
+      <c r="G61" t="str">
+        <v/>
       </c>
     </row>
     <row r="62">
@@ -7629,19 +7656,22 @@
         <v>5</v>
       </c>
       <c r="B62" t="str">
-        <v>Validee / Refusee</v>
+        <v>arbitrage_codir</v>
       </c>
       <c r="C62" t="str">
-        <v/>
+        <v>Presentation et arbitrage CODIR</v>
       </c>
       <c r="D62" t="str">
-        <v>in-app</v>
+        <v>CODIR</v>
       </c>
       <c r="E62" t="str">
-        <v/>
+        <v>mise_en_oeuvre / refusee_codir / standby</v>
       </c>
       <c r="F62" t="str">
-        <v>normale</v>
+        <v>Valider / Refuser</v>
+      </c>
+      <c r="G62" t="str">
+        <v/>
       </c>
     </row>
     <row r="63">
@@ -7649,19 +7679,22 @@
         <v>6</v>
       </c>
       <c r="B63" t="str">
-        <v>Cloturee</v>
+        <v>refusee_codir</v>
       </c>
       <c r="C63" t="str">
-        <v/>
+        <v>Refusee par CODIR</v>
       </c>
       <c r="D63" t="str">
-        <v>in-app</v>
+        <v>-</v>
       </c>
       <c r="E63" t="str">
-        <v/>
+        <v>-</v>
       </c>
       <c r="F63" t="str">
-        <v>normale</v>
+        <v>-</v>
+      </c>
+      <c r="G63" t="str">
+        <v>terminal</v>
       </c>
     </row>
     <row r="64">
@@ -7669,536 +7702,686 @@
         <v>7</v>
       </c>
       <c r="B64" t="str">
-        <v>SLA depasse</v>
+        <v>standby</v>
       </c>
       <c r="C64" t="str">
-        <v/>
+        <v>Mise en attente</v>
       </c>
       <c r="D64" t="str">
-        <v>in-app</v>
+        <v>CODIR</v>
       </c>
       <c r="E64" t="str">
-        <v/>
+        <v>arbitrage_codir / abandonnee</v>
       </c>
       <c r="F64" t="str">
-        <v>urgente</v>
+        <v>Reactiver</v>
+      </c>
+      <c r="G64" t="str">
+        <v/>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="str">
+      <c r="A65">
+        <v>8</v>
+      </c>
+      <c r="B65" t="str">
+        <v>mise_en_oeuvre</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Projet lance, suivi avancement</v>
+      </c>
+      <c r="D65" t="str">
+        <v>responsable projet</v>
+      </c>
+      <c r="E65" t="str">
+        <v>a_valider / abandonnee</v>
+      </c>
+      <c r="F65" t="str">
+        <v>-</v>
+      </c>
+      <c r="G65" t="str">
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="str">
-        <v># Note</v>
+      <c r="A66">
+        <v>9</v>
       </c>
       <c r="B66" t="str">
-        <v>Le commentaire de tache est deja gere par le trigger BE-010 (notif assigne+manager+demandeur). Inutile de le re-declarer.</v>
+        <v>a_valider</v>
+      </c>
+      <c r="C66" t="str">
+        <v>Projet realise, attente cloture</v>
+      </c>
+      <c r="D66" t="str">
+        <v>CRO</v>
+      </c>
+      <c r="E66" t="str">
+        <v>cloturee / mise_en_oeuvre</v>
+      </c>
+      <c r="F66" t="str">
+        <v>Cloturer</v>
+      </c>
+      <c r="G66" t="str">
+        <v/>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="str">
-        <v/>
+      <c r="A67">
+        <v>10</v>
+      </c>
+      <c r="B67" t="str">
+        <v>cloturee</v>
+      </c>
+      <c r="C67" t="str">
+        <v>Projet termine et cloture</v>
+      </c>
+      <c r="D67" t="str">
+        <v>-</v>
+      </c>
+      <c r="E67" t="str">
+        <v>-</v>
+      </c>
+      <c r="F67" t="str">
+        <v>-</v>
+      </c>
+      <c r="G67" t="str">
+        <v>terminal</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="str">
-        <v>### 7. KPI DASHBOARD ###</v>
+      <c r="A68">
+        <v>11</v>
+      </c>
+      <c r="B68" t="str">
+        <v>abandonnee</v>
+      </c>
+      <c r="C68" t="str">
+        <v>Annulee</v>
+      </c>
+      <c r="D68" t="str">
+        <v>demandeur ou CRO</v>
+      </c>
+      <c r="E68" t="str">
+        <v>-</v>
+      </c>
+      <c r="F68" t="str">
+        <v>-</v>
+      </c>
+      <c r="G68" t="str">
+        <v>terminal</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>### 5. SOUS-TACHES (uniquement si demande genere multi-taches) ###</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
         <v>#</v>
       </c>
-      <c r="B69" t="str">
-        <v>KPI (label)</v>
-      </c>
-      <c r="C69" t="str">
-        <v>Formule</v>
-      </c>
-      <c r="D69" t="str">
-        <v>Couleur</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70">
-        <v>1</v>
-      </c>
-      <c r="B70" t="str">
-        <v>Total actives</v>
-      </c>
-      <c r="C70" t="str">
-        <v>count(status NOT IN terminaux)</v>
-      </c>
-      <c r="D70" t="str">
-        <v>neutre</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71">
-        <v>2</v>
-      </c>
       <c r="B71" t="str">
-        <v>En retard</v>
+        <v>Prestation</v>
       </c>
       <c r="C71" t="str">
-        <v>count(due_date &lt; today AND active)</v>
+        <v>Sous-tache</v>
       </c>
       <c r="D71" t="str">
-        <v>rouge</v>
+        <v>Service cible</v>
+      </c>
+      <c r="E71" t="str">
+        <v>Affectation</v>
+      </c>
+      <c r="F71" t="str">
+        <v>Validateur N1</v>
+      </c>
+      <c r="G71" t="str">
+        <v>Duree</v>
+      </c>
+      <c r="H71" t="str">
+        <v>Ordre</v>
+      </c>
+      <c r="I71" t="str">
+        <v>Parallele ?</v>
       </c>
     </row>
     <row r="72">
       <c r="A72">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B72" t="str">
-        <v>A valider</v>
+        <v>NOUVELLE DEMANDE INNOVATION</v>
       </c>
       <c r="C72" t="str">
-        <v>count(status=a_valider)</v>
+        <v>Qualification idee</v>
       </c>
       <c r="D72" t="str">
-        <v>ambre</v>
+        <v>Innovation</v>
+      </c>
+      <c r="E72" t="str">
+        <v>service Innovation</v>
+      </c>
+      <c r="F72" t="str">
+        <v>CRO</v>
+      </c>
+      <c r="G72" t="str">
+        <v>2j</v>
+      </c>
+      <c r="H72">
+        <v>1</v>
+      </c>
+      <c r="I72" t="str">
+        <v>NON</v>
       </c>
     </row>
     <row r="73">
       <c r="A73">
+        <v>2</v>
+      </c>
+      <c r="B73" t="str">
+        <v>NOUVELLE DEMANDE INNOVATION</v>
+      </c>
+      <c r="C73" t="str">
+        <v>Evaluation faisabilite technique</v>
+      </c>
+      <c r="D73" t="str">
+        <v>Technique</v>
+      </c>
+      <c r="E73" t="str">
+        <v>service porteur</v>
+      </c>
+      <c r="F73" t="str">
+        <v>CRO</v>
+      </c>
+      <c r="G73" t="str">
+        <v>5j</v>
+      </c>
+      <c r="H73">
+        <v>2</v>
+      </c>
+      <c r="I73" t="str">
+        <v>OUI</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>3</v>
+      </c>
+      <c r="B74" t="str">
+        <v>NOUVELLE DEMANDE INNOVATION</v>
+      </c>
+      <c r="C74" t="str">
+        <v>Estimation budget / ROI</v>
+      </c>
+      <c r="D74" t="str">
+        <v>CDG</v>
+      </c>
+      <c r="E74" t="str">
+        <v>controle de gestion</v>
+      </c>
+      <c r="F74" t="str">
+        <v>CRO</v>
+      </c>
+      <c r="G74" t="str">
+        <v>5j</v>
+      </c>
+      <c r="H74">
+        <v>2</v>
+      </c>
+      <c r="I74" t="str">
+        <v>OUI</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
         <v>4</v>
       </c>
-      <c r="B73" t="str">
-        <v>Non assignees</v>
-      </c>
-      <c r="C73" t="str">
-        <v>count(assignee_id IS NULL AND active)</v>
-      </c>
-      <c r="D73" t="str">
-        <v>violet</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="str">
-        <v># Filtres souhaites</v>
-      </c>
       <c r="B75" t="str">
-        <v>Active ?</v>
+        <v>NOUVELLE DEMANDE INNOVATION</v>
       </c>
       <c r="C75" t="str">
-        <v>Notes</v>
+        <v>Preparation dossier CODIR</v>
+      </c>
+      <c r="D75" t="str">
+        <v>Innovation</v>
+      </c>
+      <c r="E75" t="str">
+        <v>service Innovation</v>
+      </c>
+      <c r="F75" t="str">
+        <v>CRO</v>
+      </c>
+      <c r="G75" t="str">
+        <v>3j</v>
+      </c>
+      <c r="H75">
+        <v>3</v>
+      </c>
+      <c r="I75" t="str">
+        <v>NON</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="str">
-        <v>Recherche libre</v>
+      <c r="A76">
+        <v>5</v>
       </c>
       <c r="B76" t="str">
-        <v>OUI</v>
+        <v>NOUVELLE DEMANDE INNOVATION</v>
       </c>
       <c r="C76" t="str">
-        <v>titre / numero</v>
+        <v>Presentation CODIR</v>
+      </c>
+      <c r="D76" t="str">
+        <v>CODIR</v>
+      </c>
+      <c r="E76" t="str">
+        <v>CRO</v>
+      </c>
+      <c r="F76" t="str">
+        <v>CODIR</v>
+      </c>
+      <c r="G76" t="str">
+        <v>1j</v>
+      </c>
+      <c r="H76">
+        <v>4</v>
+      </c>
+      <c r="I76" t="str">
+        <v>NON</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="str">
-        <v>Statut</v>
+      <c r="A77">
+        <v>6</v>
       </c>
       <c r="B77" t="str">
-        <v>OUI</v>
+        <v>NOUVELLE DEMANDE INNOVATION</v>
       </c>
       <c r="C77" t="str">
-        <v/>
+        <v>Lancement mise en oeuvre</v>
+      </c>
+      <c r="D77" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="E77" t="str">
+        <v>responsable projet</v>
+      </c>
+      <c r="F77" t="str">
+        <v>CRO</v>
+      </c>
+      <c r="G77" t="str">
+        <v>variable</v>
+      </c>
+      <c r="H77">
+        <v>5</v>
+      </c>
+      <c r="I77" t="str">
+        <v>NON</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Demandeur</v>
-      </c>
-      <c r="B78" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="C78" t="str">
         <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Assigne</v>
-      </c>
-      <c r="B79" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="C79" t="str">
-        <v/>
+        <v>### 6. NOTIFICATIONS ###</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>En retard (toggle)</v>
+        <v>#</v>
       </c>
       <c r="B80" t="str">
-        <v>OUI</v>
+        <v>Evenement</v>
       </c>
       <c r="C80" t="str">
-        <v/>
+        <v>Destinataire(s)</v>
+      </c>
+      <c r="D80" t="str">
+        <v>Canal</v>
+      </c>
+      <c r="E80" t="str">
+        <v>Message</v>
+      </c>
+      <c r="F80" t="str">
+        <v>Priorite</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="str">
-        <v>Prestation</v>
+      <c r="A81">
+        <v>1</v>
       </c>
       <c r="B81" t="str">
-        <v/>
+        <v>Demande soumise</v>
       </c>
       <c r="C81" t="str">
-        <v/>
+        <v>service Innovation + CRO</v>
+      </c>
+      <c r="D81" t="str">
+        <v>in-app</v>
+      </c>
+      <c r="E81" t="str">
+        <v>Nouvelle demande innovation : &lt;nom_projet&gt; de &lt;demandeur&gt;</v>
+      </c>
+      <c r="F81" t="str">
+        <v>normale</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="str">
-        <v>Filtre metier 1</v>
+      <c r="A82">
+        <v>2</v>
       </c>
       <c r="B82" t="str">
-        <v/>
+        <v>Affectation responsable</v>
       </c>
       <c r="C82" t="str">
-        <v/>
+        <v>responsable projet + demandeur</v>
+      </c>
+      <c r="D82" t="str">
+        <v>in-app</v>
+      </c>
+      <c r="E82" t="str">
+        <v>Vous etes responsable du projet &lt;nom_projet&gt;</v>
+      </c>
+      <c r="F82" t="str">
+        <v>normale</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="str">
-        <v/>
+      <c r="A83">
+        <v>3</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Complement demande</v>
+      </c>
+      <c r="C83" t="str">
+        <v>demandeur</v>
+      </c>
+      <c r="D83" t="str">
+        <v>in-app</v>
+      </c>
+      <c r="E83" t="str">
+        <v>Le service innovation demande des complements sur &lt;nom_projet&gt;</v>
+      </c>
+      <c r="F83" t="str">
+        <v>haute</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="str">
-        <v>### 8. PERMISSIONS ###</v>
+      <c r="A84">
+        <v>4</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Pret pour CODIR</v>
+      </c>
+      <c r="C84" t="str">
+        <v>CODIR</v>
+      </c>
+      <c r="D84" t="str">
+        <v>in-app + email</v>
+      </c>
+      <c r="E84" t="str">
+        <v>Dossier &lt;nom_projet&gt; a arbitrer au prochain CODIR</v>
+      </c>
+      <c r="F84" t="str">
+        <v>haute</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="str">
-        <v>Action</v>
+      <c r="A85">
+        <v>5</v>
       </c>
       <c r="B85" t="str">
-        <v>Demandeur</v>
+        <v>Decision CODIR</v>
       </c>
       <c r="C85" t="str">
-        <v>Executant/Cible</v>
+        <v>demandeur + sponsor + responsable</v>
       </c>
       <c r="D85" t="str">
-        <v>Manager service</v>
+        <v>in-app + email</v>
       </c>
       <c r="E85" t="str">
-        <v>Validateur N1</v>
+        <v>CODIR a statue sur &lt;nom_projet&gt; : &lt;decision&gt;</v>
       </c>
       <c r="F85" t="str">
-        <v>Validateur N2</v>
-      </c>
-      <c r="G85" t="str">
-        <v>Admin</v>
-      </c>
-      <c r="H85" t="str">
-        <v>Autre</v>
+        <v>haute</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="str">
-        <v>Creer demande</v>
+      <c r="A86">
+        <v>6</v>
       </c>
       <c r="B86" t="str">
-        <v>OUI</v>
+        <v>Mise en oeuvre lancee</v>
       </c>
       <c r="C86" t="str">
-        <v/>
+        <v>equipe projet + sponsor</v>
       </c>
       <c r="D86" t="str">
-        <v/>
+        <v>in-app</v>
       </c>
       <c r="E86" t="str">
-        <v/>
+        <v>Projet &lt;nom_projet&gt; en mise en oeuvre</v>
       </c>
       <c r="F86" t="str">
-        <v/>
-      </c>
-      <c r="G86" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="H86" t="str">
-        <v/>
+        <v>normale</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="str">
-        <v>Voir ses demandes</v>
+      <c r="A87">
+        <v>7</v>
       </c>
       <c r="B87" t="str">
-        <v>OUI</v>
+        <v>MAJ avancement</v>
       </c>
       <c r="C87" t="str">
-        <v>OUI</v>
+        <v>sponsor + CRO</v>
       </c>
       <c r="D87" t="str">
-        <v/>
+        <v>in-app</v>
       </c>
       <c r="E87" t="str">
-        <v/>
+        <v>&lt;responsable&gt; a mis a jour &lt;nom_projet&gt; : &lt;%avancement&gt;</v>
       </c>
       <c r="F87" t="str">
-        <v/>
-      </c>
-      <c r="G87" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="H87" t="str">
-        <v/>
+        <v>normale</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="str">
-        <v>Voir TOUTES</v>
+      <c r="A88">
+        <v>8</v>
       </c>
       <c r="B88" t="str">
-        <v/>
+        <v>Cloture projet</v>
       </c>
       <c r="C88" t="str">
-        <v/>
+        <v>demandeur + sponsor + CODIR</v>
       </c>
       <c r="D88" t="str">
-        <v/>
+        <v>in-app</v>
       </c>
       <c r="E88" t="str">
-        <v/>
+        <v>Projet &lt;nom_projet&gt; cloture</v>
       </c>
       <c r="F88" t="str">
-        <v/>
-      </c>
-      <c r="G88" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="H88" t="str">
-        <v/>
+        <v>normale</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="str">
-        <v>Affecter</v>
+      <c r="A89">
+        <v>9</v>
       </c>
       <c r="B89" t="str">
-        <v/>
+        <v>Sponsor (like)</v>
       </c>
       <c r="C89" t="str">
-        <v/>
+        <v>demandeur + responsable</v>
       </c>
       <c r="D89" t="str">
-        <v/>
+        <v>in-app</v>
       </c>
       <c r="E89" t="str">
-        <v/>
+        <v>&lt;sponsor&gt; soutient le projet &lt;nom_projet&gt;</v>
       </c>
       <c r="F89" t="str">
-        <v/>
-      </c>
-      <c r="G89" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="H89" t="str">
-        <v/>
+        <v>normale</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Reaffecter</v>
-      </c>
-      <c r="B90" t="str">
-        <v/>
-      </c>
-      <c r="C90" t="str">
-        <v/>
-      </c>
-      <c r="D90" t="str">
-        <v/>
-      </c>
-      <c r="E90" t="str">
-        <v/>
-      </c>
-      <c r="F90" t="str">
-        <v/>
-      </c>
-      <c r="G90" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="H90" t="str">
         <v/>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Annuler</v>
+        <v># Note</v>
       </c>
       <c r="B91" t="str">
-        <v>sienne</v>
-      </c>
-      <c r="C91" t="str">
-        <v/>
-      </c>
-      <c r="D91" t="str">
-        <v/>
-      </c>
-      <c r="E91" t="str">
-        <v/>
-      </c>
-      <c r="F91" t="str">
-        <v/>
-      </c>
-      <c r="G91" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="H91" t="str">
-        <v/>
+        <v>Le commentaire de tache est deja gere par le trigger BE-010 (notif assigne+manager+demandeur). Inutile de le re-declarer.</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Valider N1</v>
-      </c>
-      <c r="B92" t="str">
-        <v/>
-      </c>
-      <c r="C92" t="str">
-        <v/>
-      </c>
-      <c r="D92" t="str">
-        <v/>
-      </c>
-      <c r="E92" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="F92" t="str">
-        <v/>
-      </c>
-      <c r="G92" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="H92" t="str">
         <v/>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Valider N2</v>
-      </c>
-      <c r="B93" t="str">
-        <v/>
-      </c>
-      <c r="C93" t="str">
-        <v/>
-      </c>
-      <c r="D93" t="str">
-        <v/>
-      </c>
-      <c r="E93" t="str">
-        <v/>
-      </c>
-      <c r="F93" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="G93" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="H93" t="str">
-        <v/>
+        <v>### 7. KPI DASHBOARD ###</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v/>
+        <v>#</v>
+      </c>
+      <c r="B94" t="str">
+        <v>KPI (label)</v>
+      </c>
+      <c r="C94" t="str">
+        <v>Formule</v>
+      </c>
+      <c r="D94" t="str">
+        <v>Couleur</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="str">
-        <v>### 9. HUB PROJET / DOSSIER (si applicable) ###</v>
+      <c r="A95">
+        <v>1</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Demandes en instruction</v>
+      </c>
+      <c r="C95" t="str">
+        <v>count(status=en_instruction)</v>
+      </c>
+      <c r="D95" t="str">
+        <v>ambre</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="str">
-        <v>Champ</v>
+      <c r="A96">
+        <v>2</v>
       </c>
       <c r="B96" t="str">
-        <v>Valeur</v>
+        <v>A presenter au prochain CODIR</v>
       </c>
       <c r="C96" t="str">
-        <v>Aide</v>
+        <v>count(status=preparation_codir)</v>
+      </c>
+      <c r="D96" t="str">
+        <v>bleu</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="str">
-        <v>Hub active ?</v>
+      <c r="A97">
+        <v>3</v>
       </c>
       <c r="B97" t="str">
-        <v/>
+        <v>En arbitrage CODIR</v>
       </c>
       <c r="C97" t="str">
-        <v>OUI / NON</v>
+        <v>count(status=arbitrage_codir)</v>
+      </c>
+      <c r="D97" t="str">
+        <v>violet</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="str">
-        <v>Concept</v>
+      <c r="A98">
+        <v>4</v>
       </c>
       <c r="B98" t="str">
-        <v/>
+        <v>Projets en mise en oeuvre</v>
       </c>
       <c r="C98" t="str">
-        <v>ex. dossier client, projet R&amp;D, audit</v>
+        <v>count(status=mise_en_oeuvre)</v>
+      </c>
+      <c r="D98" t="str">
+        <v>vert</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="str">
-        <v>Nom entite</v>
+      <c r="A99">
+        <v>5</v>
       </c>
       <c r="B99" t="str">
-        <v/>
+        <v>Cloturees ce mois</v>
       </c>
       <c r="C99" t="str">
-        <v/>
+        <v>count(status=cloturee AND month=current)</v>
+      </c>
+      <c r="D99" t="str">
+        <v>vert</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="str">
-        <v>Code/identifiant</v>
+      <c r="A100">
+        <v>6</v>
       </c>
       <c r="B100" t="str">
-        <v/>
+        <v>Refusees / abandonnees</v>
       </c>
       <c r="C100" t="str">
-        <v>format</v>
+        <v>count(status IN (refusee_codir, abandonnee))</v>
+      </c>
+      <c r="D100" t="str">
+        <v>gris</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="str">
-        <v>Onglets souhaites</v>
+      <c r="A101">
+        <v>7</v>
       </c>
       <c r="B101" t="str">
-        <v/>
+        <v>Taux conversion idee-&gt;projet</v>
       </c>
       <c r="C101" t="str">
-        <v>Fiche / Taches / Timeline / Discussions / Fichiers</v>
+        <v>count(cloturee+mise_en_oeuvre) / count(total) * 100</v>
+      </c>
+      <c r="D101" t="str">
+        <v>neutre</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="str">
-        <v>Visibilite</v>
+      <c r="A102">
+        <v>8</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>Delai moyen instruction (j)</v>
       </c>
       <c r="C102" t="str">
-        <v>qui peut lire / ecrire</v>
+        <v>avg(date_arbitrage_codir - date_soumission)</v>
+      </c>
+      <c r="D102" t="str">
+        <v>neutre</v>
       </c>
     </row>
     <row r="103">
@@ -8208,126 +8391,90 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>### 10. INTEGRATIONS EXTERNES ###</v>
+        <v># Filtres souhaites</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Active ?</v>
+      </c>
+      <c r="C104" t="str">
+        <v>Notes</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Outil</v>
+        <v>Recherche libre</v>
       </c>
       <c r="B105" t="str">
-        <v>Pour quoi ?</v>
+        <v>OUI</v>
       </c>
       <c r="C105" t="str">
-        <v>Sens</v>
-      </c>
-      <c r="D105" t="str">
-        <v>Statut</v>
-      </c>
-      <c r="E105" t="str">
-        <v>Priorite</v>
+        <v>titre / numero</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Lucca</v>
+        <v>Statut</v>
       </c>
       <c r="B106" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="C106" t="str">
-        <v/>
-      </c>
-      <c r="D106" t="str">
-        <v/>
-      </c>
-      <c r="E106" t="str">
         <v/>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Yooz</v>
+        <v>Demandeur</v>
       </c>
       <c r="B107" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="C107" t="str">
-        <v/>
-      </c>
-      <c r="D107" t="str">
-        <v/>
-      </c>
-      <c r="E107" t="str">
         <v/>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Pipedrive</v>
+        <v>Assigne</v>
       </c>
       <c r="B108" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="C108" t="str">
-        <v/>
-      </c>
-      <c r="D108" t="str">
-        <v/>
-      </c>
-      <c r="E108" t="str">
         <v/>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Divalto</v>
+        <v>En retard (toggle)</v>
       </c>
       <c r="B109" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="C109" t="str">
-        <v/>
-      </c>
-      <c r="D109" t="str">
-        <v/>
-      </c>
-      <c r="E109" t="str">
         <v/>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>SharePoint</v>
+        <v>Prestation</v>
       </c>
       <c r="B110" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="C110" t="str">
-        <v/>
-      </c>
-      <c r="D110" t="str">
-        <v/>
-      </c>
-      <c r="E110" t="str">
         <v/>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v/>
+        <v>Filtre metier 1</v>
       </c>
       <c r="B111" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="C111" t="str">
-        <v/>
-      </c>
-      <c r="D111" t="str">
-        <v/>
-      </c>
-      <c r="E111" t="str">
-        <v/>
+        <v>Filiale / Service / Etat / Sponsor / Niveau strategique</v>
       </c>
     </row>
     <row r="112">
@@ -8337,96 +8484,599 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>### 11. QUESTIONS OUVERTES ###</v>
+        <v>### 8. PERMISSIONS ###</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
+        <v>Action</v>
+      </c>
+      <c r="B114" t="str">
+        <v>Demandeur</v>
+      </c>
+      <c r="C114" t="str">
+        <v>Executant/Cible</v>
+      </c>
+      <c r="D114" t="str">
+        <v>Manager service</v>
+      </c>
+      <c r="E114" t="str">
+        <v>Validateur N1</v>
+      </c>
+      <c r="F114" t="str">
+        <v>Validateur N2</v>
+      </c>
+      <c r="G114" t="str">
+        <v>Admin</v>
+      </c>
+      <c r="H114" t="str">
+        <v>Autre</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>Creer demande</v>
+      </c>
+      <c r="B115" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="C115" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="D115" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="E115" t="str">
+        <v/>
+      </c>
+      <c r="F115" t="str">
+        <v/>
+      </c>
+      <c r="G115" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="H115" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>Voir ses demandes</v>
+      </c>
+      <c r="B116" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="C116" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="D116" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="E116" t="str">
+        <v/>
+      </c>
+      <c r="F116" t="str">
+        <v/>
+      </c>
+      <c r="G116" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="H116" t="str">
+        <v>sponsor : ses likes</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>Voir TOUTES</v>
+      </c>
+      <c r="B117" t="str">
+        <v/>
+      </c>
+      <c r="C117" t="str">
+        <v/>
+      </c>
+      <c r="D117" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="E117" t="str">
+        <v/>
+      </c>
+      <c r="F117" t="str">
+        <v/>
+      </c>
+      <c r="G117" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="H117" t="str">
+        <v>CODIR : OUI</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>Affecter</v>
+      </c>
+      <c r="B118" t="str">
+        <v/>
+      </c>
+      <c r="C118" t="str">
+        <v/>
+      </c>
+      <c r="D118" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="E118" t="str">
+        <v/>
+      </c>
+      <c r="F118" t="str">
+        <v/>
+      </c>
+      <c r="G118" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="H118" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>Reaffecter</v>
+      </c>
+      <c r="B119" t="str">
+        <v/>
+      </c>
+      <c r="C119" t="str">
+        <v/>
+      </c>
+      <c r="D119" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="E119" t="str">
+        <v/>
+      </c>
+      <c r="F119" t="str">
+        <v/>
+      </c>
+      <c r="G119" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="H119" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>Annuler</v>
+      </c>
+      <c r="B120" t="str">
+        <v>sienne avant CODIR</v>
+      </c>
+      <c r="C120" t="str">
+        <v/>
+      </c>
+      <c r="D120" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="E120" t="str">
+        <v/>
+      </c>
+      <c r="F120" t="str">
+        <v/>
+      </c>
+      <c r="G120" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="H120" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>Valider N1</v>
+      </c>
+      <c r="B121" t="str">
+        <v/>
+      </c>
+      <c r="C121" t="str">
+        <v/>
+      </c>
+      <c r="D121" t="str">
+        <v/>
+      </c>
+      <c r="E121" t="str">
+        <v>CRO</v>
+      </c>
+      <c r="F121" t="str">
+        <v/>
+      </c>
+      <c r="G121" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="H121" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>Valider N2</v>
+      </c>
+      <c r="B122" t="str">
+        <v/>
+      </c>
+      <c r="C122" t="str">
+        <v/>
+      </c>
+      <c r="D122" t="str">
+        <v/>
+      </c>
+      <c r="E122" t="str">
+        <v/>
+      </c>
+      <c r="F122" t="str">
+        <v>CODIR</v>
+      </c>
+      <c r="G122" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="H122" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>### 9. HUB PROJET / DOSSIER (si applicable) ###</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>Champ</v>
+      </c>
+      <c r="B125" t="str">
+        <v>Valeur</v>
+      </c>
+      <c r="C125" t="str">
+        <v>Aide</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>Hub active ?</v>
+      </c>
+      <c r="B126" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="C126" t="str">
+        <v>OUI / NON</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>Concept</v>
+      </c>
+      <c r="B127" t="str">
+        <v>Dossier projet innovation</v>
+      </c>
+      <c r="C127" t="str">
+        <v>regroupe instruction + CODIR + mise en oeuvre + suivi</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>Nom entite</v>
+      </c>
+      <c r="B128" t="str">
+        <v>Projet</v>
+      </c>
+      <c r="C128" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>Code/identifiant</v>
+      </c>
+      <c r="B129" t="str">
+        <v>Code projet (ex: MONI, MIXI) ou INNO-2026-0001</v>
+      </c>
+      <c r="C129" t="str">
+        <v>code court 4 lettres prefere, sinon auto</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>Onglets souhaites</v>
+      </c>
+      <c r="B130" t="str">
+        <v>Fiche / Avancement / Taches / Discussions / Fichiers / CODIR</v>
+      </c>
+      <c r="C130" t="str">
+        <v>Fiche / Taches / Timeline / Discussions / Fichiers</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>Visibilite</v>
+      </c>
+      <c r="B131" t="str">
+        <v>tous (lecture) / responsable + service Inno + CODIR (ecriture)</v>
+      </c>
+      <c r="C131" t="str">
+        <v>visibilite large = effet "like / sponsor"</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>### 10. INTEGRATIONS EXTERNES ###</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>Outil</v>
+      </c>
+      <c r="B134" t="str">
+        <v>Pour quoi ?</v>
+      </c>
+      <c r="C134" t="str">
+        <v>Sens</v>
+      </c>
+      <c r="D134" t="str">
+        <v>Statut</v>
+      </c>
+      <c r="E134" t="str">
+        <v>Priorite</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>Lucca</v>
+      </c>
+      <c r="B135" t="str">
+        <v>annuaire collaborateurs (porteur, sponsor, responsable)</v>
+      </c>
+      <c r="C135" t="str">
+        <v>lecture</v>
+      </c>
+      <c r="D135" t="str">
+        <v>a faire</v>
+      </c>
+      <c r="E135" t="str">
+        <v>haute</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>Yooz</v>
+      </c>
+      <c r="B136" t="str">
+        <v>rapprochement budget projet</v>
+      </c>
+      <c r="C136" t="str">
+        <v>lecture</v>
+      </c>
+      <c r="D136" t="str">
+        <v>a faire</v>
+      </c>
+      <c r="E136" t="str">
+        <v>normal</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>Pipedrive</v>
+      </c>
+      <c r="B137" t="str">
+        <v>lien projets commerciaux</v>
+      </c>
+      <c r="C137" t="str">
+        <v>lecture</v>
+      </c>
+      <c r="D137" t="str">
+        <v>a faire</v>
+      </c>
+      <c r="E137" t="str">
+        <v>normal</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>Divalto</v>
+      </c>
+      <c r="B138" t="str">
+        <v>rapprochement code projet ERP</v>
+      </c>
+      <c r="C138" t="str">
+        <v>ecriture/lecture</v>
+      </c>
+      <c r="D138" t="str">
+        <v>a faire</v>
+      </c>
+      <c r="E138" t="str">
+        <v>normal</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>SharePoint</v>
+      </c>
+      <c r="B139" t="str">
+        <v>stockage livrables (note de cadrage, presentations CODIR)</v>
+      </c>
+      <c r="C139" t="str">
+        <v>ecriture</v>
+      </c>
+      <c r="D139" t="str">
+        <v>a faire</v>
+      </c>
+      <c r="E139" t="str">
+        <v>haute</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>Power BI</v>
+      </c>
+      <c r="B140" t="str">
+        <v>reporting consolidé portefeuille innovation</v>
+      </c>
+      <c r="C140" t="str">
+        <v>lecture</v>
+      </c>
+      <c r="D140" t="str">
+        <v>a faire</v>
+      </c>
+      <c r="E140" t="str">
+        <v>normal</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>### 11. QUESTIONS OUVERTES ###</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
         <v>#</v>
       </c>
-      <c r="B114" t="str">
+      <c r="B143" t="str">
         <v>Question</v>
       </c>
-      <c r="C114" t="str">
+      <c r="C143" t="str">
         <v>Importance</v>
       </c>
-      <c r="D114" t="str">
+      <c r="D143" t="str">
         <v>Reponse</v>
       </c>
     </row>
-    <row r="115">
-      <c r="A115">
+    <row r="144">
+      <c r="A144">
         <v>1</v>
       </c>
-      <c r="B115" t="str">
-        <v/>
-      </c>
-      <c r="C115" t="str">
+      <c r="B144" t="str">
+        <v>Generation auto du code projet (ex: MONI) ou saisi manuellement ?</v>
+      </c>
+      <c r="C144" t="str">
+        <v>bloquant</v>
+      </c>
+      <c r="D144" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145">
+        <v>2</v>
+      </c>
+      <c r="B145" t="str">
+        <v>Qui est le CRO (manager du module) ? Quels backups en cas d absence ?</v>
+      </c>
+      <c r="C145" t="str">
+        <v>bloquant</v>
+      </c>
+      <c r="D145" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146">
+        <v>3</v>
+      </c>
+      <c r="B146" t="str">
+        <v>Composition exacte du CODIR (validateurs N2) ?</v>
+      </c>
+      <c r="C146" t="str">
+        <v>bloquant</v>
+      </c>
+      <c r="D146" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147">
+        <v>4</v>
+      </c>
+      <c r="B147" t="str">
+        <v>Sponsor = simple like (compteur) ou role formel avec acces ecriture sur le dossier ?</v>
+      </c>
+      <c r="C147" t="str">
         <v>normal</v>
       </c>
-      <c r="D115" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116">
-        <v>2</v>
-      </c>
-      <c r="B116" t="str">
-        <v/>
-      </c>
-      <c r="C116" t="str">
+      <c r="D147" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148">
+        <v>5</v>
+      </c>
+      <c r="B148" t="str">
+        <v>Frequence CODIR (mensuel/bimensuel) -&gt; impact sur calcul des SLA "preparation_codir" ?</v>
+      </c>
+      <c r="C148" t="str">
         <v>normal</v>
       </c>
-      <c r="D116" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117">
-        <v>3</v>
-      </c>
-      <c r="B117" t="str">
-        <v/>
-      </c>
-      <c r="C117" t="str">
+      <c r="D148" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149">
+        <v>6</v>
+      </c>
+      <c r="B149" t="str">
+        <v>Reset des donnees inno_demandes existantes (Lovable) au demarrage de l app ?</v>
+      </c>
+      <c r="C149" t="str">
         <v>normal</v>
       </c>
-      <c r="D117" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118">
-        <v>4</v>
-      </c>
-      <c r="B118" t="str">
-        <v/>
-      </c>
-      <c r="C118" t="str">
+      <c r="D149" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150">
+        <v>7</v>
+      </c>
+      <c r="B150" t="str">
+        <v>Avancement % : saisie libre ou liaison automatique avec sous-taches realisees ?</v>
+      </c>
+      <c r="C150" t="str">
         <v>normal</v>
       </c>
-      <c r="D118" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119">
-        <v>5</v>
-      </c>
-      <c r="B119" t="str">
-        <v/>
-      </c>
-      <c r="C119" t="str">
+      <c r="D150" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151">
+        <v>8</v>
+      </c>
+      <c r="B151" t="str">
+        <v>Niveau strategique / Priorisation : remplis par CODIR seul ou aussi par service Innovation ?</v>
+      </c>
+      <c r="C151" t="str">
         <v>normal</v>
       </c>
-      <c r="D119" t="str">
+      <c r="D151" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I119"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I151"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -8434,17 +9084,6 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I117"/>
-  <cols>
-    <col min="1" max="1" width="28.83203125" customWidth="1"/>
-    <col min="2" max="2" width="32.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="22.83203125" customWidth="1"/>
-    <col min="5" max="5" width="22.83203125" customWidth="1"/>
-    <col min="6" max="6" width="22.83203125" customWidth="1"/>
-    <col min="7" max="7" width="18.83203125" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -10282,18 +10921,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I119"/>
-  <cols>
-    <col min="1" max="1" width="28.83203125" customWidth="1"/>
-    <col min="2" max="2" width="32.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="22.83203125" customWidth="1"/>
-    <col min="5" max="5" width="22.83203125" customWidth="1"/>
-    <col min="6" max="6" width="22.83203125" customWidth="1"/>
-    <col min="7" max="7" width="18.83203125" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:I147"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -10379,7 +11007,7 @@
         <v>Nom metier</v>
       </c>
       <c r="B6" t="str">
-        <v/>
+        <v>Logistique</v>
       </c>
       <c r="C6" t="str">
         <v>ex. Maintenance, RH, SMQ</v>
@@ -10390,7 +11018,7 @@
         <v>Code court (URL)</v>
       </c>
       <c r="B7" t="str">
-        <v/>
+        <v>log</v>
       </c>
       <c r="C7" t="str">
         <v>ex. maint, rh, smq</v>
@@ -10401,7 +11029,7 @@
         <v>Service responsable</v>
       </c>
       <c r="B8" t="str">
-        <v/>
+        <v>Service Logistique</v>
       </c>
       <c r="C8" t="str">
         <v>equipe traitante</v>
@@ -10412,7 +11040,7 @@
         <v>Manager du service</v>
       </c>
       <c r="B9" t="str">
-        <v/>
+        <v>Nicolas NAROLLE</v>
       </c>
       <c r="C9" t="str">
         <v>prenom NOM</v>
@@ -10423,7 +11051,7 @@
         <v>Hub projet/dossier ?</v>
       </c>
       <c r="B10" t="str">
-        <v/>
+        <v>NON</v>
       </c>
       <c r="C10" t="str">
         <v>OUI / NON</v>
@@ -10434,7 +11062,7 @@
         <v>Plusieurs sous-types ?</v>
       </c>
       <c r="B11" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="C11" t="str">
         <v>OUI / NON</v>
@@ -10445,7 +11073,7 @@
         <v>Demandeurs autorises</v>
       </c>
       <c r="B12" t="str">
-        <v/>
+        <v>tous les collaborateurs</v>
       </c>
       <c r="C12" t="str">
         <v>tous / managers / services X,Y</v>
@@ -10456,7 +11084,7 @@
         <v>Donnees sensibles ?</v>
       </c>
       <c r="B13" t="str">
-        <v/>
+        <v>NON</v>
       </c>
       <c r="C13" t="str">
         <v>OUI / NON</v>
@@ -10503,25 +11131,25 @@
         <v>1</v>
       </c>
       <c r="B17" t="str">
-        <v/>
+        <v>DEMANDE DE TRANSPORT</v>
       </c>
       <c r="C17" t="str">
-        <v/>
+        <v>Transport courant : colis 24/48h si annonce avant 14h30 ; palette 24/48/72h selon zone si annonce avant 11h30 ; avant midi si depart hors Bouguenais</v>
       </c>
       <c r="D17" t="str">
-        <v/>
+        <v>Nicolas NAROLLE ou Paul LAPYRE</v>
       </c>
       <c r="E17" t="str">
-        <v/>
+        <v>NON</v>
       </c>
       <c r="F17" t="str">
-        <v/>
+        <v>NON</v>
       </c>
       <c r="G17" t="str">
-        <v/>
+        <v>24-72h selon type</v>
       </c>
       <c r="H17" t="str">
-        <v/>
+        <v>date livraison annoncee</v>
       </c>
     </row>
     <row r="18">
@@ -10529,25 +11157,25 @@
         <v>2</v>
       </c>
       <c r="B18" t="str">
-        <v/>
+        <v>DEMANDE DE TRANSPORT URGENT</v>
       </c>
       <c r="C18" t="str">
-        <v/>
+        <v>Transport express (case URGENCE = OUI) : traitement prioritaire</v>
       </c>
       <c r="D18" t="str">
-        <v/>
+        <v>Nicolas NAROLLE ou Paul LAPYRE</v>
       </c>
       <c r="E18" t="str">
-        <v/>
+        <v>NON</v>
       </c>
       <c r="F18" t="str">
-        <v/>
+        <v>NON</v>
       </c>
       <c r="G18" t="str">
-        <v/>
+        <v>24h max</v>
       </c>
       <c r="H18" t="str">
-        <v/>
+        <v>date livraison annoncee</v>
       </c>
     </row>
     <row r="19">
@@ -10758,22 +11386,22 @@
         <v>5</v>
       </c>
       <c r="B29" t="str">
-        <v/>
+        <v>Prestation</v>
       </c>
       <c r="C29" t="str">
-        <v/>
+        <v>select</v>
       </c>
       <c r="D29" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="E29" t="str">
-        <v/>
+        <v>COMMUN</v>
       </c>
       <c r="F29" t="str">
-        <v/>
+        <v>demandeur</v>
       </c>
       <c r="G29" t="str">
-        <v/>
+        <v>2 valeurs</v>
       </c>
     </row>
     <row r="30">
@@ -10781,22 +11409,22 @@
         <v>6</v>
       </c>
       <c r="B30" t="str">
-        <v/>
+        <v>Filiale</v>
       </c>
       <c r="C30" t="str">
-        <v/>
+        <v>select</v>
       </c>
       <c r="D30" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="E30" t="str">
-        <v/>
+        <v>COMMUN</v>
       </c>
       <c r="F30" t="str">
-        <v/>
+        <v>demandeur</v>
       </c>
       <c r="G30" t="str">
-        <v/>
+        <v>KEON/NASKEO/KEONBIO/TERGREEN/SYCOMORE/TEIKEI/CERES/AUNIS/SURG/DOLE/OUZO/VINZ/AKEN45</v>
       </c>
     </row>
     <row r="31">
@@ -10804,19 +11432,19 @@
         <v>7</v>
       </c>
       <c r="B31" t="str">
-        <v/>
+        <v>Code Projet</v>
       </c>
       <c r="C31" t="str">
-        <v/>
+        <v>text</v>
       </c>
       <c r="D31" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="E31" t="str">
-        <v/>
+        <v>COMMUN</v>
       </c>
       <c r="F31" t="str">
-        <v/>
+        <v>demandeur</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -10827,22 +11455,22 @@
         <v>8</v>
       </c>
       <c r="B32" t="str">
-        <v/>
+        <v>Quotation / Organisation sans quotation</v>
       </c>
       <c r="C32" t="str">
-        <v/>
+        <v>select</v>
       </c>
       <c r="D32" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="E32" t="str">
-        <v/>
+        <v>COMMUN</v>
       </c>
       <c r="F32" t="str">
-        <v/>
+        <v>demandeur</v>
       </c>
       <c r="G32" t="str">
-        <v/>
+        <v>liste a definir</v>
       </c>
     </row>
     <row r="33">
@@ -10850,22 +11478,22 @@
         <v>9</v>
       </c>
       <c r="B33" t="str">
-        <v/>
+        <v>URGENCE</v>
       </c>
       <c r="C33" t="str">
-        <v/>
+        <v>bool</v>
       </c>
       <c r="D33" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="E33" t="str">
-        <v/>
+        <v>COMMUN</v>
       </c>
       <c r="F33" t="str">
-        <v/>
+        <v>demandeur</v>
       </c>
       <c r="G33" t="str">
-        <v/>
+        <v>cocher si transport express</v>
       </c>
     </row>
     <row r="34">
@@ -10873,96 +11501,180 @@
         <v>10</v>
       </c>
       <c r="B34" t="str">
-        <v/>
+        <v>Nature de la marchandise</v>
       </c>
       <c r="C34" t="str">
-        <v/>
+        <v>text</v>
       </c>
       <c r="D34" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="E34" t="str">
-        <v/>
+        <v>COMMUN</v>
       </c>
       <c r="F34" t="str">
-        <v/>
+        <v>demandeur</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="str">
-        <v/>
+      <c r="A35">
+        <v>11</v>
+      </c>
+      <c r="B35" t="str">
+        <v>DEPART DU STOCK BGN</v>
+      </c>
+      <c r="C35" t="str">
+        <v>bool</v>
+      </c>
+      <c r="D35" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="E35" t="str">
+        <v>COMMUN</v>
+      </c>
+      <c r="F35" t="str">
+        <v>demandeur</v>
+      </c>
+      <c r="G35" t="str">
+        <v>OUI = depart Bouguenais / NON = autre adresse</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="str">
-        <v># Aide types</v>
+      <c r="A36">
+        <v>12</v>
       </c>
       <c r="B36" t="str">
-        <v>text / textarea / number / date / datetime / select / multi-select / bool / files / profile / company / department</v>
+        <v>Adresse complete d expedition</v>
+      </c>
+      <c r="C36" t="str">
+        <v>textarea</v>
+      </c>
+      <c r="D36" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="E36" t="str">
+        <v>COMMUN</v>
+      </c>
+      <c r="F36" t="str">
+        <v>demandeur</v>
+      </c>
+      <c r="G36" t="str">
+        <v>requis si DEPART STOCK BGN = NON</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="str">
-        <v># Communs OU prestation</v>
+      <c r="A37">
+        <v>13</v>
       </c>
       <c r="B37" t="str">
-        <v>COMMUN ou nom(s) prestation(s) separes par |</v>
+        <v>Nom - Prenom expediteur</v>
+      </c>
+      <c r="C37" t="str">
+        <v>text</v>
+      </c>
+      <c r="D37" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="E37" t="str">
+        <v>COMMUN</v>
+      </c>
+      <c r="F37" t="str">
+        <v>demandeur</v>
+      </c>
+      <c r="G37" t="str">
+        <v>requis si DEPART STOCK BGN = NON</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="str">
-        <v/>
+      <c r="A38">
+        <v>14</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Numero de telephone expediteur</v>
+      </c>
+      <c r="C38" t="str">
+        <v>text</v>
+      </c>
+      <c r="D38" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="E38" t="str">
+        <v>COMMUN</v>
+      </c>
+      <c r="F38" t="str">
+        <v>demandeur</v>
+      </c>
+      <c r="G38" t="str">
+        <v>requis si DEPART STOCK BGN = NON</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="str">
-        <v>### 4. WORKFLOW (etats et transitions) ###</v>
+      <c r="A39">
+        <v>15</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Adresse complete de livraison</v>
+      </c>
+      <c r="C39" t="str">
+        <v>textarea</v>
+      </c>
+      <c r="D39" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="E39" t="str">
+        <v>COMMUN</v>
+      </c>
+      <c r="F39" t="str">
+        <v>demandeur</v>
+      </c>
+      <c r="G39" t="str">
+        <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="str">
-        <v>#</v>
+      <c r="A40">
+        <v>16</v>
       </c>
       <c r="B40" t="str">
-        <v>Statut</v>
+        <v>Nom - Prenom destinataire</v>
       </c>
       <c r="C40" t="str">
-        <v>Description</v>
+        <v>text</v>
       </c>
       <c r="D40" t="str">
-        <v>Qui agit ?</v>
+        <v>OUI</v>
       </c>
       <c r="E40" t="str">
-        <v>Statuts suivants</v>
+        <v>COMMUN</v>
       </c>
       <c r="F40" t="str">
-        <v>Action UI (label bouton)</v>
+        <v>demandeur</v>
       </c>
       <c r="G40" t="str">
-        <v>Effet</v>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B41" t="str">
-        <v>soumise</v>
+        <v>Numero de telephone destinataire</v>
       </c>
       <c r="C41" t="str">
-        <v>Demande creee</v>
+        <v>text</v>
       </c>
       <c r="D41" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="E41" t="str">
-        <v/>
+        <v>COMMUN</v>
       </c>
       <c r="F41" t="str">
-        <v/>
+        <v>demandeur</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -10970,22 +11682,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="B42" t="str">
-        <v>affectee</v>
+        <v>NOMBRE DE COLIS</v>
       </c>
       <c r="C42" t="str">
-        <v>Affectee a executant</v>
+        <v>number</v>
       </c>
       <c r="D42" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="E42" t="str">
-        <v/>
+        <v>COMMUN</v>
       </c>
       <c r="F42" t="str">
-        <v/>
+        <v>demandeur</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -10993,1181 +11705,1655 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="B43" t="str">
-        <v>en_cours</v>
+        <v>Type de colis</v>
       </c>
       <c r="C43" t="str">
-        <v>En cours</v>
+        <v>select</v>
       </c>
       <c r="D43" t="str">
-        <v/>
+        <v>NON</v>
       </c>
       <c r="E43" t="str">
-        <v/>
+        <v>COMMUN</v>
       </c>
       <c r="F43" t="str">
-        <v/>
+        <v>demandeur</v>
       </c>
       <c r="G43" t="str">
-        <v/>
+        <v>colis / palette / autre</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="B44" t="str">
-        <v>a_valider</v>
+        <v>Date souhaitee enlevement</v>
       </c>
       <c r="C44" t="str">
-        <v>Attente validation</v>
+        <v>date</v>
       </c>
       <c r="D44" t="str">
-        <v/>
+        <v>NON</v>
       </c>
       <c r="E44" t="str">
-        <v/>
+        <v>COMMUN</v>
       </c>
       <c r="F44" t="str">
-        <v/>
+        <v>demandeur</v>
       </c>
       <c r="G44" t="str">
-        <v/>
+        <v>indicatif</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="B45" t="str">
-        <v>complement_demande</v>
+        <v>Date prise en charge</v>
       </c>
       <c r="C45" t="str">
-        <v>Manque info</v>
+        <v>date</v>
       </c>
       <c r="D45" t="str">
-        <v/>
+        <v>NON</v>
       </c>
       <c r="E45" t="str">
-        <v/>
+        <v>COMMUN</v>
       </c>
       <c r="F45" t="str">
-        <v/>
+        <v>cible</v>
       </c>
       <c r="G45" t="str">
-        <v/>
+        <v>remplie par logistique a la planification</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B46" t="str">
-        <v>realisee</v>
+        <v>Transporteur</v>
       </c>
       <c r="C46" t="str">
-        <v>Terminee</v>
+        <v>text</v>
       </c>
       <c r="D46" t="str">
-        <v>-</v>
+        <v>NON</v>
       </c>
       <c r="E46" t="str">
-        <v>-</v>
+        <v>COMMUN</v>
       </c>
       <c r="F46" t="str">
-        <v>-</v>
+        <v>cible</v>
       </c>
       <c r="G46" t="str">
-        <v>terminal</v>
+        <v>remplie par logistique</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="B47" t="str">
-        <v>cloturee</v>
+        <v>N° de suivi transporteur</v>
       </c>
       <c r="C47" t="str">
-        <v>Cloturee</v>
+        <v>text</v>
       </c>
       <c r="D47" t="str">
-        <v>-</v>
+        <v>NON</v>
       </c>
       <c r="E47" t="str">
-        <v>-</v>
+        <v>COMMUN</v>
       </c>
       <c r="F47" t="str">
-        <v>-</v>
+        <v>cible</v>
       </c>
       <c r="G47" t="str">
-        <v>terminal</v>
+        <v>remplie par logistique</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="B48" t="str">
-        <v>abandonnee</v>
+        <v>Date livraison prevue</v>
       </c>
       <c r="C48" t="str">
-        <v>Annulee</v>
+        <v>date</v>
       </c>
       <c r="D48" t="str">
-        <v>-</v>
+        <v>NON</v>
       </c>
       <c r="E48" t="str">
-        <v>-</v>
+        <v>COMMUN</v>
       </c>
       <c r="F48" t="str">
-        <v>-</v>
+        <v>cible</v>
       </c>
       <c r="G48" t="str">
-        <v>terminal</v>
+        <v>remplie par logistique</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="str">
-        <v/>
+      <c r="A49">
+        <v>25</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Date livraison effective</v>
+      </c>
+      <c r="C49" t="str">
+        <v>date</v>
+      </c>
+      <c r="D49" t="str">
+        <v>NON</v>
+      </c>
+      <c r="E49" t="str">
+        <v>COMMUN</v>
+      </c>
+      <c r="F49" t="str">
+        <v>cible</v>
+      </c>
+      <c r="G49" t="str">
+        <v>remplie a la cloture</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="str">
-        <v>### 5. SOUS-TACHES (uniquement si demande genere multi-taches) ###</v>
+      <c r="A50">
+        <v>26</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Cout</v>
+      </c>
+      <c r="C50" t="str">
+        <v>number</v>
+      </c>
+      <c r="D50" t="str">
+        <v>NON</v>
+      </c>
+      <c r="E50" t="str">
+        <v>COMMUN</v>
+      </c>
+      <c r="F50" t="str">
+        <v>cible</v>
+      </c>
+      <c r="G50" t="str">
+        <v>optionnel</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>#</v>
-      </c>
-      <c r="B51" t="str">
-        <v>Prestation</v>
-      </c>
-      <c r="C51" t="str">
-        <v>Sous-tache</v>
-      </c>
-      <c r="D51" t="str">
-        <v>Service cible</v>
-      </c>
-      <c r="E51" t="str">
-        <v>Affectation</v>
-      </c>
-      <c r="F51" t="str">
-        <v>Validateur N1</v>
-      </c>
-      <c r="G51" t="str">
-        <v>Duree</v>
-      </c>
-      <c r="H51" t="str">
-        <v>Ordre</v>
-      </c>
-      <c r="I51" t="str">
-        <v>Parallele ?</v>
+        <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52">
-        <v>1</v>
+      <c r="A52" t="str">
+        <v># Aide types</v>
       </c>
       <c r="B52" t="str">
-        <v/>
-      </c>
-      <c r="C52" t="str">
-        <v/>
-      </c>
-      <c r="D52" t="str">
-        <v/>
-      </c>
-      <c r="E52" t="str">
-        <v/>
-      </c>
-      <c r="F52" t="str">
-        <v/>
-      </c>
-      <c r="G52" t="str">
-        <v/>
-      </c>
-      <c r="H52">
-        <v>0</v>
-      </c>
-      <c r="I52" t="str">
-        <v>OUI</v>
+        <v>text / textarea / number / date / datetime / select / multi-select / bool / files / profile / company / department</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53">
-        <v>2</v>
+      <c r="A53" t="str">
+        <v># Communs OU prestation</v>
       </c>
       <c r="B53" t="str">
-        <v/>
-      </c>
-      <c r="C53" t="str">
-        <v/>
-      </c>
-      <c r="D53" t="str">
-        <v/>
-      </c>
-      <c r="E53" t="str">
-        <v/>
-      </c>
-      <c r="F53" t="str">
-        <v/>
-      </c>
-      <c r="G53" t="str">
-        <v/>
-      </c>
-      <c r="H53">
-        <v>0</v>
-      </c>
-      <c r="I53" t="str">
-        <v>OUI</v>
+        <v>COMMUN ou nom(s) prestation(s) separes par |</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54">
-        <v>3</v>
-      </c>
-      <c r="B54" t="str">
-        <v/>
-      </c>
-      <c r="C54" t="str">
-        <v/>
-      </c>
-      <c r="D54" t="str">
-        <v/>
-      </c>
-      <c r="E54" t="str">
-        <v/>
-      </c>
-      <c r="F54" t="str">
-        <v/>
-      </c>
-      <c r="G54" t="str">
-        <v/>
-      </c>
-      <c r="H54">
-        <v>0</v>
-      </c>
-      <c r="I54" t="str">
-        <v>OUI</v>
+      <c r="A54" t="str">
+        <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v/>
+        <v>### 4. WORKFLOW (etats et transitions) ###</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>### 6. NOTIFICATIONS ###</v>
+        <v>#</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Statut</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Description</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Qui agit ?</v>
+      </c>
+      <c r="E56" t="str">
+        <v>Statuts suivants</v>
+      </c>
+      <c r="F56" t="str">
+        <v>Action UI (label bouton)</v>
+      </c>
+      <c r="G56" t="str">
+        <v>Effet</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="str">
-        <v>#</v>
+      <c r="A57">
+        <v>1</v>
       </c>
       <c r="B57" t="str">
-        <v>Evenement</v>
+        <v>soumise</v>
       </c>
       <c r="C57" t="str">
-        <v>Destinataire(s)</v>
+        <v>Demande creee</v>
       </c>
       <c r="D57" t="str">
-        <v>Canal</v>
+        <v>(auto)</v>
       </c>
       <c r="E57" t="str">
-        <v>Message</v>
+        <v>affectee</v>
       </c>
       <c r="F57" t="str">
-        <v>Priorite</v>
+        <v>-</v>
+      </c>
+      <c r="G57" t="str">
+        <v>auto-affectee a Nicolas/Paul</v>
       </c>
     </row>
     <row r="58">
       <c r="A58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B58" t="str">
-        <v>Demande soumise</v>
+        <v>affectee</v>
       </c>
       <c r="C58" t="str">
-        <v/>
+        <v>Recue par logistique</v>
       </c>
       <c r="D58" t="str">
-        <v>in-app</v>
+        <v>Nicolas NAROLLE / Paul LAPYRE</v>
       </c>
       <c r="E58" t="str">
-        <v/>
+        <v>planifiee / complement_demande / abandonnee</v>
       </c>
       <c r="F58" t="str">
-        <v>normale</v>
+        <v>Prendre en charge</v>
+      </c>
+      <c r="G58" t="str">
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B59" t="str">
-        <v>Affectation</v>
+        <v>complement_demande</v>
       </c>
       <c r="C59" t="str">
-        <v/>
+        <v>Manque info</v>
       </c>
       <c r="D59" t="str">
-        <v>in-app</v>
+        <v>demandeur</v>
       </c>
       <c r="E59" t="str">
-        <v/>
+        <v>affectee</v>
       </c>
       <c r="F59" t="str">
-        <v>normale</v>
+        <v>J ai repondu</v>
+      </c>
+      <c r="G59" t="str">
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B60" t="str">
-        <v>Demande validation</v>
+        <v>planifiee</v>
       </c>
       <c r="C60" t="str">
-        <v/>
+        <v>Date prise en charge fixee</v>
       </c>
       <c r="D60" t="str">
-        <v>in-app</v>
+        <v>Nicolas NAROLLE / Paul LAPYRE</v>
       </c>
       <c r="E60" t="str">
-        <v/>
+        <v>en_enlevement / en_livraison</v>
       </c>
       <c r="F60" t="str">
-        <v>haute</v>
+        <v>Demarrer enlevement</v>
+      </c>
+      <c r="G60" t="str">
+        <v>date prise en charge renseignee</v>
       </c>
     </row>
     <row r="61">
       <c r="A61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B61" t="str">
-        <v>Complement demande</v>
+        <v>en_enlevement</v>
       </c>
       <c r="C61" t="str">
-        <v/>
+        <v>Enlevement chez expediteur en cours</v>
       </c>
       <c r="D61" t="str">
-        <v>in-app</v>
+        <v>transporteur</v>
       </c>
       <c r="E61" t="str">
-        <v/>
+        <v>en_livraison</v>
       </c>
       <c r="F61" t="str">
-        <v>haute</v>
+        <v>Enleve</v>
+      </c>
+      <c r="G61" t="str">
+        <v>uniquement si DEPART STOCK BGN = NON</v>
       </c>
     </row>
     <row r="62">
       <c r="A62">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B62" t="str">
-        <v>Validee / Refusee</v>
+        <v>en_livraison</v>
       </c>
       <c r="C62" t="str">
-        <v/>
+        <v>Colis en cours de livraison</v>
       </c>
       <c r="D62" t="str">
-        <v>in-app</v>
+        <v>transporteur</v>
       </c>
       <c r="E62" t="str">
-        <v/>
+        <v>livree</v>
       </c>
       <c r="F62" t="str">
-        <v>normale</v>
+        <v>Livre</v>
+      </c>
+      <c r="G62" t="str">
+        <v>date livraison prevue communiquee</v>
       </c>
     </row>
     <row r="63">
       <c r="A63">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B63" t="str">
-        <v>Cloturee</v>
+        <v>livree</v>
       </c>
       <c r="C63" t="str">
-        <v/>
+        <v>Livraison effective confirmee</v>
       </c>
       <c r="D63" t="str">
-        <v>in-app</v>
+        <v>Nicolas NAROLLE / Paul LAPYRE</v>
       </c>
       <c r="E63" t="str">
-        <v/>
+        <v>cloturee</v>
       </c>
       <c r="F63" t="str">
-        <v>normale</v>
+        <v>Cloturer</v>
+      </c>
+      <c r="G63" t="str">
+        <v>date livraison effective renseignee</v>
       </c>
     </row>
     <row r="64">
       <c r="A64">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B64" t="str">
-        <v>SLA depasse</v>
+        <v>cloturee</v>
       </c>
       <c r="C64" t="str">
-        <v/>
+        <v>Demande cloturee</v>
       </c>
       <c r="D64" t="str">
-        <v>in-app</v>
+        <v>-</v>
       </c>
       <c r="E64" t="str">
-        <v/>
+        <v>-</v>
       </c>
       <c r="F64" t="str">
-        <v>urgente</v>
+        <v>-</v>
+      </c>
+      <c r="G64" t="str">
+        <v>terminal</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="str">
-        <v/>
+      <c r="A65">
+        <v>9</v>
+      </c>
+      <c r="B65" t="str">
+        <v>abandonnee</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Annulee</v>
+      </c>
+      <c r="D65" t="str">
+        <v>demandeur ou cible</v>
+      </c>
+      <c r="E65" t="str">
+        <v>-</v>
+      </c>
+      <c r="F65" t="str">
+        <v>-</v>
+      </c>
+      <c r="G65" t="str">
+        <v>terminal</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v># Note</v>
-      </c>
-      <c r="B66" t="str">
-        <v>Le commentaire de tache est deja gere par le trigger BE-010 (notif assigne+manager+demandeur). Inutile de le re-declarer.</v>
+        <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v/>
+        <v>### 5. SOUS-TACHES (uniquement si demande genere multi-taches) ###</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>### 7. KPI DASHBOARD ###</v>
+        <v>#</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Prestation</v>
+      </c>
+      <c r="C68" t="str">
+        <v>Sous-tache</v>
+      </c>
+      <c r="D68" t="str">
+        <v>Service cible</v>
+      </c>
+      <c r="E68" t="str">
+        <v>Affectation</v>
+      </c>
+      <c r="F68" t="str">
+        <v>Validateur N1</v>
+      </c>
+      <c r="G68" t="str">
+        <v>Duree</v>
+      </c>
+      <c r="H68" t="str">
+        <v>Ordre</v>
+      </c>
+      <c r="I68" t="str">
+        <v>Parallele ?</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="str">
-        <v>#</v>
+      <c r="A69">
+        <v>1</v>
       </c>
       <c r="B69" t="str">
-        <v>KPI (label)</v>
+        <v>DEMANDE DE TRANSPORT</v>
       </c>
       <c r="C69" t="str">
-        <v>Formule</v>
+        <v>Organiser enlevement chez expediteur</v>
       </c>
       <c r="D69" t="str">
-        <v>Couleur</v>
+        <v>Logistique</v>
+      </c>
+      <c r="E69" t="str">
+        <v>Nicolas / Paul</v>
+      </c>
+      <c r="F69" t="str">
+        <v>NON</v>
+      </c>
+      <c r="G69" t="str">
+        <v>4h</v>
+      </c>
+      <c r="H69">
+        <v>1</v>
+      </c>
+      <c r="I69" t="str">
+        <v>NON</v>
       </c>
     </row>
     <row r="70">
       <c r="A70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B70" t="str">
-        <v>Total actives</v>
+        <v>DEMANDE DE TRANSPORT</v>
       </c>
       <c r="C70" t="str">
-        <v>count(status NOT IN terminaux)</v>
+        <v>Choix transporteur et reservation</v>
       </c>
       <c r="D70" t="str">
-        <v>neutre</v>
+        <v>Logistique</v>
+      </c>
+      <c r="E70" t="str">
+        <v>Nicolas / Paul</v>
+      </c>
+      <c r="F70" t="str">
+        <v>NON</v>
+      </c>
+      <c r="G70" t="str">
+        <v>2h</v>
+      </c>
+      <c r="H70">
+        <v>2</v>
+      </c>
+      <c r="I70" t="str">
+        <v>NON</v>
       </c>
     </row>
     <row r="71">
       <c r="A71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B71" t="str">
-        <v>En retard</v>
+        <v>DEMANDE DE TRANSPORT</v>
       </c>
       <c r="C71" t="str">
-        <v>count(due_date &lt; today AND active)</v>
+        <v>Suivi livraison</v>
       </c>
       <c r="D71" t="str">
-        <v>rouge</v>
+        <v>Logistique</v>
+      </c>
+      <c r="E71" t="str">
+        <v>Nicolas / Paul</v>
+      </c>
+      <c r="F71" t="str">
+        <v>NON</v>
+      </c>
+      <c r="G71" t="str">
+        <v>variable</v>
+      </c>
+      <c r="H71">
+        <v>3</v>
+      </c>
+      <c r="I71" t="str">
+        <v>NON</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72">
-        <v>3</v>
-      </c>
-      <c r="B72" t="str">
-        <v>A valider</v>
-      </c>
-      <c r="C72" t="str">
-        <v>count(status=a_valider)</v>
-      </c>
-      <c r="D72" t="str">
-        <v>ambre</v>
+      <c r="A72" t="str">
+        <v/>
       </c>
     </row>
     <row r="73">
-      <c r="A73">
-        <v>4</v>
-      </c>
-      <c r="B73" t="str">
-        <v>Non assignees</v>
-      </c>
-      <c r="C73" t="str">
-        <v>count(assignee_id IS NULL AND active)</v>
-      </c>
-      <c r="D73" t="str">
-        <v>violet</v>
+      <c r="A73" t="str">
+        <v>### 6. NOTIFICATIONS ###</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v/>
+        <v>#</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Evenement</v>
+      </c>
+      <c r="C74" t="str">
+        <v>Destinataire(s)</v>
+      </c>
+      <c r="D74" t="str">
+        <v>Canal</v>
+      </c>
+      <c r="E74" t="str">
+        <v>Message</v>
+      </c>
+      <c r="F74" t="str">
+        <v>Priorite</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="str">
-        <v># Filtres souhaites</v>
+      <c r="A75">
+        <v>1</v>
       </c>
       <c r="B75" t="str">
-        <v>Active ?</v>
+        <v>Demande soumise</v>
       </c>
       <c r="C75" t="str">
-        <v>Notes</v>
+        <v>Nicolas NAROLLE + Paul LAPYRE</v>
+      </c>
+      <c r="D75" t="str">
+        <v>in-app</v>
+      </c>
+      <c r="E75" t="str">
+        <v>Nouvelle demande de transport &lt;filiale&gt; - &lt;code_projet&gt; de &lt;demandeur&gt;</v>
+      </c>
+      <c r="F75" t="str">
+        <v>normale</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="str">
-        <v>Recherche libre</v>
+      <c r="A76">
+        <v>2</v>
       </c>
       <c r="B76" t="str">
-        <v>OUI</v>
+        <v>URGENCE = OUI</v>
       </c>
       <c r="C76" t="str">
-        <v>titre / numero</v>
+        <v>Nicolas NAROLLE + Paul LAPYRE</v>
+      </c>
+      <c r="D76" t="str">
+        <v>in-app + email</v>
+      </c>
+      <c r="E76" t="str">
+        <v>TRANSPORT URGENT : &lt;filiale&gt; - &lt;nature_marchandise&gt; - &lt;demandeur&gt;</v>
+      </c>
+      <c r="F76" t="str">
+        <v>urgente</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="str">
-        <v>Statut</v>
+      <c r="A77">
+        <v>3</v>
       </c>
       <c r="B77" t="str">
-        <v>OUI</v>
+        <v>Affectation</v>
       </c>
       <c r="C77" t="str">
-        <v/>
+        <v>demandeur</v>
+      </c>
+      <c r="D77" t="str">
+        <v>in-app</v>
+      </c>
+      <c r="E77" t="str">
+        <v>Votre demande de transport est prise en charge par &lt;cible&gt;</v>
+      </c>
+      <c r="F77" t="str">
+        <v>normale</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="str">
-        <v>Demandeur</v>
+      <c r="A78">
+        <v>4</v>
       </c>
       <c r="B78" t="str">
-        <v>OUI</v>
+        <v>Complement demande</v>
       </c>
       <c r="C78" t="str">
-        <v/>
+        <v>demandeur</v>
+      </c>
+      <c r="D78" t="str">
+        <v>in-app</v>
+      </c>
+      <c r="E78" t="str">
+        <v>La logistique demande des informations complementaires</v>
+      </c>
+      <c r="F78" t="str">
+        <v>haute</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="str">
-        <v>Assigne</v>
+      <c r="A79">
+        <v>5</v>
       </c>
       <c r="B79" t="str">
-        <v>OUI</v>
+        <v>Planifiee (date prise en charge)</v>
       </c>
       <c r="C79" t="str">
-        <v/>
+        <v>demandeur</v>
+      </c>
+      <c r="D79" t="str">
+        <v>in-app + email</v>
+      </c>
+      <c r="E79" t="str">
+        <v>Votre transport sera pris en charge le &lt;date_prise_en_charge&gt;</v>
+      </c>
+      <c r="F79" t="str">
+        <v>normale</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="str">
-        <v>En retard (toggle)</v>
+      <c r="A80">
+        <v>6</v>
       </c>
       <c r="B80" t="str">
-        <v>OUI</v>
+        <v>Date livraison prevue</v>
       </c>
       <c r="C80" t="str">
-        <v/>
+        <v>demandeur</v>
+      </c>
+      <c r="D80" t="str">
+        <v>in-app + email</v>
+      </c>
+      <c r="E80" t="str">
+        <v>Date de livraison prevue : &lt;date_livraison_prevue&gt; par &lt;transporteur&gt; (suivi &lt;num_suivi&gt;)</v>
+      </c>
+      <c r="F80" t="str">
+        <v>normale</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="str">
-        <v>Prestation</v>
+      <c r="A81">
+        <v>7</v>
       </c>
       <c r="B81" t="str">
-        <v/>
+        <v>Livree</v>
       </c>
       <c r="C81" t="str">
-        <v/>
+        <v>demandeur + manager demandeur</v>
+      </c>
+      <c r="D81" t="str">
+        <v>in-app + email</v>
+      </c>
+      <c r="E81" t="str">
+        <v>Votre colis a ete livre le &lt;date_livraison_effective&gt;</v>
+      </c>
+      <c r="F81" t="str">
+        <v>normale</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="str">
-        <v>Filtre metier 1</v>
+      <c r="A82">
+        <v>8</v>
       </c>
       <c r="B82" t="str">
-        <v/>
+        <v>Cloturee</v>
       </c>
       <c r="C82" t="str">
-        <v/>
+        <v>demandeur</v>
+      </c>
+      <c r="D82" t="str">
+        <v>in-app</v>
+      </c>
+      <c r="E82" t="str">
+        <v>Demande de transport &lt;id&gt; cloturee</v>
+      </c>
+      <c r="F82" t="str">
+        <v>normale</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="str">
-        <v/>
+      <c r="A83">
+        <v>9</v>
+      </c>
+      <c r="B83" t="str">
+        <v>SLA depasse</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Nicolas NAROLLE + Paul LAPYRE + manager</v>
+      </c>
+      <c r="D83" t="str">
+        <v>in-app</v>
+      </c>
+      <c r="E83" t="str">
+        <v>SLA depasse sur demande &lt;id&gt;</v>
+      </c>
+      <c r="F83" t="str">
+        <v>urgente</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>### 8. PERMISSIONS ###</v>
+        <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Action</v>
+        <v># Note</v>
       </c>
       <c r="B85" t="str">
-        <v>Demandeur</v>
-      </c>
-      <c r="C85" t="str">
-        <v>Executant/Cible</v>
-      </c>
-      <c r="D85" t="str">
-        <v>Manager service</v>
-      </c>
-      <c r="E85" t="str">
-        <v>Validateur N1</v>
-      </c>
-      <c r="F85" t="str">
-        <v>Validateur N2</v>
-      </c>
-      <c r="G85" t="str">
-        <v>Admin</v>
-      </c>
-      <c r="H85" t="str">
-        <v>Autre</v>
+        <v>Le commentaire de tache est deja gere par le trigger BE-010 (notif assigne+manager+demandeur). Inutile de le re-declarer.</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Creer demande</v>
-      </c>
-      <c r="B86" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="C86" t="str">
-        <v/>
-      </c>
-      <c r="D86" t="str">
-        <v/>
-      </c>
-      <c r="E86" t="str">
-        <v/>
-      </c>
-      <c r="F86" t="str">
-        <v/>
-      </c>
-      <c r="G86" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="H86" t="str">
         <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Voir ses demandes</v>
-      </c>
-      <c r="B87" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="C87" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="D87" t="str">
-        <v/>
-      </c>
-      <c r="E87" t="str">
-        <v/>
-      </c>
-      <c r="F87" t="str">
-        <v/>
-      </c>
-      <c r="G87" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="H87" t="str">
-        <v/>
+        <v>### 7. KPI DASHBOARD ###</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Voir TOUTES</v>
+        <v>#</v>
       </c>
       <c r="B88" t="str">
-        <v/>
+        <v>KPI (label)</v>
       </c>
       <c r="C88" t="str">
-        <v/>
+        <v>Formule</v>
       </c>
       <c r="D88" t="str">
-        <v/>
-      </c>
-      <c r="E88" t="str">
-        <v/>
-      </c>
-      <c r="F88" t="str">
-        <v/>
-      </c>
-      <c r="G88" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="H88" t="str">
-        <v/>
+        <v>Couleur</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="str">
-        <v>Affecter</v>
+      <c r="A89">
+        <v>1</v>
       </c>
       <c r="B89" t="str">
-        <v/>
+        <v>Demandes en cours</v>
       </c>
       <c r="C89" t="str">
-        <v/>
+        <v>count(status NOT IN (cloturee, abandonnee))</v>
       </c>
       <c r="D89" t="str">
-        <v/>
-      </c>
-      <c r="E89" t="str">
-        <v/>
-      </c>
-      <c r="F89" t="str">
-        <v/>
-      </c>
-      <c r="G89" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="H89" t="str">
-        <v/>
+        <v>neutre</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="str">
-        <v>Reaffecter</v>
+      <c r="A90">
+        <v>2</v>
       </c>
       <c r="B90" t="str">
-        <v/>
+        <v>Urgentes a traiter</v>
       </c>
       <c r="C90" t="str">
-        <v/>
+        <v>count(URGENCE=OUI AND status IN (soumise, affectee))</v>
       </c>
       <c r="D90" t="str">
-        <v/>
-      </c>
-      <c r="E90" t="str">
-        <v/>
-      </c>
-      <c r="F90" t="str">
-        <v/>
-      </c>
-      <c r="G90" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="H90" t="str">
-        <v/>
+        <v>rouge</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="str">
-        <v>Annuler</v>
+      <c r="A91">
+        <v>3</v>
       </c>
       <c r="B91" t="str">
-        <v>sienne</v>
+        <v>A planifier</v>
       </c>
       <c r="C91" t="str">
-        <v/>
+        <v>count(status=affectee)</v>
       </c>
       <c r="D91" t="str">
-        <v/>
-      </c>
-      <c r="E91" t="str">
-        <v/>
-      </c>
-      <c r="F91" t="str">
-        <v/>
-      </c>
-      <c r="G91" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="H91" t="str">
-        <v/>
+        <v>ambre</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="str">
-        <v>Valider N1</v>
+      <c r="A92">
+        <v>4</v>
       </c>
       <c r="B92" t="str">
-        <v/>
+        <v>En livraison</v>
       </c>
       <c r="C92" t="str">
-        <v/>
+        <v>count(status IN (en_enlevement, en_livraison))</v>
       </c>
       <c r="D92" t="str">
-        <v/>
-      </c>
-      <c r="E92" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="F92" t="str">
-        <v/>
-      </c>
-      <c r="G92" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="H92" t="str">
-        <v/>
+        <v>bleu</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="str">
-        <v>Valider N2</v>
+      <c r="A93">
+        <v>5</v>
       </c>
       <c r="B93" t="str">
-        <v/>
+        <v>Livrees ce mois</v>
       </c>
       <c r="C93" t="str">
-        <v/>
+        <v>count(status=livree AND month=current)</v>
       </c>
       <c r="D93" t="str">
-        <v/>
-      </c>
-      <c r="E93" t="str">
-        <v/>
-      </c>
-      <c r="F93" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="G93" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="H93" t="str">
-        <v/>
+        <v>vert</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="str">
-        <v/>
+      <c r="A94">
+        <v>6</v>
+      </c>
+      <c r="B94" t="str">
+        <v>En retard / SLA depasse</v>
+      </c>
+      <c r="C94" t="str">
+        <v>count(date_livraison_prevue &lt; today AND status NOT IN (livree, cloturee))</v>
+      </c>
+      <c r="D94" t="str">
+        <v>rouge</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="str">
-        <v>### 9. HUB PROJET / DOSSIER (si applicable) ###</v>
+      <c r="A95">
+        <v>7</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Delai moyen prise en charge (h)</v>
+      </c>
+      <c r="C95" t="str">
+        <v>avg(date_prise_en_charge - date_demande)</v>
+      </c>
+      <c r="D95" t="str">
+        <v>neutre</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="str">
-        <v>Champ</v>
+      <c r="A96">
+        <v>8</v>
       </c>
       <c r="B96" t="str">
-        <v>Valeur</v>
+        <v>Delai moyen livraison (j)</v>
       </c>
       <c r="C96" t="str">
-        <v>Aide</v>
+        <v>avg(date_livraison_effective - date_prise_en_charge)</v>
+      </c>
+      <c r="D96" t="str">
+        <v>neutre</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Hub active ?</v>
-      </c>
-      <c r="B97" t="str">
-        <v/>
-      </c>
-      <c r="C97" t="str">
-        <v>OUI / NON</v>
+        <v/>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Concept</v>
+        <v># Filtres souhaites</v>
       </c>
       <c r="B98" t="str">
-        <v/>
+        <v>Active ?</v>
       </c>
       <c r="C98" t="str">
-        <v>ex. dossier client, projet R&amp;D, audit</v>
+        <v>Notes</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Nom entite</v>
+        <v>Recherche libre</v>
       </c>
       <c r="B99" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="C99" t="str">
-        <v/>
+        <v>titre / numero</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Code/identifiant</v>
+        <v>Statut</v>
       </c>
       <c r="B100" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="C100" t="str">
-        <v>format</v>
+        <v/>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Onglets souhaites</v>
+        <v>Demandeur</v>
       </c>
       <c r="B101" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="C101" t="str">
-        <v>Fiche / Taches / Timeline / Discussions / Fichiers</v>
+        <v/>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Visibilite</v>
+        <v>Assigne</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="C102" t="str">
-        <v>qui peut lire / ecrire</v>
+        <v/>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
+        <v>En retard (toggle)</v>
+      </c>
+      <c r="B103" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="C103" t="str">
         <v/>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>### 10. INTEGRATIONS EXTERNES ###</v>
+        <v>Prestation</v>
+      </c>
+      <c r="B104" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="C104" t="str">
+        <v/>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Outil</v>
+        <v>Filtre metier 1</v>
       </c>
       <c r="B105" t="str">
-        <v>Pour quoi ?</v>
+        <v>OUI</v>
       </c>
       <c r="C105" t="str">
-        <v>Sens</v>
-      </c>
-      <c r="D105" t="str">
-        <v>Statut</v>
-      </c>
-      <c r="E105" t="str">
-        <v>Priorite</v>
+        <v>Filiale / Code projet / URGENCE / Depart BGN / Transporteur</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Lucca</v>
-      </c>
-      <c r="B106" t="str">
-        <v/>
-      </c>
-      <c r="C106" t="str">
-        <v/>
-      </c>
-      <c r="D106" t="str">
-        <v/>
-      </c>
-      <c r="E106" t="str">
         <v/>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Yooz</v>
-      </c>
-      <c r="B107" t="str">
-        <v/>
-      </c>
-      <c r="C107" t="str">
-        <v/>
-      </c>
-      <c r="D107" t="str">
-        <v/>
-      </c>
-      <c r="E107" t="str">
-        <v/>
+        <v>### 8. PERMISSIONS ###</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Pipedrive</v>
+        <v>Action</v>
       </c>
       <c r="B108" t="str">
-        <v/>
+        <v>Demandeur</v>
       </c>
       <c r="C108" t="str">
-        <v/>
+        <v>Executant/Cible</v>
       </c>
       <c r="D108" t="str">
-        <v/>
+        <v>Manager service</v>
       </c>
       <c r="E108" t="str">
-        <v/>
+        <v>Validateur N1</v>
+      </c>
+      <c r="F108" t="str">
+        <v>Validateur N2</v>
+      </c>
+      <c r="G108" t="str">
+        <v>Admin</v>
+      </c>
+      <c r="H108" t="str">
+        <v>Autre</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Divalto</v>
+        <v>Creer demande</v>
       </c>
       <c r="B109" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="C109" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="D109" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="E109" t="str">
+        <v/>
+      </c>
+      <c r="F109" t="str">
+        <v/>
+      </c>
+      <c r="G109" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="H109" t="str">
         <v/>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>SharePoint</v>
+        <v>Voir ses demandes</v>
       </c>
       <c r="B110" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="C110" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="D110" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="E110" t="str">
+        <v/>
+      </c>
+      <c r="F110" t="str">
+        <v/>
+      </c>
+      <c r="G110" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="H110" t="str">
         <v/>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v/>
+        <v>Voir TOUTES</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="D111" t="str">
-        <v/>
+        <v>OUI</v>
       </c>
       <c r="E111" t="str">
+        <v/>
+      </c>
+      <c r="F111" t="str">
+        <v/>
+      </c>
+      <c r="G111" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="H111" t="str">
         <v/>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v/>
+        <v>Affecter</v>
+      </c>
+      <c r="B112" t="str">
+        <v/>
+      </c>
+      <c r="C112" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="D112" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="E112" t="str">
+        <v/>
+      </c>
+      <c r="F112" t="str">
+        <v/>
+      </c>
+      <c r="G112" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="H112" t="str">
+        <v>auto-affectation Nicolas/Paul</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>### 11. QUESTIONS OUVERTES ###</v>
+        <v>Reaffecter</v>
+      </c>
+      <c r="B113" t="str">
+        <v/>
+      </c>
+      <c r="C113" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="D113" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="E113" t="str">
+        <v/>
+      </c>
+      <c r="F113" t="str">
+        <v/>
+      </c>
+      <c r="G113" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="H113" t="str">
+        <v/>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
+        <v>Annuler</v>
+      </c>
+      <c r="B114" t="str">
+        <v>sienne avant prise en charge</v>
+      </c>
+      <c r="C114" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="D114" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="E114" t="str">
+        <v/>
+      </c>
+      <c r="F114" t="str">
+        <v/>
+      </c>
+      <c r="G114" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="H114" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>Valider N1</v>
+      </c>
+      <c r="B115" t="str">
+        <v/>
+      </c>
+      <c r="C115" t="str">
+        <v/>
+      </c>
+      <c r="D115" t="str">
+        <v/>
+      </c>
+      <c r="E115" t="str">
+        <v/>
+      </c>
+      <c r="F115" t="str">
+        <v/>
+      </c>
+      <c r="G115" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="H115" t="str">
+        <v>pas de validation N1 par defaut</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>Valider N2</v>
+      </c>
+      <c r="B116" t="str">
+        <v/>
+      </c>
+      <c r="C116" t="str">
+        <v/>
+      </c>
+      <c r="D116" t="str">
+        <v/>
+      </c>
+      <c r="E116" t="str">
+        <v/>
+      </c>
+      <c r="F116" t="str">
+        <v/>
+      </c>
+      <c r="G116" t="str">
+        <v>OUI</v>
+      </c>
+      <c r="H116" t="str">
+        <v>pas de validation N2 par defaut</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>### 9. HUB PROJET / DOSSIER (si applicable) ###</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>Champ</v>
+      </c>
+      <c r="B119" t="str">
+        <v>Valeur</v>
+      </c>
+      <c r="C119" t="str">
+        <v>Aide</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>Hub active ?</v>
+      </c>
+      <c r="B120" t="str">
+        <v>NON</v>
+      </c>
+      <c r="C120" t="str">
+        <v>demandes ponctuelles, pas de regroupement</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>Concept</v>
+      </c>
+      <c r="B121" t="str">
+        <v/>
+      </c>
+      <c r="C121" t="str">
+        <v>ex. dossier client, projet R&amp;D, audit</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>Nom entite</v>
+      </c>
+      <c r="B122" t="str">
+        <v/>
+      </c>
+      <c r="C122" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>Code/identifiant</v>
+      </c>
+      <c r="B123" t="str">
+        <v/>
+      </c>
+      <c r="C123" t="str">
+        <v>format</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>Onglets souhaites</v>
+      </c>
+      <c r="B124" t="str">
+        <v/>
+      </c>
+      <c r="C124" t="str">
+        <v>Fiche / Taches / Timeline / Discussions / Fichiers</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>Visibilite</v>
+      </c>
+      <c r="B125" t="str">
+        <v/>
+      </c>
+      <c r="C125" t="str">
+        <v>qui peut lire / ecrire</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>### 10. INTEGRATIONS EXTERNES ###</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>Outil</v>
+      </c>
+      <c r="B128" t="str">
+        <v>Pour quoi ?</v>
+      </c>
+      <c r="C128" t="str">
+        <v>Sens</v>
+      </c>
+      <c r="D128" t="str">
+        <v>Statut</v>
+      </c>
+      <c r="E128" t="str">
+        <v>Priorite</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>Lucca</v>
+      </c>
+      <c r="B129" t="str">
+        <v>annuaire collaborateurs (demandeur, manager)</v>
+      </c>
+      <c r="C129" t="str">
+        <v>lecture</v>
+      </c>
+      <c r="D129" t="str">
+        <v>a faire</v>
+      </c>
+      <c r="E129" t="str">
+        <v>normal</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>Yooz</v>
+      </c>
+      <c r="B130" t="str">
+        <v>rapprochement facture transporteur</v>
+      </c>
+      <c r="C130" t="str">
+        <v>lecture</v>
+      </c>
+      <c r="D130" t="str">
+        <v>a faire</v>
+      </c>
+      <c r="E130" t="str">
+        <v>nice-to-have</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>Pipedrive</v>
+      </c>
+      <c r="B131" t="str">
+        <v>non utilise</v>
+      </c>
+      <c r="C131" t="str">
+        <v>-</v>
+      </c>
+      <c r="D131" t="str">
+        <v>sans objet</v>
+      </c>
+      <c r="E131" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>Divalto</v>
+      </c>
+      <c r="B132" t="str">
+        <v>rattachement code projet</v>
+      </c>
+      <c r="C132" t="str">
+        <v>lecture</v>
+      </c>
+      <c r="D132" t="str">
+        <v>a faire</v>
+      </c>
+      <c r="E132" t="str">
+        <v>normal</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>SharePoint</v>
+      </c>
+      <c r="B133" t="str">
+        <v>migration depuis le formulaire actuel (liste DEMANDE DE TRANSPORT, site PIECES)</v>
+      </c>
+      <c r="C133" t="str">
+        <v>lecture (migration)</v>
+      </c>
+      <c r="D133" t="str">
+        <v>a faire</v>
+      </c>
+      <c r="E133" t="str">
+        <v>haute</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>Outlook / Email</v>
+      </c>
+      <c r="B134" t="str">
+        <v>notifications externes (transporteurs, expediteurs)</v>
+      </c>
+      <c r="C134" t="str">
+        <v>ecriture</v>
+      </c>
+      <c r="D134" t="str">
+        <v>a faire</v>
+      </c>
+      <c r="E134" t="str">
+        <v>normal</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>### 11. QUESTIONS OUVERTES ###</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
         <v>#</v>
       </c>
-      <c r="B114" t="str">
+      <c r="B137" t="str">
         <v>Question</v>
       </c>
-      <c r="C114" t="str">
+      <c r="C137" t="str">
         <v>Importance</v>
       </c>
-      <c r="D114" t="str">
+      <c r="D137" t="str">
         <v>Reponse</v>
       </c>
     </row>
-    <row r="115">
-      <c r="A115">
+    <row r="138">
+      <c r="A138">
         <v>1</v>
       </c>
-      <c r="B115" t="str">
-        <v/>
-      </c>
-      <c r="C115" t="str">
+      <c r="B138" t="str">
+        <v>Liste fermee des valeurs "Quotation / Organisation sans quotation" ?</v>
+      </c>
+      <c r="C138" t="str">
+        <v>bloquant</v>
+      </c>
+      <c r="D138" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139">
+        <v>2</v>
+      </c>
+      <c r="B139" t="str">
+        <v>Backup en cas d absence Nicolas ET Paul ?</v>
+      </c>
+      <c r="C139" t="str">
+        <v>bloquant</v>
+      </c>
+      <c r="D139" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140">
+        <v>3</v>
+      </c>
+      <c r="B140" t="str">
+        <v>Validation requise pour transports urgents (manager du demandeur) ou auto-traite ?</v>
+      </c>
+      <c r="C140" t="str">
+        <v>bloquant</v>
+      </c>
+      <c r="D140" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141">
+        <v>4</v>
+      </c>
+      <c r="B141" t="str">
+        <v>Reset des donnees SharePoint existantes ou migration historique ?</v>
+      </c>
+      <c r="C141" t="str">
+        <v>bloquant</v>
+      </c>
+      <c r="D141" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142">
+        <v>5</v>
+      </c>
+      <c r="B142" t="str">
+        <v>Saisie manuelle du transporteur ou liste fermee (Geodis, DHL, Chronopost...) ?</v>
+      </c>
+      <c r="C142" t="str">
         <v>normal</v>
       </c>
-      <c r="D115" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116">
-        <v>2</v>
-      </c>
-      <c r="B116" t="str">
-        <v/>
-      </c>
-      <c r="C116" t="str">
+      <c r="D142" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143">
+        <v>6</v>
+      </c>
+      <c r="B143" t="str">
+        <v>Integration tracking automatique via API transporteur ou saisie manuelle du n° de suivi ?</v>
+      </c>
+      <c r="C143" t="str">
         <v>normal</v>
       </c>
-      <c r="D116" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117">
-        <v>3</v>
-      </c>
-      <c r="B117" t="str">
-        <v/>
-      </c>
-      <c r="C117" t="str">
+      <c r="D143" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144">
+        <v>7</v>
+      </c>
+      <c r="B144" t="str">
+        <v>Cas d emoticones / images / PJ photos colis abime - prevoir un champ litige ?</v>
+      </c>
+      <c r="C144" t="str">
         <v>normal</v>
       </c>
-      <c r="D117" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118">
-        <v>4</v>
-      </c>
-      <c r="B118" t="str">
-        <v/>
-      </c>
-      <c r="C118" t="str">
+      <c r="D144" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145">
+        <v>8</v>
+      </c>
+      <c r="B145" t="str">
+        <v>Workflow "DEMANDE DE TRANSPORT URGENT" identique au courant ou SLA et notifs differents ?</v>
+      </c>
+      <c r="C145" t="str">
         <v>normal</v>
       </c>
-      <c r="D118" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119">
-        <v>5</v>
-      </c>
-      <c r="B119" t="str">
-        <v/>
-      </c>
-      <c r="C119" t="str">
+      <c r="D145" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146">
+        <v>9</v>
+      </c>
+      <c r="B146" t="str">
+        <v>Cout transport saisi manuellement ou import depuis Yooz ?</v>
+      </c>
+      <c r="C146" t="str">
         <v>normal</v>
       </c>
-      <c r="D119" t="str">
+      <c r="D146" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147">
+        <v>10</v>
+      </c>
+      <c r="B147" t="str">
+        <v>Quel format pour le code projet (libre, liste, masque) ? Lien Divalto ?</v>
+      </c>
+      <c r="C147" t="str">
+        <v>normal</v>
+      </c>
+      <c r="D147" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I119"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I147"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -12175,17 +13361,6 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I160"/>
-  <cols>
-    <col min="1" max="1" width="28.83203125" customWidth="1"/>
-    <col min="2" max="2" width="32.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="22.83203125" customWidth="1"/>
-    <col min="5" max="5" width="22.83203125" customWidth="1"/>
-    <col min="6" max="6" width="22.83203125" customWidth="1"/>
-    <col min="7" max="7" width="18.83203125" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -14968,17 +16143,6 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I119"/>
-  <cols>
-    <col min="1" max="1" width="28.83203125" customWidth="1"/>
-    <col min="2" max="2" width="32.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="22.83203125" customWidth="1"/>
-    <col min="5" max="5" width="22.83203125" customWidth="1"/>
-    <col min="6" max="6" width="22.83203125" customWidth="1"/>
-    <col min="7" max="7" width="18.83203125" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -16851,6 +18015,7 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:I119"/>
   </ignoredErrors>

--- a/docs/CDC/CDC_MODULES.xlsx
+++ b/docs/CDC/CDC_MODULES.xlsx
@@ -18020,4 +18020,231 @@
     <ignoredError numberStoredAsText="1" sqref="A1:I119"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009BEF677D670BB2419FA43814D38E94C6" ma:contentTypeVersion="11" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="f561f94c1b8e46644735d1ce853ee2f9">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1f379aea-0a68-417f-a19d-f15dddeacdaa" xmlns:ns3="6d8edc88-d8be-473b-8f67-5bdf8d1e078a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4583b4248361d07d1c95068a57973815" ns2:_="" ns3:_="">
+    <xsd:import namespace="1f379aea-0a68-417f-a19d-f15dddeacdaa"/>
+    <xsd:import namespace="6d8edc88-d8be-473b-8f67-5bdf8d1e078a"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="1f379aea-0a68-417f-a19d-f15dddeacdaa" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="16" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Balises d’images" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4c0effd6-da17-4831-afea-f5e423d5594b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="6d8edc88-d8be-473b-8f67-5bdf8d1e078a" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="17" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{a47a72f4-958e-4e26-862b-0add6a6ff580}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="6d8edc88-d8be-473b-8f67-5bdf8d1e078a">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Type de contenu"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titre"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1f379aea-0a68-417f-a19d-f15dddeacdaa">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="6d8edc88-d8be-473b-8f67-5bdf8d1e078a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9B80AA8-A987-4CA9-8F26-7D330FF46859}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{089F1948-9362-4EAE-9BBD-5A92C4970937}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE196307-57BD-44CC-B6E0-FD83C543DEFB}"/>
 </file>